--- a/Fakemon Region.xlsx
+++ b/Fakemon Region.xlsx
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7729" uniqueCount="2989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7723" uniqueCount="2984">
   <si>
     <t xml:space="preserve">FAKEMON - DOGON REGION</t>
   </si>
@@ -8381,21 +8381,6 @@
   </si>
   <si>
     <t xml:space="preserve">Galáxias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*****</t>
-  </si>
-  <si>
-    <t xml:space="preserve">****</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introduzido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fóssil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">********** àgua</t>
   </si>
   <si>
     <t xml:space="preserve">Kanto</t>
@@ -18313,7 +18298,7 @@
         <v>1070</v>
       </c>
       <c r="C2" s="660" t="s">
-        <v>2740</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18321,7 +18306,7 @@
         <v>1059</v>
       </c>
       <c r="C3" s="995" t="s">
-        <v>2741</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18329,7 +18314,7 @@
         <v>1067</v>
       </c>
       <c r="C4" s="995" t="s">
-        <v>2742</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18337,7 +18322,7 @@
         <v>800</v>
       </c>
       <c r="C5" s="995" t="s">
-        <v>2743</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18345,15 +18330,15 @@
         <v>797</v>
       </c>
       <c r="C6" s="995" t="s">
-        <v>2744</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="2" t="s">
-        <v>2745</v>
+        <v>2740</v>
       </c>
       <c r="C7" s="660" t="s">
-        <v>2746</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18361,7 +18346,7 @@
         <v>1442</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>2747</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18369,39 +18354,39 @@
         <v>1416</v>
       </c>
       <c r="C9" s="995" t="s">
-        <v>2748</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>2749</v>
+        <v>2744</v>
       </c>
       <c r="C10" s="995" t="s">
-        <v>2750</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="660" t="s">
-        <v>2751</v>
+        <v>2746</v>
       </c>
       <c r="C11" s="995" t="s">
-        <v>2752</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
-        <v>2753</v>
+        <v>2748</v>
       </c>
       <c r="C12" s="996" t="s">
-        <v>2754</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>2755</v>
+        <v>2750</v>
       </c>
       <c r="C13" s="995" t="s">
-        <v>2756</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18409,15 +18394,15 @@
         <v>1433</v>
       </c>
       <c r="C14" s="995" t="s">
-        <v>2757</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
-        <v>2758</v>
+        <v>2753</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>2759</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18425,7 +18410,7 @@
         <v>1566</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>2760</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18433,7 +18418,7 @@
         <v>1796</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>2761</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18441,7 +18426,7 @@
         <v>1992</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>2762</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18449,7 +18434,7 @@
         <v>1989</v>
       </c>
       <c r="C19" s="660" t="s">
-        <v>2763</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18457,7 +18442,7 @@
         <v>1809</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>2764</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18465,23 +18450,23 @@
         <v>1995</v>
       </c>
       <c r="C21" s="660" t="s">
-        <v>2765</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>2766</v>
+        <v>2761</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>2767</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>2768</v>
+        <v>2763</v>
       </c>
       <c r="C23" s="660" t="s">
-        <v>2769</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18489,15 +18474,15 @@
         <v>2160</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="C25" s="660" t="s">
-        <v>2772</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18510,31 +18495,31 @@
         <v>2246</v>
       </c>
       <c r="C27" s="660" t="s">
-        <v>2773</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>2774</v>
+        <v>2769</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>2775</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>2776</v>
+        <v>2771</v>
       </c>
       <c r="C29" s="660" t="s">
-        <v>2777</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>2778</v>
+        <v>2773</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>2779</v>
+        <v>2774</v>
       </c>
     </row>
   </sheetData>
@@ -18569,7 +18554,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="998" t="s">
-        <v>2780</v>
+        <v>2775</v>
       </c>
       <c r="B1" s="998"/>
       <c r="C1" s="998"/>
@@ -18582,35 +18567,35 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2781</v>
+        <v>2776</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>2782</v>
+        <v>2777</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>2783</v>
+        <v>2778</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>2784</v>
+        <v>2779</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>2785</v>
+        <v>2780</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2786</v>
+        <v>2781</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>2785</v>
+        <v>2780</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2786</v>
+        <v>2781</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="1"/>
@@ -18620,13 +18605,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="999" t="s">
-        <v>2787</v>
+        <v>2782</v>
       </c>
       <c r="B4" s="999"/>
       <c r="C4" s="33"/>
       <c r="D4" s="1000"/>
       <c r="E4" s="1001" t="s">
-        <v>2788</v>
+        <v>2783</v>
       </c>
       <c r="F4" s="916"/>
       <c r="G4" s="916"/>
@@ -18635,15 +18620,15 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1002" t="s">
-        <v>2789</v>
+        <v>2784</v>
       </c>
       <c r="B5" s="1000" t="s">
-        <v>2790</v>
+        <v>2785</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="24"/>
       <c r="E5" s="1003" t="s">
-        <v>2791</v>
+        <v>2786</v>
       </c>
       <c r="F5" s="919"/>
       <c r="G5" s="919"/>
@@ -18652,10 +18637,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1004" t="s">
-        <v>2792</v>
+        <v>2787</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>2793</v>
+        <v>2788</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="24"/>
@@ -18667,10 +18652,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1004" t="s">
-        <v>2794</v>
+        <v>2789</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>2795</v>
+        <v>2790</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="24"/>
@@ -18682,10 +18667,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1004" t="s">
-        <v>2796</v>
+        <v>2791</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>2797</v>
+        <v>2792</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="24"/>
@@ -18698,10 +18683,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1004" t="s">
-        <v>2798</v>
+        <v>2793</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>2799</v>
+        <v>2794</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="24"/>
@@ -18713,10 +18698,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1004" t="s">
-        <v>2800</v>
+        <v>2795</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>2801</v>
+        <v>2796</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="24"/>
@@ -18728,10 +18713,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1004" t="s">
-        <v>2802</v>
+        <v>2797</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>2803</v>
+        <v>2798</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="24"/>
@@ -18744,10 +18729,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1004" t="s">
-        <v>2804</v>
+        <v>2799</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>2805</v>
+        <v>2800</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="24"/>
@@ -18759,10 +18744,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1004" t="s">
-        <v>2806</v>
+        <v>2801</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>2807</v>
+        <v>2802</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="24"/>
@@ -18774,10 +18759,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1004" t="s">
-        <v>2808</v>
+        <v>2803</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>2809</v>
+        <v>2804</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="24"/>
@@ -18789,10 +18774,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1004" t="s">
-        <v>2810</v>
+        <v>2805</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>2811</v>
+        <v>2806</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="24"/>
@@ -18804,10 +18789,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1004" t="s">
-        <v>2812</v>
+        <v>2807</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>2813</v>
+        <v>2808</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="24"/>
@@ -18819,7 +18804,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="999" t="s">
-        <v>2814</v>
+        <v>2809</v>
       </c>
       <c r="B17" s="999"/>
       <c r="C17" s="20"/>
@@ -18832,10 +18817,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1004" t="s">
-        <v>2815</v>
+        <v>2810</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>2816</v>
+        <v>2811</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="24"/>
@@ -18847,10 +18832,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1004" t="s">
-        <v>2817</v>
+        <v>2812</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>2818</v>
+        <v>2813</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="24"/>
@@ -18862,10 +18847,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1004" t="s">
-        <v>2819</v>
+        <v>2814</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>2820</v>
+        <v>2815</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="24"/>
@@ -18877,10 +18862,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1004" t="s">
-        <v>2821</v>
+        <v>2816</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>2822</v>
+        <v>2817</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="24"/>
@@ -18892,10 +18877,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1004" t="s">
-        <v>2823</v>
+        <v>2818</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>2824</v>
+        <v>2819</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="24"/>
@@ -18907,10 +18892,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1004" t="s">
-        <v>2825</v>
+        <v>2820</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>2826</v>
+        <v>2821</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="24"/>
@@ -18922,10 +18907,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1004" t="s">
-        <v>2827</v>
+        <v>2822</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>2828</v>
+        <v>2823</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="24"/>
@@ -18948,7 +18933,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="999" t="s">
-        <v>2829</v>
+        <v>2824</v>
       </c>
       <c r="B26" s="999"/>
       <c r="C26" s="20"/>
@@ -18961,7 +18946,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1004" t="s">
-        <v>2830</v>
+        <v>2825</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>1294</v>
@@ -18976,10 +18961,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1004" t="s">
-        <v>2831</v>
+        <v>2826</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>2832</v>
+        <v>2827</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="24"/>
@@ -18991,10 +18976,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1004" t="s">
-        <v>2833</v>
+        <v>2828</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>2834</v>
+        <v>2829</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="24"/>
@@ -19006,10 +18991,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1004" t="s">
-        <v>2835</v>
+        <v>2830</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>2836</v>
+        <v>2831</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="24"/>
@@ -19021,10 +19006,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1004" t="s">
-        <v>2837</v>
+        <v>2832</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>2838</v>
+        <v>2833</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="24"/>
@@ -19036,10 +19021,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1004" t="s">
-        <v>2839</v>
+        <v>2834</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>2840</v>
+        <v>2835</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="24"/>
@@ -19051,10 +19036,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1004" t="s">
-        <v>2841</v>
+        <v>2836</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>2842</v>
+        <v>2837</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="24"/>
@@ -19066,10 +19051,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1004" t="s">
-        <v>2843</v>
+        <v>2838</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>2844</v>
+        <v>2839</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="24"/>
@@ -19081,10 +19066,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1004" t="s">
-        <v>2845</v>
+        <v>2840</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>2846</v>
+        <v>2841</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="24"/>
@@ -19096,10 +19081,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1004" t="s">
-        <v>2847</v>
+        <v>2842</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>2848</v>
+        <v>2843</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="24"/>
@@ -19111,10 +19096,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1004" t="s">
-        <v>2849</v>
+        <v>2844</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>2850</v>
+        <v>2845</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="24"/>
@@ -19126,10 +19111,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1004" t="s">
-        <v>2851</v>
+        <v>2846</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>2852</v>
+        <v>2847</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="24"/>
@@ -19141,10 +19126,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1004" t="s">
-        <v>2853</v>
+        <v>2848</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>2854</v>
+        <v>2849</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="24"/>
@@ -19156,10 +19141,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1004" t="s">
-        <v>2855</v>
+        <v>2850</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>2856</v>
+        <v>2851</v>
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="24"/>
@@ -19171,10 +19156,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1004" t="s">
-        <v>2857</v>
+        <v>2852</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>2858</v>
+        <v>2853</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="24"/>
@@ -19186,10 +19171,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1004" t="s">
-        <v>2859</v>
+        <v>2854</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>2860</v>
+        <v>2855</v>
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="24"/>
@@ -19201,10 +19186,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1004" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="24"/>
@@ -19216,7 +19201,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="999" t="s">
-        <v>2863</v>
+        <v>2858</v>
       </c>
       <c r="B44" s="999"/>
       <c r="C44" s="20"/>
@@ -19229,10 +19214,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1004" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="24"/>
@@ -19244,10 +19229,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1004" t="s">
-        <v>2866</v>
+        <v>2861</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>2867</v>
+        <v>2862</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="24"/>
@@ -19259,10 +19244,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1004" t="s">
-        <v>2868</v>
+        <v>2863</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>2869</v>
+        <v>2864</v>
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="24"/>
@@ -19274,7 +19259,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1004" t="s">
-        <v>2870</v>
+        <v>2865</v>
       </c>
       <c r="B48" s="24"/>
       <c r="C48" s="20"/>
@@ -19287,7 +19272,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1004" t="s">
-        <v>2871</v>
+        <v>2866</v>
       </c>
       <c r="B49" s="24"/>
       <c r="C49" s="20"/>
@@ -19300,7 +19285,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1004" t="s">
-        <v>2872</v>
+        <v>2867</v>
       </c>
       <c r="B50" s="24"/>
       <c r="C50" s="20"/>
@@ -19324,7 +19309,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="999" t="s">
-        <v>2873</v>
+        <v>2868</v>
       </c>
       <c r="B52" s="999"/>
       <c r="C52" s="20"/>
@@ -19337,10 +19322,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1004" t="s">
-        <v>2874</v>
+        <v>2869</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>2875</v>
+        <v>2870</v>
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="24"/>
@@ -19352,10 +19337,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1004" t="s">
-        <v>2876</v>
+        <v>2871</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>2877</v>
+        <v>2872</v>
       </c>
       <c r="C54" s="20"/>
       <c r="D54" s="24"/>
@@ -19462,7 +19447,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="999" t="s">
-        <v>2878</v>
+        <v>2873</v>
       </c>
       <c r="B64" s="999"/>
       <c r="F64" s="997"/>
@@ -19472,10 +19457,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1004" t="s">
-        <v>2879</v>
+        <v>2874</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>2880</v>
+        <v>2875</v>
       </c>
       <c r="F65" s="997"/>
       <c r="G65" s="997"/>
@@ -19583,7 +19568,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K82" s="1012" t="s">
-        <v>2881</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19680,22 +19665,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="6" t="s">
-        <v>2882</v>
+        <v>2877</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2883</v>
+        <v>2878</v>
       </c>
       <c r="D1" s="909" t="s">
-        <v>2884</v>
+        <v>2879</v>
       </c>
       <c r="E1" s="905" t="s">
-        <v>2884</v>
+        <v>2879</v>
       </c>
       <c r="F1" s="305" t="s">
-        <v>2884</v>
+        <v>2879</v>
       </c>
       <c r="G1" s="305" t="s">
-        <v>2884</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19703,16 +19688,16 @@
         <v>44</v>
       </c>
       <c r="C2" s="593" t="s">
-        <v>2885</v>
+        <v>2880</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>2886</v>
+        <v>2881</v>
       </c>
       <c r="E2" s="590" t="s">
-        <v>2887</v>
+        <v>2882</v>
       </c>
       <c r="F2" s="1000" t="s">
-        <v>2888</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19720,31 +19705,31 @@
         <v>78</v>
       </c>
       <c r="C3" s="576" t="s">
+        <v>2884</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>2885</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>2886</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>2887</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>2888</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>2889</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="M3" s="2" t="s">
         <v>2890</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="N3" s="2" t="s">
         <v>2891</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="O3" s="2" t="s">
         <v>2892</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>2893</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>2894</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>2895</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>2896</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>2897</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19752,28 +19737,28 @@
         <v>468</v>
       </c>
       <c r="C4" s="576" t="s">
+        <v>2893</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>2894</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>2895</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>2896</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>2897</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>2897</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>2897</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>2898</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>2899</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>2900</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>2901</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>2902</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>2902</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>2902</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>2903</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19781,28 +19766,28 @@
         <v>418</v>
       </c>
       <c r="C5" s="576" t="s">
+        <v>2899</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>2900</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>2901</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>2902</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>2903</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>2904</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="N5" s="2" t="s">
         <v>2905</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="O5" s="2" t="s">
         <v>2906</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>2907</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>2908</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>2909</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>2910</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>2911</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19810,28 +19795,28 @@
         <v>406</v>
       </c>
       <c r="C6" s="576" t="s">
+        <v>2907</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>2908</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>2909</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>2910</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>2911</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>2912</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="N6" s="2" t="s">
         <v>2913</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="O6" s="2" t="s">
         <v>2914</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>2915</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>2916</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>2917</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>2918</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>2919</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19839,19 +19824,19 @@
         <v>440</v>
       </c>
       <c r="C7" s="576" t="s">
-        <v>2920</v>
+        <v>2915</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>2921</v>
+        <v>2916</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>2922</v>
+        <v>2917</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>2923</v>
+        <v>2918</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>2924</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19859,16 +19844,16 @@
         <v>441</v>
       </c>
       <c r="C8" s="576" t="s">
-        <v>2925</v>
+        <v>2920</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>2926</v>
+        <v>2921</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>2927</v>
+        <v>2922</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>2928</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19876,16 +19861,16 @@
         <v>612</v>
       </c>
       <c r="C9" s="576" t="s">
-        <v>2929</v>
+        <v>2924</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>2930</v>
+        <v>2925</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>2930</v>
+        <v>2925</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>2930</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19893,16 +19878,16 @@
         <v>514</v>
       </c>
       <c r="C10" s="576" t="s">
-        <v>2931</v>
+        <v>2926</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>2932</v>
+        <v>2927</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>2933</v>
+        <v>2928</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>2934</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19910,16 +19895,16 @@
         <v>487</v>
       </c>
       <c r="C11" s="576" t="s">
-        <v>2935</v>
+        <v>2930</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>2915</v>
+        <v>2910</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>2936</v>
+        <v>2931</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>2937</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19927,16 +19912,16 @@
         <v>411</v>
       </c>
       <c r="C12" s="576" t="s">
-        <v>2938</v>
+        <v>2933</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>2939</v>
+        <v>2934</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>2940</v>
+        <v>2935</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>2941</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19944,7 +19929,7 @@
         <v>141</v>
       </c>
       <c r="C13" s="576" t="s">
-        <v>2942</v>
+        <v>2937</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="23"/>
@@ -19955,16 +19940,16 @@
         <v>535</v>
       </c>
       <c r="C14" s="576" t="s">
-        <v>2943</v>
+        <v>2938</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>2944</v>
+        <v>2939</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>2945</v>
+        <v>2940</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>2946</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19972,16 +19957,16 @@
         <v>158</v>
       </c>
       <c r="C15" s="576" t="s">
-        <v>2885</v>
+        <v>2880</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>2947</v>
+        <v>2942</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>2946</v>
+        <v>2941</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>2948</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19989,16 +19974,16 @@
         <v>570</v>
       </c>
       <c r="C16" s="576" t="s">
-        <v>2949</v>
+        <v>2944</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>2950</v>
+        <v>2945</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>2951</v>
+        <v>2946</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>2952</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20006,16 +19991,16 @@
         <v>464</v>
       </c>
       <c r="C17" s="576" t="s">
-        <v>2953</v>
+        <v>2948</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>2954</v>
+        <v>2949</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>2955</v>
+        <v>2950</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>2956</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20023,19 +20008,19 @@
         <v>454</v>
       </c>
       <c r="C18" s="576" t="s">
-        <v>2957</v>
+        <v>2952</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>2958</v>
+        <v>2953</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>2959</v>
+        <v>2954</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>2960</v>
+        <v>2955</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>2961</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20043,16 +20028,16 @@
         <v>100</v>
       </c>
       <c r="C19" s="583" t="s">
-        <v>2962</v>
+        <v>2957</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>2963</v>
+        <v>2958</v>
       </c>
       <c r="E19" s="149" t="s">
-        <v>2964</v>
+        <v>2959</v>
       </c>
       <c r="F19" s="174" t="s">
-        <v>2965</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -20080,7 +20065,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1036" t="s">
-        <v>2966</v>
+        <v>2961</v>
       </c>
       <c r="B1" s="1036"/>
       <c r="C1" s="1036"/>
@@ -20093,73 +20078,73 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2963</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2965</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>2966</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>2967</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2968</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2969</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2970</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>2971</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>2972</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>2973</v>
+        <v>2968</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2974</v>
+        <v>2969</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2975</v>
+        <v>2970</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>2976</v>
+        <v>2971</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>2977</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>2978</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>2979</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>2980</v>
+        <v>2975</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>2981</v>
+        <v>2976</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>2980</v>
+        <v>2975</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>2982</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>2983</v>
+        <v>2978</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>2984</v>
+        <v>2979</v>
       </c>
       <c r="Q15" s="365" t="s">
         <v>418</v>
@@ -20167,10 +20152,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>2983</v>
+        <v>2978</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>2985</v>
+        <v>2980</v>
       </c>
       <c r="Q16" s="663" t="s">
         <v>441</v>
@@ -20178,10 +20163,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>2986</v>
+        <v>2981</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>2987</v>
+        <v>2982</v>
       </c>
       <c r="Q17" s="342" t="s">
         <v>514</v>
@@ -20189,7 +20174,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>2988</v>
+        <v>2983</v>
       </c>
       <c r="Q18" s="467" t="s">
         <v>487</v>
@@ -50044,7 +50029,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q270"/>
+  <dimension ref="A1:Q269"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="888" width="4.14"/>
@@ -55432,9 +55417,7 @@
       <c r="I196" s="199"/>
       <c r="J196" s="200"/>
       <c r="K196" s="201"/>
-      <c r="L196" s="224" t="s">
-        <v>2725</v>
-      </c>
+      <c r="L196" s="224"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B197" s="194"/>
@@ -55460,9 +55443,7 @@
       <c r="I198" s="199"/>
       <c r="J198" s="200"/>
       <c r="K198" s="201"/>
-      <c r="L198" s="224" t="s">
-        <v>2726</v>
-      </c>
+      <c r="L198" s="224"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B199" s="194"/>
@@ -55618,9 +55599,7 @@
       <c r="I210" s="199"/>
       <c r="J210" s="200"/>
       <c r="K210" s="201"/>
-      <c r="L210" s="224" t="s">
-        <v>2727</v>
-      </c>
+      <c r="L210" s="224"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B211" s="194"/>
@@ -55633,9 +55612,7 @@
       <c r="I211" s="199"/>
       <c r="J211" s="200"/>
       <c r="K211" s="201"/>
-      <c r="L211" s="224" t="s">
-        <v>2728</v>
-      </c>
+      <c r="L211" s="224"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B212" s="194"/>
@@ -55648,9 +55625,7 @@
       <c r="I212" s="199"/>
       <c r="J212" s="200"/>
       <c r="K212" s="201"/>
-      <c r="L212" s="224" t="s">
-        <v>2728</v>
-      </c>
+      <c r="L212" s="224"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B213" s="194"/>
@@ -55689,9 +55664,7 @@
       <c r="I215" s="199"/>
       <c r="J215" s="200"/>
       <c r="K215" s="201"/>
-      <c r="L215" s="224" t="s">
-        <v>2729</v>
-      </c>
+      <c r="L215" s="224"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B216" s="194"/>
@@ -56395,7 +56368,6 @@
       <c r="K269" s="210"/>
       <c r="L269" s="211"/>
     </row>
-    <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
@@ -56434,32 +56406,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>2730</v>
+        <v>2725</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>2731</v>
+        <v>2726</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1" t="s">
-        <v>2732</v>
+        <v>2727</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>2733</v>
+        <v>2728</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
-        <v>2734</v>
+        <v>2729</v>
       </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -56467,61 +56439,61 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="904" t="s">
-        <v>2736</v>
+        <v>2731</v>
       </c>
       <c r="B2" s="905" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="C2" s="906" t="s">
-        <v>2736</v>
+        <v>2731</v>
       </c>
       <c r="D2" s="905" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="E2" s="907" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="F2" s="908" t="s">
-        <v>2736</v>
+        <v>2731</v>
       </c>
       <c r="G2" s="905" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="H2" s="305" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="I2" s="909" t="s">
-        <v>2736</v>
+        <v>2731</v>
       </c>
       <c r="J2" s="905" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="K2" s="907" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="L2" s="904" t="s">
-        <v>2736</v>
+        <v>2731</v>
       </c>
       <c r="M2" s="905" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="N2" s="907" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>2738</v>
+        <v>2733</v>
       </c>
       <c r="P2" s="904" t="s">
-        <v>2736</v>
+        <v>2731</v>
       </c>
       <c r="Q2" s="905" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="R2" s="907" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>2738</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56709,13 +56681,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="926" t="s">
-        <v>2739</v>
+        <v>2734</v>
       </c>
       <c r="B6" s="919" t="n">
         <v>12</v>
       </c>
       <c r="C6" s="927" t="s">
-        <v>2739</v>
+        <v>2734</v>
       </c>
       <c r="D6" s="919" t="n">
         <v>7</v>
@@ -57870,14 +57842,14 @@
     </row>
     <row r="26" s="312" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="68" t="s">
-        <v>2738</v>
+        <v>2733</v>
       </c>
       <c r="B26" s="705" t="n">
         <f aca="false">SUM(B3:B25)</f>
         <v>151</v>
       </c>
       <c r="C26" s="68" t="s">
-        <v>2738</v>
+        <v>2733</v>
       </c>
       <c r="D26" s="991" t="n">
         <f aca="false">SUM(D3:D25)</f>
@@ -57888,7 +57860,7 @@
         <v>64</v>
       </c>
       <c r="F26" s="68" t="s">
-        <v>2738</v>
+        <v>2733</v>
       </c>
       <c r="G26" s="991" t="n">
         <f aca="false">SUM(G3:G25)</f>
@@ -57899,7 +57871,7 @@
         <v>138</v>
       </c>
       <c r="I26" s="68" t="s">
-        <v>2738</v>
+        <v>2733</v>
       </c>
       <c r="J26" s="991" t="n">
         <f aca="false">SUM(J3:J25)</f>
@@ -57910,7 +57882,7 @@
         <v>64</v>
       </c>
       <c r="L26" s="68" t="s">
-        <v>2738</v>
+        <v>2733</v>
       </c>
       <c r="M26" s="993" t="n">
         <f aca="false">SUM(M3:M25)</f>
@@ -57925,7 +57897,7 @@
         <v>334</v>
       </c>
       <c r="P26" s="68" t="s">
-        <v>2738</v>
+        <v>2733</v>
       </c>
       <c r="Q26" s="993" t="n">
         <f aca="false">SUM(Q3:Q25)</f>

--- a/Fakemon Region.xlsx
+++ b/Fakemon Region.xlsx
@@ -16,11 +16,9 @@
     <sheet name="Bokmal" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="MiniDex" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Unknown" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Tipos" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="habilidades Criadas" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Idéias" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Pokejeto" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="TRIBAL" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="habilidades Criadas" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Idéias" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="TRIBAL" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Brasca!$A$2:$K$253</definedName>
@@ -28,7 +26,6 @@
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Dunnottar!$A$2:$O$102</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Lekker!$A$2:$P$203</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Rebueno!$A$2:$P$103</definedName>
-    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">Tipos!$A$2:$S$2</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -39,7 +36,7 @@
 </workbook>
 </file>
 
-<file path=xl/comments13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Fabio Meireles</author>
@@ -122,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7723" uniqueCount="2984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7763" uniqueCount="2992">
   <si>
     <t xml:space="preserve">FAKEMON - DOGON REGION</t>
   </si>
@@ -7486,9 +7483,27 @@
     <t xml:space="preserve">Morcego (Thyroptera tricolor)</t>
   </si>
   <si>
+    <t xml:space="preserve">Calenmaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maya Calendar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Calendário Maia</t>
   </si>
   <si>
+    <t xml:space="preserve">Coystat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green Coyote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arena Trap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coiote (Canis latrans)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aleguin</t>
   </si>
   <si>
@@ -7501,7 +7516,16 @@
     <t xml:space="preserve">Pinguim-Gentoo (Pygoscelis papua)</t>
   </si>
   <si>
-    <t xml:space="preserve">Camazotz</t>
+    <t xml:space="preserve">Batmazotz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend Bat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camazotz (Lenda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escultura Batman (DC Comics)</t>
   </si>
   <si>
     <t xml:space="preserve">Lahomuerte</t>
@@ -7513,15 +7537,18 @@
     <t xml:space="preserve">Cemitery</t>
   </si>
   <si>
-    <t xml:space="preserve">Santa Muerte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chiuaua</t>
+    <t xml:space="preserve">Santa Muerte (Divindade)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinairy</t>
   </si>
   <si>
     <t xml:space="preserve">Pinata</t>
   </si>
   <si>
+    <t xml:space="preserve">Pinhata</t>
+  </si>
+  <si>
     <t xml:space="preserve">Xoloitzaw</t>
   </si>
   <si>
@@ -7534,6 +7561,15 @@
     <t xml:space="preserve">Cachorro-Xoloitzcuintle (Canis familiaris)</t>
   </si>
   <si>
+    <t xml:space="preserve">Pamnrertos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poison Bread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pan de muertos (Pão Doce)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zebaurus</t>
   </si>
   <si>
@@ -7552,6 +7588,9 @@
     <t xml:space="preserve">Alebrije</t>
   </si>
   <si>
+    <t xml:space="preserve">Alebrije (Lenda)</t>
+  </si>
+  <si>
     <t xml:space="preserve">FAKEMON - UNKNOWN DEX</t>
   </si>
   <si>
@@ -7876,9 +7915,6 @@
     <t xml:space="preserve">Little Ghost</t>
   </si>
   <si>
-    <t xml:space="preserve">Arena Trap</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cemetery's</t>
   </si>
   <si>
@@ -8383,34 +8419,271 @@
     <t xml:space="preserve">Galáxias</t>
   </si>
   <si>
-    <t xml:space="preserve">Kanto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOGON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRASCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUNNOTTAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEKKER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REBUENO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elemento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fire</t>
+    <t xml:space="preserve">Turufus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire vocal bird</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sabiá-Laranjeira (Turdus rufiventris) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cambuci (Campomanesia phaea)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inkger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spotted Tiger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tigre (Panthera tigris) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cetragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cetus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cetus (Constelação)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masktopus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mask Octopus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polvo-de-anéis-azuis (Hapalochlaena maculosa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aracnoline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feline Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gato (Felis catus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aranha (Araneae)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calfdae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grumpy calf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bovinos (Bovidae)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evo Caldae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oribalu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obalu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obalu (Orixá)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragonyx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Little Dinosaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therapoda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barygon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinosaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hermitenemon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hermit Crab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caranguejo-Eremita (Paguroidea) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collectant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collector Ant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formigas (Formicidae)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octooze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ooze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polvo (Octopoda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necrosarco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark Devil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vital Spirit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demônio-da-Tasmânia (Sarcophilus harrisii)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drajawgron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Bug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragão (Mitologia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slugerark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electric Slug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lesma-Marinha (Cyerce nigra)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fayralien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alienigena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wortiticve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radioactive Worm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radioactive places</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minhoca Indiana (Pheretima posthuma)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commwordictive </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communal Radioactive Worm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toothiger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sabretooth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Techinician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tigre dentes de sabre (Smilodon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poistatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electric Poison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astato (At)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winesider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wine Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcoholic web</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viticultor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baditchark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malicious witch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruxa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stegosectric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electric Dinosaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estegossauro (Stegosaurus stenops)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crablugly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ugly Crab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caranguejo (Brachyura)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quindim (comida)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beetronger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giant Beetle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besouro Serra-Pau (Psygmatocerus wagleri)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinocchevil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cursed Doll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head Rip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinóquio ()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strantire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Ant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formiga de Fogo (Solenopsis invicta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crucafor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pincer Crustacean</t>
   </si>
   <si>
     <t xml:space="preserve">É uma habilidade única, sendo encontrado somente nos Tardidragon, faz o pokemon ter imunidade a burn, paralyze, poisoned e sleep. ainda o pokemon não é afetado a situações climáticas e tem os ataques do tipo inseto com poder dobrado.</t>
@@ -8837,258 +9110,6 @@
   </si>
   <si>
     <t xml:space="preserve">O Parcel é conhecido como “Triângulo das Bermudas Brasileiro” justamente por ser o segundo ponto de maior concentração de navios naufragados do mundo, atrás apenas da própria região das Bermudas. Isso acontece porque no Parcel fica o maior conjunto de corais da América do Sul, um dos maiores do mundo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAINER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POKE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walisson Luan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carracosta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primarina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kingdra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamele Jesus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chatot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ditto (marsht)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drampa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FBO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GABS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANDY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G VICTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raul Brener</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drapion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scolipede</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skuntank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insivibilidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabio Meireles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volcarona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapidash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comunicação animais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superforça</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pyrosinesia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Super Velocidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gil Alves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roserade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torterra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elemental AR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teletransporte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmutação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leonardo Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Araquanid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heracross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crustle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">teu recor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thiago Torres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luxray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heliolisk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emolga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Ookami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lycanroc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adriano Nascimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elgyem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mewtwo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriel Pacheco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gliscor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golurk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedro Leonardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chesnaught</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blaziken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hawlucha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priscilla Dastre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anderson Pedrosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dusclops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marowak (A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mimikyu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florges (az)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grambull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedro Leopoldo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glaceon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weavile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mamoswine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Martins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staraptor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beautifly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adriano C./Karina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empoleon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scizor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steelix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magearna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diego Guilherme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umbreon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharpedo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sableye</t>
   </si>
   <si>
     <t xml:space="preserve">TIPO TRIBAL</t>
@@ -9386,11 +9407,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial Unicode MS"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -10215,7 +10235,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1038">
+  <cellXfs count="932">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -13816,11 +13836,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="58" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="69" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -13832,406 +13852,50 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="70" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="47" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="45" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="54" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="33" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="66" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="80" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="37" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="35" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="58" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="55" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="15" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="55" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="14" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="14" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="14" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="19" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="19" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="19" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="16" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="16" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="16" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="13" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="13" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="13" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="55" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="17" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="17" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="17" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="18" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="18" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="18" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="55" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="48" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="68" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="15" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="15" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="48" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="68" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="74" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="61" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="67" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="70" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="70" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="47" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="37" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -14289,74 +13953,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="19" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="16" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="13" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="17" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="18" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14670,10 +14266,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tema do Office">
   <a:themeElements>
@@ -18285,259 +17877,6 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="11.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="33.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="181.29"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C2" s="660" t="s">
-        <v>2735</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C3" s="995" t="s">
-        <v>2736</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C4" s="995" t="s">
-        <v>2737</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="C5" s="995" t="s">
-        <v>2738</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="C6" s="995" t="s">
-        <v>2739</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
-        <v>2740</v>
-      </c>
-      <c r="C7" s="660" t="s">
-        <v>2741</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
-        <v>1442</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>2742</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="s">
-        <v>1416</v>
-      </c>
-      <c r="C9" s="995" t="s">
-        <v>2743</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
-        <v>2744</v>
-      </c>
-      <c r="C10" s="995" t="s">
-        <v>2745</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="660" t="s">
-        <v>2746</v>
-      </c>
-      <c r="C11" s="995" t="s">
-        <v>2747</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2" t="s">
-        <v>2748</v>
-      </c>
-      <c r="C12" s="996" t="s">
-        <v>2749</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="s">
-        <v>2750</v>
-      </c>
-      <c r="C13" s="995" t="s">
-        <v>2751</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="2" t="s">
-        <v>1433</v>
-      </c>
-      <c r="C14" s="995" t="s">
-        <v>2752</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="2" t="s">
-        <v>2753</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>2754</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
-        <v>1566</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>2755</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="2" t="s">
-        <v>1796</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>2756</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2" t="s">
-        <v>1992</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>2757</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="2" t="s">
-        <v>1989</v>
-      </c>
-      <c r="C19" s="660" t="s">
-        <v>2758</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="2" t="s">
-        <v>1809</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>2759</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="2" t="s">
-        <v>1995</v>
-      </c>
-      <c r="C21" s="660" t="s">
-        <v>2760</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="2" t="s">
-        <v>2761</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>2762</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="2" t="s">
-        <v>2763</v>
-      </c>
-      <c r="C23" s="660" t="s">
-        <v>2764</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="2" t="s">
-        <v>2160</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>2765</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="2" t="s">
-        <v>2766</v>
-      </c>
-      <c r="C25" s="660" t="s">
-        <v>2767</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="2" t="s">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="2" t="s">
-        <v>2246</v>
-      </c>
-      <c r="C27" s="660" t="s">
-        <v>2768</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="2" t="s">
-        <v>2769</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>2770</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="2" t="s">
-        <v>2771</v>
-      </c>
-      <c r="C29" s="660" t="s">
-        <v>2772</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="2" t="s">
-        <v>2773</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>2774</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
   <dimension ref="A1:L104"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -18545,7 +17884,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="578" width="38.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="163" width="30.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="578" width="30.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="997" width="21.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="906" width="21.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="163" width="19.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="163" width="16.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="163" width="15.29"/>
@@ -18553,49 +17892,49 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="998" t="s">
-        <v>2775</v>
-      </c>
-      <c r="B1" s="998"/>
-      <c r="C1" s="998"/>
-      <c r="D1" s="998"/>
-      <c r="E1" s="998"/>
-      <c r="F1" s="998"/>
-      <c r="G1" s="998"/>
-      <c r="H1" s="998"/>
-      <c r="I1" s="998"/>
+      <c r="A1" s="907" t="s">
+        <v>2867</v>
+      </c>
+      <c r="B1" s="907"/>
+      <c r="C1" s="907"/>
+      <c r="D1" s="907"/>
+      <c r="E1" s="907"/>
+      <c r="F1" s="907"/>
+      <c r="G1" s="907"/>
+      <c r="H1" s="907"/>
+      <c r="I1" s="907"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2776</v>
+        <v>2868</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>2777</v>
+        <v>2869</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>2778</v>
+        <v>2870</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>2779</v>
+        <v>2871</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>2780</v>
+        <v>2872</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2781</v>
+        <v>2873</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>2780</v>
+        <v>2872</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2781</v>
+        <v>2873</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="1"/>
@@ -18604,794 +17943,794 @@
       <c r="I3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="999" t="s">
-        <v>2782</v>
-      </c>
-      <c r="B4" s="999"/>
+      <c r="A4" s="908" t="s">
+        <v>2874</v>
+      </c>
+      <c r="B4" s="908"/>
       <c r="C4" s="33"/>
-      <c r="D4" s="1000"/>
-      <c r="E4" s="1001" t="s">
-        <v>2783</v>
-      </c>
-      <c r="F4" s="916"/>
-      <c r="G4" s="916"/>
-      <c r="H4" s="916"/>
+      <c r="D4" s="909"/>
+      <c r="E4" s="910" t="s">
+        <v>2875</v>
+      </c>
+      <c r="F4" s="911"/>
+      <c r="G4" s="911"/>
+      <c r="H4" s="911"/>
       <c r="I4" s="88"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1002" t="s">
-        <v>2784</v>
-      </c>
-      <c r="B5" s="1000" t="s">
-        <v>2785</v>
+      <c r="A5" s="912" t="s">
+        <v>2876</v>
+      </c>
+      <c r="B5" s="909" t="s">
+        <v>2877</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="24"/>
-      <c r="E5" s="1003" t="s">
-        <v>2786</v>
-      </c>
-      <c r="F5" s="919"/>
-      <c r="G5" s="919"/>
-      <c r="H5" s="919"/>
+      <c r="E5" s="913" t="s">
+        <v>2878</v>
+      </c>
+      <c r="F5" s="914"/>
+      <c r="G5" s="914"/>
+      <c r="H5" s="914"/>
       <c r="I5" s="22"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1004" t="s">
-        <v>2787</v>
+      <c r="A6" s="915" t="s">
+        <v>2879</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>2788</v>
+        <v>2880</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="24"/>
-      <c r="E6" s="1003"/>
-      <c r="F6" s="919"/>
-      <c r="G6" s="919"/>
-      <c r="H6" s="919"/>
+      <c r="E6" s="913"/>
+      <c r="F6" s="914"/>
+      <c r="G6" s="914"/>
+      <c r="H6" s="914"/>
       <c r="I6" s="22"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1004" t="s">
-        <v>2789</v>
+      <c r="A7" s="915" t="s">
+        <v>2881</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>2790</v>
+        <v>2882</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="24"/>
-      <c r="E7" s="1003"/>
-      <c r="F7" s="919"/>
-      <c r="G7" s="919"/>
-      <c r="H7" s="919"/>
+      <c r="E7" s="913"/>
+      <c r="F7" s="914"/>
+      <c r="G7" s="914"/>
+      <c r="H7" s="914"/>
       <c r="I7" s="22"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1004" t="s">
-        <v>2791</v>
+      <c r="A8" s="915" t="s">
+        <v>2883</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>2792</v>
+        <v>2884</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="24"/>
-      <c r="E8" s="1003"/>
-      <c r="F8" s="919"/>
-      <c r="G8" s="919"/>
-      <c r="H8" s="919"/>
+      <c r="E8" s="913"/>
+      <c r="F8" s="914"/>
+      <c r="G8" s="914"/>
+      <c r="H8" s="914"/>
       <c r="I8" s="22"/>
       <c r="J8" s="138"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1004" t="s">
-        <v>2793</v>
+      <c r="A9" s="915" t="s">
+        <v>2885</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>2794</v>
+        <v>2886</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="24"/>
-      <c r="E9" s="1003"/>
-      <c r="F9" s="919"/>
-      <c r="G9" s="919"/>
-      <c r="H9" s="919"/>
+      <c r="E9" s="913"/>
+      <c r="F9" s="914"/>
+      <c r="G9" s="914"/>
+      <c r="H9" s="914"/>
       <c r="I9" s="22"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1004" t="s">
-        <v>2795</v>
+      <c r="A10" s="915" t="s">
+        <v>2887</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>2796</v>
+        <v>2888</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="24"/>
-      <c r="E10" s="1003"/>
-      <c r="F10" s="919"/>
-      <c r="G10" s="919"/>
-      <c r="H10" s="919"/>
+      <c r="E10" s="913"/>
+      <c r="F10" s="914"/>
+      <c r="G10" s="914"/>
+      <c r="H10" s="914"/>
       <c r="I10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1004" t="s">
-        <v>2797</v>
+      <c r="A11" s="915" t="s">
+        <v>2889</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>2798</v>
+        <v>2890</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="24"/>
-      <c r="E11" s="1003"/>
-      <c r="F11" s="919"/>
-      <c r="G11" s="919"/>
-      <c r="H11" s="919"/>
+      <c r="E11" s="913"/>
+      <c r="F11" s="914"/>
+      <c r="G11" s="914"/>
+      <c r="H11" s="914"/>
       <c r="I11" s="22"/>
       <c r="J11" s="138"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1004" t="s">
-        <v>2799</v>
+      <c r="A12" s="915" t="s">
+        <v>2891</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>2800</v>
+        <v>2892</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="24"/>
-      <c r="E12" s="1003"/>
-      <c r="F12" s="919"/>
-      <c r="G12" s="919"/>
-      <c r="H12" s="919"/>
+      <c r="E12" s="913"/>
+      <c r="F12" s="914"/>
+      <c r="G12" s="914"/>
+      <c r="H12" s="914"/>
       <c r="I12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1004" t="s">
-        <v>2801</v>
+      <c r="A13" s="915" t="s">
+        <v>2893</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>2802</v>
+        <v>2894</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="24"/>
-      <c r="E13" s="1003"/>
-      <c r="F13" s="919"/>
-      <c r="G13" s="919"/>
-      <c r="H13" s="919"/>
+      <c r="E13" s="913"/>
+      <c r="F13" s="914"/>
+      <c r="G13" s="914"/>
+      <c r="H13" s="914"/>
       <c r="I13" s="22"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1004" t="s">
-        <v>2803</v>
+      <c r="A14" s="915" t="s">
+        <v>2895</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>2804</v>
+        <v>2896</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="24"/>
-      <c r="E14" s="1003"/>
-      <c r="F14" s="919"/>
-      <c r="G14" s="919"/>
-      <c r="H14" s="919"/>
+      <c r="E14" s="913"/>
+      <c r="F14" s="914"/>
+      <c r="G14" s="914"/>
+      <c r="H14" s="914"/>
       <c r="I14" s="22"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1004" t="s">
-        <v>2805</v>
+      <c r="A15" s="915" t="s">
+        <v>2897</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>2806</v>
+        <v>2898</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="24"/>
-      <c r="E15" s="1003"/>
-      <c r="F15" s="919"/>
-      <c r="G15" s="919"/>
-      <c r="H15" s="919"/>
+      <c r="E15" s="913"/>
+      <c r="F15" s="914"/>
+      <c r="G15" s="914"/>
+      <c r="H15" s="914"/>
       <c r="I15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1004" t="s">
-        <v>2807</v>
+      <c r="A16" s="915" t="s">
+        <v>2899</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>2808</v>
+        <v>2900</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="24"/>
-      <c r="E16" s="1003"/>
-      <c r="F16" s="919"/>
-      <c r="G16" s="919"/>
-      <c r="H16" s="919"/>
+      <c r="E16" s="913"/>
+      <c r="F16" s="914"/>
+      <c r="G16" s="914"/>
+      <c r="H16" s="914"/>
       <c r="I16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="999" t="s">
-        <v>2809</v>
-      </c>
-      <c r="B17" s="999"/>
+      <c r="A17" s="908" t="s">
+        <v>2901</v>
+      </c>
+      <c r="B17" s="908"/>
       <c r="C17" s="20"/>
       <c r="D17" s="24"/>
-      <c r="E17" s="1003"/>
-      <c r="F17" s="919"/>
-      <c r="G17" s="919"/>
-      <c r="H17" s="919"/>
+      <c r="E17" s="913"/>
+      <c r="F17" s="914"/>
+      <c r="G17" s="914"/>
+      <c r="H17" s="914"/>
       <c r="I17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1004" t="s">
-        <v>2810</v>
+      <c r="A18" s="915" t="s">
+        <v>2902</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>2811</v>
+        <v>2903</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="24"/>
-      <c r="E18" s="1003"/>
-      <c r="F18" s="919"/>
-      <c r="G18" s="919"/>
-      <c r="H18" s="919"/>
+      <c r="E18" s="913"/>
+      <c r="F18" s="914"/>
+      <c r="G18" s="914"/>
+      <c r="H18" s="914"/>
       <c r="I18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1004" t="s">
-        <v>2812</v>
+      <c r="A19" s="915" t="s">
+        <v>2904</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>2813</v>
+        <v>2905</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="24"/>
-      <c r="E19" s="1003"/>
-      <c r="F19" s="919"/>
-      <c r="G19" s="919"/>
-      <c r="H19" s="919"/>
+      <c r="E19" s="913"/>
+      <c r="F19" s="914"/>
+      <c r="G19" s="914"/>
+      <c r="H19" s="914"/>
       <c r="I19" s="22"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1004" t="s">
-        <v>2814</v>
+      <c r="A20" s="915" t="s">
+        <v>2906</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>2815</v>
+        <v>2907</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="24"/>
-      <c r="E20" s="1003"/>
-      <c r="F20" s="919"/>
-      <c r="G20" s="919"/>
-      <c r="H20" s="919"/>
+      <c r="E20" s="913"/>
+      <c r="F20" s="914"/>
+      <c r="G20" s="914"/>
+      <c r="H20" s="914"/>
       <c r="I20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1004" t="s">
-        <v>2816</v>
+      <c r="A21" s="915" t="s">
+        <v>2908</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>2817</v>
+        <v>2909</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="24"/>
-      <c r="E21" s="1003"/>
-      <c r="F21" s="919"/>
-      <c r="G21" s="919"/>
-      <c r="H21" s="919"/>
+      <c r="E21" s="913"/>
+      <c r="F21" s="914"/>
+      <c r="G21" s="914"/>
+      <c r="H21" s="914"/>
       <c r="I21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1004" t="s">
-        <v>2818</v>
+      <c r="A22" s="915" t="s">
+        <v>2910</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>2819</v>
+        <v>2911</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="24"/>
-      <c r="E22" s="1003"/>
-      <c r="F22" s="919"/>
-      <c r="G22" s="919"/>
-      <c r="H22" s="919"/>
+      <c r="E22" s="913"/>
+      <c r="F22" s="914"/>
+      <c r="G22" s="914"/>
+      <c r="H22" s="914"/>
       <c r="I22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1004" t="s">
-        <v>2820</v>
+      <c r="A23" s="915" t="s">
+        <v>2912</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>2821</v>
+        <v>2913</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="24"/>
-      <c r="E23" s="1003"/>
-      <c r="F23" s="919"/>
-      <c r="G23" s="919"/>
-      <c r="H23" s="919"/>
+      <c r="E23" s="913"/>
+      <c r="F23" s="914"/>
+      <c r="G23" s="914"/>
+      <c r="H23" s="914"/>
       <c r="I23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1004" t="s">
-        <v>2822</v>
+      <c r="A24" s="915" t="s">
+        <v>2914</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>2823</v>
+        <v>2915</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="24"/>
-      <c r="E24" s="1003"/>
-      <c r="F24" s="919"/>
-      <c r="G24" s="919"/>
-      <c r="H24" s="919"/>
+      <c r="E24" s="913"/>
+      <c r="F24" s="914"/>
+      <c r="G24" s="914"/>
+      <c r="H24" s="914"/>
       <c r="I24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1004"/>
+      <c r="A25" s="915"/>
       <c r="B25" s="24"/>
       <c r="C25" s="20"/>
       <c r="D25" s="24"/>
-      <c r="E25" s="1003"/>
-      <c r="F25" s="919"/>
-      <c r="G25" s="919"/>
-      <c r="H25" s="919"/>
+      <c r="E25" s="913"/>
+      <c r="F25" s="914"/>
+      <c r="G25" s="914"/>
+      <c r="H25" s="914"/>
       <c r="I25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="999" t="s">
-        <v>2824</v>
-      </c>
-      <c r="B26" s="999"/>
+      <c r="A26" s="908" t="s">
+        <v>2916</v>
+      </c>
+      <c r="B26" s="908"/>
       <c r="C26" s="20"/>
       <c r="D26" s="24"/>
-      <c r="E26" s="1003"/>
-      <c r="F26" s="919"/>
-      <c r="G26" s="919"/>
-      <c r="H26" s="919"/>
+      <c r="E26" s="913"/>
+      <c r="F26" s="914"/>
+      <c r="G26" s="914"/>
+      <c r="H26" s="914"/>
       <c r="I26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1004" t="s">
-        <v>2825</v>
+      <c r="A27" s="915" t="s">
+        <v>2917</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>1294</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="24"/>
-      <c r="E27" s="1003"/>
-      <c r="F27" s="919"/>
-      <c r="G27" s="919"/>
-      <c r="H27" s="919"/>
+      <c r="E27" s="913"/>
+      <c r="F27" s="914"/>
+      <c r="G27" s="914"/>
+      <c r="H27" s="914"/>
       <c r="I27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1004" t="s">
-        <v>2826</v>
+      <c r="A28" s="915" t="s">
+        <v>2918</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>2827</v>
+        <v>2919</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="24"/>
-      <c r="E28" s="1003"/>
-      <c r="F28" s="919"/>
-      <c r="G28" s="919"/>
-      <c r="H28" s="919"/>
+      <c r="E28" s="913"/>
+      <c r="F28" s="914"/>
+      <c r="G28" s="914"/>
+      <c r="H28" s="914"/>
       <c r="I28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1004" t="s">
-        <v>2828</v>
+      <c r="A29" s="915" t="s">
+        <v>2920</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>2829</v>
+        <v>2921</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="24"/>
-      <c r="E29" s="1003"/>
-      <c r="F29" s="919"/>
-      <c r="G29" s="919"/>
-      <c r="H29" s="919"/>
+      <c r="E29" s="913"/>
+      <c r="F29" s="914"/>
+      <c r="G29" s="914"/>
+      <c r="H29" s="914"/>
       <c r="I29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1004" t="s">
-        <v>2830</v>
+      <c r="A30" s="915" t="s">
+        <v>2922</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>2831</v>
+        <v>2923</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="24"/>
-      <c r="E30" s="1003"/>
-      <c r="F30" s="919"/>
-      <c r="G30" s="919"/>
-      <c r="H30" s="919"/>
+      <c r="E30" s="913"/>
+      <c r="F30" s="914"/>
+      <c r="G30" s="914"/>
+      <c r="H30" s="914"/>
       <c r="I30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1004" t="s">
-        <v>2832</v>
+      <c r="A31" s="915" t="s">
+        <v>2924</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>2833</v>
+        <v>2925</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="24"/>
-      <c r="E31" s="1003"/>
-      <c r="F31" s="919"/>
-      <c r="G31" s="919"/>
-      <c r="H31" s="919"/>
+      <c r="E31" s="913"/>
+      <c r="F31" s="914"/>
+      <c r="G31" s="914"/>
+      <c r="H31" s="914"/>
       <c r="I31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1004" t="s">
-        <v>2834</v>
+      <c r="A32" s="915" t="s">
+        <v>2926</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>2835</v>
+        <v>2927</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="24"/>
-      <c r="E32" s="1003"/>
-      <c r="F32" s="919"/>
-      <c r="G32" s="919"/>
-      <c r="H32" s="919"/>
+      <c r="E32" s="913"/>
+      <c r="F32" s="914"/>
+      <c r="G32" s="914"/>
+      <c r="H32" s="914"/>
       <c r="I32" s="22"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1004" t="s">
-        <v>2836</v>
+      <c r="A33" s="915" t="s">
+        <v>2928</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>2837</v>
+        <v>2929</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="24"/>
-      <c r="E33" s="1003"/>
-      <c r="F33" s="919"/>
-      <c r="G33" s="919"/>
-      <c r="H33" s="919"/>
+      <c r="E33" s="913"/>
+      <c r="F33" s="914"/>
+      <c r="G33" s="914"/>
+      <c r="H33" s="914"/>
       <c r="I33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1004" t="s">
-        <v>2838</v>
+      <c r="A34" s="915" t="s">
+        <v>2930</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>2839</v>
+        <v>2931</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="24"/>
-      <c r="E34" s="1003"/>
-      <c r="F34" s="919"/>
-      <c r="G34" s="919"/>
-      <c r="H34" s="919"/>
+      <c r="E34" s="913"/>
+      <c r="F34" s="914"/>
+      <c r="G34" s="914"/>
+      <c r="H34" s="914"/>
       <c r="I34" s="22"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1004" t="s">
-        <v>2840</v>
+      <c r="A35" s="915" t="s">
+        <v>2932</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>2841</v>
+        <v>2933</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="24"/>
-      <c r="E35" s="1003"/>
-      <c r="F35" s="919"/>
-      <c r="G35" s="919"/>
-      <c r="H35" s="919"/>
+      <c r="E35" s="913"/>
+      <c r="F35" s="914"/>
+      <c r="G35" s="914"/>
+      <c r="H35" s="914"/>
       <c r="I35" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1004" t="s">
-        <v>2842</v>
+      <c r="A36" s="915" t="s">
+        <v>2934</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>2843</v>
+        <v>2935</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="24"/>
-      <c r="E36" s="1003"/>
-      <c r="F36" s="919"/>
-      <c r="G36" s="919"/>
-      <c r="H36" s="919"/>
+      <c r="E36" s="913"/>
+      <c r="F36" s="914"/>
+      <c r="G36" s="914"/>
+      <c r="H36" s="914"/>
       <c r="I36" s="22"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1004" t="s">
-        <v>2844</v>
+      <c r="A37" s="915" t="s">
+        <v>2936</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>2845</v>
+        <v>2937</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="24"/>
-      <c r="E37" s="1003"/>
-      <c r="F37" s="919"/>
-      <c r="G37" s="919"/>
-      <c r="H37" s="919"/>
+      <c r="E37" s="913"/>
+      <c r="F37" s="914"/>
+      <c r="G37" s="914"/>
+      <c r="H37" s="914"/>
       <c r="I37" s="22"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1004" t="s">
-        <v>2846</v>
+      <c r="A38" s="915" t="s">
+        <v>2938</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>2847</v>
+        <v>2939</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="24"/>
-      <c r="E38" s="1003"/>
-      <c r="F38" s="919"/>
-      <c r="G38" s="919"/>
-      <c r="H38" s="919"/>
+      <c r="E38" s="913"/>
+      <c r="F38" s="914"/>
+      <c r="G38" s="914"/>
+      <c r="H38" s="914"/>
       <c r="I38" s="22"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1004" t="s">
-        <v>2848</v>
+      <c r="A39" s="915" t="s">
+        <v>2940</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>2849</v>
+        <v>2941</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="24"/>
-      <c r="E39" s="1003"/>
-      <c r="F39" s="919"/>
-      <c r="G39" s="919"/>
-      <c r="H39" s="919"/>
+      <c r="E39" s="913"/>
+      <c r="F39" s="914"/>
+      <c r="G39" s="914"/>
+      <c r="H39" s="914"/>
       <c r="I39" s="22"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1004" t="s">
-        <v>2850</v>
+      <c r="A40" s="915" t="s">
+        <v>2942</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>2851</v>
+        <v>2943</v>
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="24"/>
-      <c r="E40" s="1003"/>
-      <c r="F40" s="919"/>
-      <c r="G40" s="919"/>
-      <c r="H40" s="919"/>
+      <c r="E40" s="913"/>
+      <c r="F40" s="914"/>
+      <c r="G40" s="914"/>
+      <c r="H40" s="914"/>
       <c r="I40" s="22"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1004" t="s">
-        <v>2852</v>
+      <c r="A41" s="915" t="s">
+        <v>2944</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>2853</v>
+        <v>2945</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="24"/>
-      <c r="E41" s="1003"/>
-      <c r="F41" s="919"/>
-      <c r="G41" s="919"/>
-      <c r="H41" s="919"/>
+      <c r="E41" s="913"/>
+      <c r="F41" s="914"/>
+      <c r="G41" s="914"/>
+      <c r="H41" s="914"/>
       <c r="I41" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1004" t="s">
-        <v>2854</v>
+      <c r="A42" s="915" t="s">
+        <v>2946</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>2855</v>
+        <v>2947</v>
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="24"/>
-      <c r="E42" s="1003"/>
-      <c r="F42" s="919"/>
-      <c r="G42" s="919"/>
-      <c r="H42" s="919"/>
+      <c r="E42" s="913"/>
+      <c r="F42" s="914"/>
+      <c r="G42" s="914"/>
+      <c r="H42" s="914"/>
       <c r="I42" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1004" t="s">
-        <v>2856</v>
+      <c r="A43" s="915" t="s">
+        <v>2948</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>2857</v>
+        <v>2949</v>
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="24"/>
-      <c r="E43" s="1003"/>
-      <c r="F43" s="919"/>
-      <c r="G43" s="919"/>
-      <c r="H43" s="919"/>
+      <c r="E43" s="913"/>
+      <c r="F43" s="914"/>
+      <c r="G43" s="914"/>
+      <c r="H43" s="914"/>
       <c r="I43" s="22"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="999" t="s">
-        <v>2858</v>
-      </c>
-      <c r="B44" s="999"/>
+      <c r="A44" s="908" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B44" s="908"/>
       <c r="C44" s="20"/>
       <c r="D44" s="24"/>
-      <c r="E44" s="1003"/>
-      <c r="F44" s="919"/>
-      <c r="G44" s="919"/>
-      <c r="H44" s="919"/>
+      <c r="E44" s="913"/>
+      <c r="F44" s="914"/>
+      <c r="G44" s="914"/>
+      <c r="H44" s="914"/>
       <c r="I44" s="22"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1004" t="s">
-        <v>2859</v>
+      <c r="A45" s="915" t="s">
+        <v>2951</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>2860</v>
+        <v>2952</v>
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="24"/>
-      <c r="E45" s="1003"/>
-      <c r="F45" s="919"/>
-      <c r="G45" s="919"/>
-      <c r="H45" s="919"/>
+      <c r="E45" s="913"/>
+      <c r="F45" s="914"/>
+      <c r="G45" s="914"/>
+      <c r="H45" s="914"/>
       <c r="I45" s="22"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1004" t="s">
-        <v>2861</v>
+      <c r="A46" s="915" t="s">
+        <v>2953</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>2862</v>
+        <v>2954</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="24"/>
-      <c r="E46" s="1003"/>
-      <c r="F46" s="919"/>
-      <c r="G46" s="919"/>
-      <c r="H46" s="919"/>
+      <c r="E46" s="913"/>
+      <c r="F46" s="914"/>
+      <c r="G46" s="914"/>
+      <c r="H46" s="914"/>
       <c r="I46" s="22"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1004" t="s">
-        <v>2863</v>
+      <c r="A47" s="915" t="s">
+        <v>2955</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>2864</v>
+        <v>2956</v>
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="24"/>
-      <c r="E47" s="1003"/>
-      <c r="F47" s="919"/>
-      <c r="G47" s="919"/>
-      <c r="H47" s="919"/>
+      <c r="E47" s="913"/>
+      <c r="F47" s="914"/>
+      <c r="G47" s="914"/>
+      <c r="H47" s="914"/>
       <c r="I47" s="22"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1004" t="s">
-        <v>2865</v>
+      <c r="A48" s="915" t="s">
+        <v>2957</v>
       </c>
       <c r="B48" s="24"/>
       <c r="C48" s="20"/>
       <c r="D48" s="24"/>
-      <c r="E48" s="1003"/>
-      <c r="F48" s="919"/>
-      <c r="G48" s="919"/>
-      <c r="H48" s="919"/>
+      <c r="E48" s="913"/>
+      <c r="F48" s="914"/>
+      <c r="G48" s="914"/>
+      <c r="H48" s="914"/>
       <c r="I48" s="22"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1004" t="s">
-        <v>2866</v>
+      <c r="A49" s="915" t="s">
+        <v>2958</v>
       </c>
       <c r="B49" s="24"/>
       <c r="C49" s="20"/>
       <c r="D49" s="24"/>
-      <c r="E49" s="1003"/>
-      <c r="F49" s="919"/>
-      <c r="G49" s="919"/>
-      <c r="H49" s="919"/>
+      <c r="E49" s="913"/>
+      <c r="F49" s="914"/>
+      <c r="G49" s="914"/>
+      <c r="H49" s="914"/>
       <c r="I49" s="22"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1004" t="s">
-        <v>2867</v>
+      <c r="A50" s="915" t="s">
+        <v>2959</v>
       </c>
       <c r="B50" s="24"/>
       <c r="C50" s="20"/>
       <c r="D50" s="24"/>
-      <c r="E50" s="1003"/>
-      <c r="F50" s="919"/>
-      <c r="G50" s="919"/>
-      <c r="H50" s="919"/>
+      <c r="E50" s="913"/>
+      <c r="F50" s="914"/>
+      <c r="G50" s="914"/>
+      <c r="H50" s="914"/>
       <c r="I50" s="22"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1004"/>
+      <c r="A51" s="915"/>
       <c r="B51" s="24"/>
       <c r="C51" s="20"/>
       <c r="D51" s="24"/>
-      <c r="E51" s="1003"/>
-      <c r="F51" s="919"/>
-      <c r="G51" s="919"/>
-      <c r="H51" s="919"/>
+      <c r="E51" s="913"/>
+      <c r="F51" s="914"/>
+      <c r="G51" s="914"/>
+      <c r="H51" s="914"/>
       <c r="I51" s="22"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="999" t="s">
-        <v>2868</v>
-      </c>
-      <c r="B52" s="999"/>
+      <c r="A52" s="908" t="s">
+        <v>2960</v>
+      </c>
+      <c r="B52" s="908"/>
       <c r="C52" s="20"/>
       <c r="D52" s="24"/>
-      <c r="E52" s="1003"/>
-      <c r="F52" s="919"/>
-      <c r="G52" s="919"/>
-      <c r="H52" s="919"/>
+      <c r="E52" s="913"/>
+      <c r="F52" s="914"/>
+      <c r="G52" s="914"/>
+      <c r="H52" s="914"/>
       <c r="I52" s="22"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1004" t="s">
-        <v>2869</v>
+      <c r="A53" s="915" t="s">
+        <v>2961</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>2870</v>
+        <v>2962</v>
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="24"/>
-      <c r="E53" s="1003"/>
-      <c r="F53" s="919"/>
-      <c r="G53" s="919"/>
-      <c r="H53" s="919"/>
+      <c r="E53" s="913"/>
+      <c r="F53" s="914"/>
+      <c r="G53" s="914"/>
+      <c r="H53" s="914"/>
       <c r="I53" s="22"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1004" t="s">
-        <v>2871</v>
+      <c r="A54" s="915" t="s">
+        <v>2963</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>2872</v>
+        <v>2964</v>
       </c>
       <c r="C54" s="20"/>
       <c r="D54" s="24"/>
-      <c r="E54" s="1003"/>
-      <c r="F54" s="919"/>
-      <c r="G54" s="919"/>
-      <c r="H54" s="919"/>
+      <c r="E54" s="913"/>
+      <c r="F54" s="914"/>
+      <c r="G54" s="914"/>
+      <c r="H54" s="914"/>
       <c r="I54" s="22"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1004"/>
+      <c r="A55" s="915"/>
       <c r="B55" s="24"/>
       <c r="C55" s="20"/>
       <c r="D55" s="24"/>
-      <c r="E55" s="1003"/>
-      <c r="F55" s="919"/>
-      <c r="G55" s="919"/>
-      <c r="H55" s="919"/>
+      <c r="E55" s="913"/>
+      <c r="F55" s="914"/>
+      <c r="G55" s="914"/>
+      <c r="H55" s="914"/>
       <c r="I55" s="22"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1004"/>
+      <c r="A56" s="915"/>
       <c r="B56" s="24"/>
       <c r="C56" s="20"/>
       <c r="D56" s="24"/>
-      <c r="E56" s="1003"/>
-      <c r="F56" s="919"/>
-      <c r="G56" s="919"/>
-      <c r="H56" s="919"/>
+      <c r="E56" s="913"/>
+      <c r="F56" s="914"/>
+      <c r="G56" s="914"/>
+      <c r="H56" s="914"/>
       <c r="I56" s="22"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1004"/>
+      <c r="A57" s="915"/>
       <c r="B57" s="24"/>
       <c r="C57" s="20"/>
       <c r="D57" s="24"/>
-      <c r="E57" s="1003"/>
-      <c r="F57" s="919"/>
-      <c r="G57" s="919"/>
-      <c r="H57" s="919"/>
+      <c r="E57" s="913"/>
+      <c r="F57" s="914"/>
+      <c r="G57" s="914"/>
+      <c r="H57" s="914"/>
       <c r="I57" s="22"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1004"/>
+      <c r="A58" s="915"/>
       <c r="B58" s="24"/>
       <c r="C58" s="20"/>
       <c r="D58" s="24"/>
-      <c r="E58" s="1003"/>
-      <c r="F58" s="919"/>
-      <c r="G58" s="919"/>
-      <c r="H58" s="919"/>
+      <c r="E58" s="913"/>
+      <c r="F58" s="914"/>
+      <c r="G58" s="914"/>
+      <c r="H58" s="914"/>
       <c r="I58" s="22"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19399,32 +18738,32 @@
       <c r="B59" s="24"/>
       <c r="C59" s="20"/>
       <c r="D59" s="24"/>
-      <c r="E59" s="1003"/>
-      <c r="F59" s="919"/>
-      <c r="G59" s="919"/>
-      <c r="H59" s="919"/>
+      <c r="E59" s="913"/>
+      <c r="F59" s="914"/>
+      <c r="G59" s="914"/>
+      <c r="H59" s="914"/>
       <c r="I59" s="22"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="17"/>
-      <c r="B60" s="1005"/>
-      <c r="C60" s="1006"/>
-      <c r="D60" s="1005"/>
-      <c r="E60" s="1003"/>
-      <c r="F60" s="919"/>
-      <c r="G60" s="919"/>
-      <c r="H60" s="919"/>
+      <c r="B60" s="916"/>
+      <c r="C60" s="917"/>
+      <c r="D60" s="916"/>
+      <c r="E60" s="913"/>
+      <c r="F60" s="914"/>
+      <c r="G60" s="914"/>
+      <c r="H60" s="914"/>
       <c r="I60" s="22"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1007"/>
+      <c r="A61" s="918"/>
       <c r="B61" s="24"/>
       <c r="C61" s="20"/>
       <c r="D61" s="24"/>
-      <c r="E61" s="1003"/>
-      <c r="F61" s="919"/>
-      <c r="G61" s="919"/>
-      <c r="H61" s="919"/>
+      <c r="E61" s="913"/>
+      <c r="F61" s="914"/>
+      <c r="G61" s="914"/>
+      <c r="H61" s="914"/>
       <c r="I61" s="22"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19432,192 +18771,192 @@
       <c r="B62" s="24"/>
       <c r="C62" s="20"/>
       <c r="D62" s="24"/>
-      <c r="E62" s="1003"/>
-      <c r="F62" s="919"/>
-      <c r="G62" s="919"/>
-      <c r="H62" s="919"/>
+      <c r="E62" s="913"/>
+      <c r="F62" s="914"/>
+      <c r="G62" s="914"/>
+      <c r="H62" s="914"/>
       <c r="I62" s="22"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="24"/>
-      <c r="F63" s="997"/>
-      <c r="G63" s="997"/>
-      <c r="H63" s="997"/>
+      <c r="F63" s="906"/>
+      <c r="G63" s="906"/>
+      <c r="H63" s="906"/>
       <c r="I63" s="752"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="999" t="s">
-        <v>2873</v>
-      </c>
-      <c r="B64" s="999"/>
-      <c r="F64" s="997"/>
-      <c r="G64" s="997"/>
-      <c r="H64" s="997"/>
+      <c r="A64" s="908" t="s">
+        <v>2965</v>
+      </c>
+      <c r="B64" s="908"/>
+      <c r="F64" s="906"/>
+      <c r="G64" s="906"/>
+      <c r="H64" s="906"/>
       <c r="I64" s="752"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1004" t="s">
-        <v>2874</v>
+      <c r="A65" s="915" t="s">
+        <v>2966</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>2875</v>
-      </c>
-      <c r="F65" s="997"/>
-      <c r="G65" s="997"/>
-      <c r="H65" s="997"/>
+        <v>2967</v>
+      </c>
+      <c r="F65" s="906"/>
+      <c r="G65" s="906"/>
+      <c r="H65" s="906"/>
       <c r="I65" s="752"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F66" s="997"/>
-      <c r="G66" s="997"/>
-      <c r="H66" s="997"/>
+      <c r="F66" s="906"/>
+      <c r="G66" s="906"/>
+      <c r="H66" s="906"/>
       <c r="I66" s="752"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F67" s="997"/>
-      <c r="G67" s="997"/>
-      <c r="H67" s="997"/>
+      <c r="F67" s="906"/>
+      <c r="G67" s="906"/>
+      <c r="H67" s="906"/>
       <c r="I67" s="752"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F68" s="997"/>
-      <c r="G68" s="997"/>
-      <c r="H68" s="997"/>
+      <c r="F68" s="906"/>
+      <c r="G68" s="906"/>
+      <c r="H68" s="906"/>
       <c r="I68" s="752"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F69" s="997"/>
-      <c r="G69" s="997"/>
-      <c r="H69" s="997"/>
+      <c r="F69" s="906"/>
+      <c r="G69" s="906"/>
+      <c r="H69" s="906"/>
       <c r="I69" s="752"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F70" s="997"/>
-      <c r="G70" s="997"/>
-      <c r="H70" s="997"/>
+      <c r="F70" s="906"/>
+      <c r="G70" s="906"/>
+      <c r="H70" s="906"/>
       <c r="I70" s="752"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F71" s="997"/>
-      <c r="G71" s="997"/>
-      <c r="H71" s="997"/>
+      <c r="F71" s="906"/>
+      <c r="G71" s="906"/>
+      <c r="H71" s="906"/>
       <c r="I71" s="752"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F72" s="997"/>
-      <c r="G72" s="997"/>
-      <c r="H72" s="997"/>
+      <c r="F72" s="906"/>
+      <c r="G72" s="906"/>
+      <c r="H72" s="906"/>
       <c r="I72" s="752"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1008"/>
-      <c r="F73" s="997"/>
-      <c r="G73" s="997"/>
-      <c r="H73" s="997"/>
+      <c r="A73" s="919"/>
+      <c r="F73" s="906"/>
+      <c r="G73" s="906"/>
+      <c r="H73" s="906"/>
       <c r="I73" s="752"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F74" s="997"/>
-      <c r="G74" s="997"/>
-      <c r="H74" s="997"/>
+      <c r="F74" s="906"/>
+      <c r="G74" s="906"/>
+      <c r="H74" s="906"/>
       <c r="I74" s="752"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F75" s="997"/>
-      <c r="G75" s="997"/>
-      <c r="H75" s="997"/>
+      <c r="F75" s="906"/>
+      <c r="G75" s="906"/>
+      <c r="H75" s="906"/>
       <c r="I75" s="752"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="660"/>
-      <c r="F76" s="997"/>
-      <c r="G76" s="997"/>
-      <c r="H76" s="997"/>
+      <c r="F76" s="906"/>
+      <c r="G76" s="906"/>
+      <c r="H76" s="906"/>
       <c r="I76" s="752"/>
       <c r="L76" s="138"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="660"/>
-      <c r="F77" s="997"/>
-      <c r="G77" s="997"/>
-      <c r="H77" s="997"/>
+      <c r="F77" s="906"/>
+      <c r="G77" s="906"/>
+      <c r="H77" s="906"/>
       <c r="I77" s="752"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F78" s="997"/>
-      <c r="G78" s="997"/>
-      <c r="H78" s="997"/>
+      <c r="F78" s="906"/>
+      <c r="G78" s="906"/>
+      <c r="H78" s="906"/>
       <c r="I78" s="752"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1009"/>
-      <c r="F79" s="997"/>
-      <c r="G79" s="997"/>
-      <c r="H79" s="997"/>
+      <c r="A79" s="920"/>
+      <c r="F79" s="906"/>
+      <c r="G79" s="906"/>
+      <c r="H79" s="906"/>
       <c r="I79" s="752"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="660"/>
-      <c r="B80" s="1010"/>
-      <c r="C80" s="1011"/>
-      <c r="D80" s="1010"/>
-      <c r="F80" s="997"/>
-      <c r="G80" s="997"/>
-      <c r="H80" s="997"/>
+      <c r="B80" s="921"/>
+      <c r="C80" s="922"/>
+      <c r="D80" s="921"/>
+      <c r="F80" s="906"/>
+      <c r="G80" s="906"/>
+      <c r="H80" s="906"/>
       <c r="I80" s="752"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K82" s="1012" t="s">
-        <v>2876</v>
+      <c r="K82" s="923" t="s">
+        <v>2968</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1009"/>
-      <c r="K83" s="1008"/>
+      <c r="A83" s="920"/>
+      <c r="K83" s="919"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K84" s="1008"/>
+      <c r="K84" s="919"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="1013"/>
-      <c r="C87" s="1014"/>
-      <c r="D87" s="1013"/>
+      <c r="B87" s="924"/>
+      <c r="C87" s="925"/>
+      <c r="D87" s="924"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="576"/>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1015"/>
+      <c r="A89" s="926"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="1010"/>
-      <c r="C90" s="1011"/>
-      <c r="D90" s="1010"/>
+      <c r="B90" s="921"/>
+      <c r="C90" s="922"/>
+      <c r="D90" s="921"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1008"/>
-      <c r="B93" s="1016"/>
-      <c r="C93" s="1008"/>
-      <c r="D93" s="1016"/>
+      <c r="A93" s="919"/>
+      <c r="B93" s="927"/>
+      <c r="C93" s="919"/>
+      <c r="D93" s="927"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1017"/>
+      <c r="A94" s="928"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="660"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1017"/>
+      <c r="A97" s="928"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1018"/>
+      <c r="A100" s="929"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="660"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F104" s="122"/>
-      <c r="H104" s="997"/>
+      <c r="H104" s="906"/>
       <c r="I104" s="122"/>
     </row>
   </sheetData>
@@ -19644,415 +18983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B1:O20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="8.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="19.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="12.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="9.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="20.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="14.29"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="6" t="s">
-        <v>2877</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>2878</v>
-      </c>
-      <c r="D1" s="909" t="s">
-        <v>2879</v>
-      </c>
-      <c r="E1" s="905" t="s">
-        <v>2879</v>
-      </c>
-      <c r="F1" s="305" t="s">
-        <v>2879</v>
-      </c>
-      <c r="G1" s="305" t="s">
-        <v>2879</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1019" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="593" t="s">
-        <v>2880</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>2881</v>
-      </c>
-      <c r="E2" s="590" t="s">
-        <v>2882</v>
-      </c>
-      <c r="F2" s="1000" t="s">
-        <v>2883</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1020" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="576" t="s">
-        <v>2884</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>2885</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>2886</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>2887</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>2888</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>2889</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>2890</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>2891</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>2892</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1021" t="s">
-        <v>468</v>
-      </c>
-      <c r="C4" s="576" t="s">
-        <v>2893</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>2894</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>2895</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>2896</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>2897</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>2897</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>2897</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1022" t="s">
-        <v>418</v>
-      </c>
-      <c r="C5" s="576" t="s">
-        <v>2899</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>2900</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>2901</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>2902</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>2903</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>2904</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>2905</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>2906</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1023" t="s">
-        <v>406</v>
-      </c>
-      <c r="C6" s="576" t="s">
-        <v>2907</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>2908</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>2909</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>2910</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>2911</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>2912</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>2913</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>2914</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1024" t="s">
-        <v>440</v>
-      </c>
-      <c r="C7" s="576" t="s">
-        <v>2915</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>2916</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>2917</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>2918</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>2919</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1025" t="s">
-        <v>441</v>
-      </c>
-      <c r="C8" s="576" t="s">
-        <v>2920</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>2921</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>2922</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>2923</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1026" t="s">
-        <v>612</v>
-      </c>
-      <c r="C9" s="576" t="s">
-        <v>2924</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>2925</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>2925</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>2925</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1027" t="s">
-        <v>514</v>
-      </c>
-      <c r="C10" s="576" t="s">
-        <v>2926</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>2927</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>2928</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>2929</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1028" t="s">
-        <v>487</v>
-      </c>
-      <c r="C11" s="576" t="s">
-        <v>2930</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>2910</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>2931</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>2932</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1029" t="s">
-        <v>411</v>
-      </c>
-      <c r="C12" s="576" t="s">
-        <v>2933</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>2934</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>2935</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>2936</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1030" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="576" t="s">
-        <v>2937</v>
-      </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="24"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1031" t="s">
-        <v>535</v>
-      </c>
-      <c r="C14" s="576" t="s">
-        <v>2938</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>2939</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>2940</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>2941</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1032" t="s">
-        <v>158</v>
-      </c>
-      <c r="C15" s="576" t="s">
-        <v>2880</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>2942</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>2941</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>2943</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1033" t="s">
-        <v>570</v>
-      </c>
-      <c r="C16" s="576" t="s">
-        <v>2944</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>2945</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>2946</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>2947</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1034" t="s">
-        <v>464</v>
-      </c>
-      <c r="C17" s="576" t="s">
-        <v>2948</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>2949</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>2950</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>2951</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1035" t="s">
-        <v>454</v>
-      </c>
-      <c r="C18" s="576" t="s">
-        <v>2952</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>2953</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>2954</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>2955</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>2956</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="167" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="583" t="s">
-        <v>2957</v>
-      </c>
-      <c r="D19" s="38" t="s">
-        <v>2958</v>
-      </c>
-      <c r="E19" s="149" t="s">
-        <v>2959</v>
-      </c>
-      <c r="F19" s="174" t="s">
-        <v>2960</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -20064,87 +18995,87 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1036" t="s">
-        <v>2961</v>
-      </c>
-      <c r="B1" s="1036"/>
-      <c r="C1" s="1036"/>
-      <c r="D1" s="1036"/>
-      <c r="E1" s="1036"/>
-      <c r="F1" s="1036"/>
-      <c r="G1" s="1036"/>
-      <c r="H1" s="1036"/>
-      <c r="I1" s="1036"/>
+      <c r="A1" s="930" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B1" s="930"/>
+      <c r="C1" s="930"/>
+      <c r="D1" s="930"/>
+      <c r="E1" s="930"/>
+      <c r="F1" s="930"/>
+      <c r="G1" s="930"/>
+      <c r="H1" s="930"/>
+      <c r="I1" s="930"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>2962</v>
+        <v>2970</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2963</v>
+        <v>2971</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2964</v>
+        <v>2972</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2965</v>
+        <v>2973</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>2966</v>
+        <v>2974</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>2967</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>2968</v>
+        <v>2976</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2969</v>
+        <v>2977</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2970</v>
+        <v>2978</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>2971</v>
+        <v>2979</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>2972</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>2973</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>2974</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>2975</v>
+        <v>2983</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>2976</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>2975</v>
+        <v>2983</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>2977</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>2978</v>
+        <v>2986</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>2979</v>
+        <v>2987</v>
       </c>
       <c r="Q15" s="365" t="s">
         <v>418</v>
@@ -20152,10 +19083,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>2978</v>
+        <v>2986</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>2980</v>
+        <v>2988</v>
       </c>
       <c r="Q16" s="663" t="s">
         <v>441</v>
@@ -20163,10 +19094,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>2981</v>
+        <v>2989</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>2982</v>
+        <v>2990</v>
       </c>
       <c r="Q17" s="342" t="s">
         <v>514</v>
@@ -20174,7 +19105,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>2983</v>
+        <v>2991</v>
       </c>
       <c r="Q18" s="467" t="s">
         <v>487</v>
@@ -20191,7 +19122,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q21" s="1037" t="s">
+      <c r="Q21" s="931" t="s">
         <v>612</v>
       </c>
     </row>
@@ -49633,18 +48564,30 @@
       <c r="A48" s="867" t="n">
         <v>695</v>
       </c>
-      <c r="B48" s="194"/>
+      <c r="B48" s="194" t="s">
+        <v>2426</v>
+      </c>
       <c r="C48" s="744" t="s">
         <v>612</v>
       </c>
       <c r="D48" s="630"/>
-      <c r="E48" s="194"/>
-      <c r="F48" s="197"/>
+      <c r="E48" s="194" t="s">
+        <v>2427</v>
+      </c>
+      <c r="F48" s="197" t="s">
+        <v>537</v>
+      </c>
       <c r="G48" s="198"/>
       <c r="H48" s="198"/>
-      <c r="I48" s="199"/>
-      <c r="J48" s="200"/>
-      <c r="K48" s="201"/>
+      <c r="I48" s="199" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="200" t="n">
+        <v>300</v>
+      </c>
+      <c r="K48" s="201" t="s">
+        <v>1175</v>
+      </c>
       <c r="L48" s="425" t="s">
         <v>1081</v>
       </c>
@@ -49652,7 +48595,7 @@
         <v>156</v>
       </c>
       <c r="N48" s="122" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="O48" s="576"/>
       <c r="P48" s="576"/>
@@ -49661,23 +48604,39 @@
       <c r="A49" s="867" t="n">
         <v>696</v>
       </c>
-      <c r="B49" s="194"/>
+      <c r="B49" s="194" t="s">
+        <v>2429</v>
+      </c>
       <c r="C49" s="860" t="s">
         <v>487</v>
       </c>
       <c r="D49" s="601"/>
-      <c r="E49" s="197"/>
-      <c r="F49" s="197"/>
+      <c r="E49" s="197" t="s">
+        <v>2430</v>
+      </c>
+      <c r="F49" s="197" t="s">
+        <v>2431</v>
+      </c>
       <c r="G49" s="198"/>
       <c r="H49" s="198"/>
-      <c r="I49" s="199"/>
-      <c r="J49" s="200"/>
-      <c r="K49" s="201"/>
-      <c r="L49" s="224"/>
+      <c r="I49" s="199" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J49" s="200" t="n">
+        <v>45</v>
+      </c>
+      <c r="K49" s="201" t="s">
+        <v>2373</v>
+      </c>
+      <c r="L49" s="224" t="s">
+        <v>1101</v>
+      </c>
       <c r="M49" s="752" t="s">
         <v>156</v>
       </c>
-      <c r="N49" s="122"/>
+      <c r="N49" s="122" t="s">
+        <v>2432</v>
+      </c>
       <c r="O49" s="576"/>
       <c r="P49" s="576"/>
     </row>
@@ -49686,14 +48645,14 @@
         <v>697</v>
       </c>
       <c r="B50" s="194" t="s">
-        <v>2427</v>
+        <v>2433</v>
       </c>
       <c r="C50" s="111" t="s">
         <v>570</v>
       </c>
       <c r="D50" s="504"/>
       <c r="E50" s="197" t="s">
-        <v>2428</v>
+        <v>2434</v>
       </c>
       <c r="F50" s="197" t="s">
         <v>699</v>
@@ -49707,7 +48666,7 @@
         <v>87</v>
       </c>
       <c r="K50" s="201" t="s">
-        <v>2429</v>
+        <v>2435</v>
       </c>
       <c r="L50" s="224" t="s">
         <v>1101</v>
@@ -49716,7 +48675,7 @@
         <v>156</v>
       </c>
       <c r="N50" s="122" t="s">
-        <v>2430</v>
+        <v>2436</v>
       </c>
       <c r="O50" s="576"/>
       <c r="P50" s="576"/>
@@ -49725,26 +48684,44 @@
       <c r="A51" s="867" t="n">
         <v>698</v>
       </c>
-      <c r="B51" s="194"/>
+      <c r="B51" s="194" t="s">
+        <v>2437</v>
+      </c>
       <c r="C51" s="171" t="s">
         <v>100</v>
       </c>
       <c r="D51" s="223"/>
-      <c r="E51" s="197"/>
-      <c r="F51" s="197"/>
-      <c r="G51" s="198"/>
+      <c r="E51" s="197" t="s">
+        <v>2438</v>
+      </c>
+      <c r="F51" s="197" t="s">
+        <v>992</v>
+      </c>
+      <c r="G51" s="198" t="s">
+        <v>646</v>
+      </c>
       <c r="H51" s="198"/>
-      <c r="I51" s="199"/>
-      <c r="J51" s="200"/>
-      <c r="K51" s="201"/>
-      <c r="L51" s="224"/>
+      <c r="I51" s="199" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J51" s="200" t="n">
+        <v>45</v>
+      </c>
+      <c r="K51" s="201" t="s">
+        <v>2359</v>
+      </c>
+      <c r="L51" s="224" t="s">
+        <v>1081</v>
+      </c>
       <c r="M51" s="752" t="s">
         <v>156</v>
       </c>
       <c r="N51" s="122" t="s">
-        <v>2431</v>
-      </c>
-      <c r="O51" s="576"/>
+        <v>2439</v>
+      </c>
+      <c r="O51" s="576" t="s">
+        <v>2440</v>
+      </c>
       <c r="P51" s="576"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49752,14 +48729,14 @@
         <v>699</v>
       </c>
       <c r="B52" s="194" t="s">
-        <v>2432</v>
+        <v>2441</v>
       </c>
       <c r="C52" s="126" t="s">
         <v>535</v>
       </c>
       <c r="D52" s="378"/>
       <c r="E52" s="197" t="s">
-        <v>2433</v>
+        <v>2442</v>
       </c>
       <c r="F52" s="197" t="s">
         <v>1552</v>
@@ -49775,7 +48752,7 @@
         <v>33</v>
       </c>
       <c r="K52" s="201" t="s">
-        <v>2434</v>
+        <v>2443</v>
       </c>
       <c r="L52" s="224" t="s">
         <v>1272</v>
@@ -49784,35 +48761,47 @@
         <v>156</v>
       </c>
       <c r="N52" s="122" t="s">
-        <v>2435</v>
-      </c>
-      <c r="O52" s="576" t="s">
-        <v>2436</v>
-      </c>
+        <v>2444</v>
+      </c>
+      <c r="O52" s="576"/>
       <c r="P52" s="576"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="867" t="n">
         <v>700</v>
       </c>
-      <c r="B53" s="194"/>
+      <c r="B53" s="194" t="s">
+        <v>2445</v>
+      </c>
       <c r="C53" s="737" t="s">
         <v>158</v>
       </c>
       <c r="D53" s="853"/>
-      <c r="E53" s="197"/>
-      <c r="F53" s="197"/>
+      <c r="E53" s="197" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F53" s="197" t="s">
+        <v>460</v>
+      </c>
       <c r="G53" s="198"/>
       <c r="H53" s="198"/>
-      <c r="I53" s="199"/>
-      <c r="J53" s="200"/>
-      <c r="K53" s="201"/>
-      <c r="L53" s="224"/>
+      <c r="I53" s="199" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J53" s="200" t="n">
+        <v>65</v>
+      </c>
+      <c r="K53" s="201" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L53" s="224" t="s">
+        <v>1091</v>
+      </c>
       <c r="M53" s="752" t="s">
         <v>156</v>
       </c>
       <c r="N53" s="122" t="s">
-        <v>2437</v>
+        <v>2447</v>
       </c>
       <c r="O53" s="576"/>
       <c r="P53" s="576"/>
@@ -49846,17 +48835,17 @@
         <v>702</v>
       </c>
       <c r="B55" s="194" t="s">
-        <v>2438</v>
+        <v>2448</v>
       </c>
       <c r="C55" s="133" t="s">
         <v>78</v>
       </c>
       <c r="D55" s="385"/>
       <c r="E55" s="197" t="s">
-        <v>2439</v>
+        <v>2449</v>
       </c>
       <c r="F55" s="197" t="s">
-        <v>2440</v>
+        <v>2450</v>
       </c>
       <c r="G55" s="198"/>
       <c r="H55" s="198"/>
@@ -49876,7 +48865,7 @@
         <v>156</v>
       </c>
       <c r="N55" s="122" t="s">
-        <v>2441</v>
+        <v>2451</v>
       </c>
       <c r="O55" s="576"/>
       <c r="P55" s="576"/>
@@ -49909,23 +48898,39 @@
       <c r="A57" s="867" t="n">
         <v>704</v>
       </c>
-      <c r="B57" s="194"/>
+      <c r="B57" s="194" t="s">
+        <v>2452</v>
+      </c>
       <c r="C57" s="879" t="s">
         <v>468</v>
       </c>
       <c r="D57" s="880"/>
-      <c r="E57" s="197"/>
-      <c r="F57" s="197"/>
+      <c r="E57" s="197" t="s">
+        <v>2453</v>
+      </c>
+      <c r="F57" s="197" t="s">
+        <v>819</v>
+      </c>
       <c r="G57" s="198"/>
       <c r="H57" s="198"/>
-      <c r="I57" s="199"/>
-      <c r="J57" s="200"/>
-      <c r="K57" s="201"/>
-      <c r="L57" s="224"/>
+      <c r="I57" s="199" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J57" s="200" t="n">
+        <v>7</v>
+      </c>
+      <c r="K57" s="201" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L57" s="224" t="s">
+        <v>1081</v>
+      </c>
       <c r="M57" s="752" t="s">
         <v>156</v>
       </c>
-      <c r="N57" s="122"/>
+      <c r="N57" s="122" t="s">
+        <v>2454</v>
+      </c>
       <c r="O57" s="576"/>
       <c r="P57" s="576"/>
     </row>
@@ -49934,14 +48939,14 @@
         <v>705</v>
       </c>
       <c r="B58" s="194" t="s">
-        <v>2442</v>
+        <v>2455</v>
       </c>
       <c r="C58" s="652" t="s">
         <v>411</v>
       </c>
       <c r="D58" s="881"/>
       <c r="E58" s="197" t="s">
-        <v>2443</v>
+        <v>2456</v>
       </c>
       <c r="F58" s="197" t="s">
         <v>900</v>
@@ -49964,10 +48969,10 @@
         <v>156</v>
       </c>
       <c r="N58" s="576" t="s">
-        <v>2444</v>
+        <v>2457</v>
       </c>
       <c r="O58" s="576" t="s">
-        <v>2445</v>
+        <v>2458</v>
       </c>
       <c r="P58" s="576"/>
     </row>
@@ -49976,14 +48981,14 @@
         <v>706</v>
       </c>
       <c r="B59" s="203" t="s">
-        <v>2446</v>
+        <v>2459</v>
       </c>
       <c r="C59" s="399" t="s">
         <v>141</v>
       </c>
       <c r="D59" s="323"/>
       <c r="E59" s="206" t="s">
-        <v>2447</v>
+        <v>2460</v>
       </c>
       <c r="F59" s="206" t="s">
         <v>1442</v>
@@ -49997,12 +49002,14 @@
         <v>156</v>
       </c>
       <c r="K59" s="210"/>
-      <c r="L59" s="508"/>
+      <c r="L59" s="589" t="s">
+        <v>1081</v>
+      </c>
       <c r="M59" s="883" t="s">
         <v>156</v>
       </c>
       <c r="N59" s="884" t="s">
-        <v>2447</v>
+        <v>2461</v>
       </c>
       <c r="O59" s="583"/>
       <c r="P59" s="583"/>
@@ -50052,7 +49059,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="180" t="s">
-        <v>2448</v>
+        <v>2462</v>
       </c>
       <c r="B1" s="180"/>
       <c r="C1" s="180"/>
@@ -50128,14 +49135,14 @@
         <v>541</v>
       </c>
       <c r="B3" s="185" t="s">
-        <v>2449</v>
+        <v>2463</v>
       </c>
       <c r="C3" s="71" t="s">
         <v>441</v>
       </c>
       <c r="D3" s="233"/>
       <c r="E3" s="188" t="s">
-        <v>2450</v>
+        <v>2464</v>
       </c>
       <c r="F3" s="188" t="s">
         <v>914</v>
@@ -50158,7 +49165,7 @@
         <v>156</v>
       </c>
       <c r="N3" s="866" t="s">
-        <v>2451</v>
+        <v>2465</v>
       </c>
       <c r="O3" s="885"/>
       <c r="P3" s="570"/>
@@ -50168,7 +49175,7 @@
         <v>542</v>
       </c>
       <c r="B4" s="194" t="s">
-        <v>2452</v>
+        <v>2466</v>
       </c>
       <c r="C4" s="46" t="s">
         <v>440</v>
@@ -50177,13 +49184,13 @@
         <v>454</v>
       </c>
       <c r="E4" s="197" t="s">
-        <v>2453</v>
+        <v>2467</v>
       </c>
       <c r="F4" s="197" t="s">
         <v>646</v>
       </c>
       <c r="G4" s="198" t="s">
-        <v>2454</v>
+        <v>2468</v>
       </c>
       <c r="H4" s="198"/>
       <c r="I4" s="199" t="n">
@@ -50202,7 +49209,7 @@
         <v>156</v>
       </c>
       <c r="N4" s="871" t="s">
-        <v>2455</v>
+        <v>2469</v>
       </c>
       <c r="O4" s="122"/>
       <c r="P4" s="576"/>
@@ -50212,7 +49219,7 @@
         <v>543</v>
       </c>
       <c r="B5" s="194" t="s">
-        <v>2456</v>
+        <v>2470</v>
       </c>
       <c r="C5" s="79" t="s">
         <v>141</v>
@@ -50221,7 +49228,7 @@
         <v>454</v>
       </c>
       <c r="E5" s="197" t="s">
-        <v>2457</v>
+        <v>2471</v>
       </c>
       <c r="F5" s="197" t="s">
         <v>750</v>
@@ -50246,7 +49253,7 @@
         <v>156</v>
       </c>
       <c r="N5" s="871" t="s">
-        <v>2458</v>
+        <v>2472</v>
       </c>
       <c r="O5" s="122"/>
       <c r="P5" s="576"/>
@@ -50256,7 +49263,7 @@
         <v>544</v>
       </c>
       <c r="B6" s="194" t="s">
-        <v>2459</v>
+        <v>2473</v>
       </c>
       <c r="C6" s="115" t="s">
         <v>514</v>
@@ -50265,7 +49272,7 @@
         <v>535</v>
       </c>
       <c r="E6" s="197" t="s">
-        <v>2460</v>
+        <v>2474</v>
       </c>
       <c r="F6" s="197" t="s">
         <v>537</v>
@@ -50288,10 +49295,10 @@
         <v>156</v>
       </c>
       <c r="N6" s="871" t="s">
-        <v>2461</v>
+        <v>2475</v>
       </c>
       <c r="O6" s="871" t="s">
-        <v>2462</v>
+        <v>2476</v>
       </c>
       <c r="P6" s="576"/>
     </row>
@@ -50300,14 +49307,14 @@
         <v>545</v>
       </c>
       <c r="B7" s="194" t="s">
-        <v>2463</v>
+        <v>2477</v>
       </c>
       <c r="C7" s="59" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="330"/>
       <c r="E7" s="197" t="s">
-        <v>2464</v>
+        <v>2478</v>
       </c>
       <c r="F7" s="197" t="s">
         <v>435</v>
@@ -50330,10 +49337,10 @@
         <v>156</v>
       </c>
       <c r="N7" s="871" t="s">
-        <v>2465</v>
+        <v>2479</v>
       </c>
       <c r="O7" s="871" t="s">
-        <v>2466</v>
+        <v>2480</v>
       </c>
       <c r="P7" s="576"/>
     </row>
@@ -50342,14 +49349,14 @@
         <v>546</v>
       </c>
       <c r="B8" s="194" t="s">
-        <v>2467</v>
+        <v>2481</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>406</v>
       </c>
       <c r="D8" s="361"/>
       <c r="E8" s="197" t="s">
-        <v>2468</v>
+        <v>2482</v>
       </c>
       <c r="F8" s="197" t="s">
         <v>435</v>
@@ -50374,13 +49381,13 @@
         <v>156</v>
       </c>
       <c r="N8" s="871" t="s">
-        <v>2469</v>
+        <v>2483</v>
       </c>
       <c r="O8" s="871" t="s">
-        <v>2470</v>
+        <v>2484</v>
       </c>
       <c r="P8" s="576" t="s">
-        <v>2471</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="9" s="163" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50388,7 +49395,7 @@
         <v>547</v>
       </c>
       <c r="B9" s="194" t="s">
-        <v>2472</v>
+        <v>2486</v>
       </c>
       <c r="C9" s="387" t="s">
         <v>141</v>
@@ -50397,7 +49404,7 @@
         <v>468</v>
       </c>
       <c r="E9" s="197" t="s">
-        <v>2473</v>
+        <v>2487</v>
       </c>
       <c r="F9" s="197" t="s">
         <v>646</v>
@@ -50422,7 +49429,7 @@
         <v>156</v>
       </c>
       <c r="N9" s="871" t="s">
-        <v>2474</v>
+        <v>2488</v>
       </c>
       <c r="O9" s="871"/>
       <c r="P9" s="576"/>
@@ -50432,7 +49439,7 @@
         <v>548</v>
       </c>
       <c r="B10" s="194" t="s">
-        <v>2475</v>
+        <v>2489</v>
       </c>
       <c r="C10" s="861" t="s">
         <v>464</v>
@@ -50441,7 +49448,7 @@
         <v>158</v>
       </c>
       <c r="E10" s="197" t="s">
-        <v>2476</v>
+        <v>2490</v>
       </c>
       <c r="F10" s="197" t="s">
         <v>676</v>
@@ -50455,7 +49462,7 @@
         <v>19</v>
       </c>
       <c r="K10" s="201" t="s">
-        <v>2477</v>
+        <v>2491</v>
       </c>
       <c r="L10" s="224" t="s">
         <v>1091</v>
@@ -50464,13 +49471,13 @@
         <v>156</v>
       </c>
       <c r="N10" s="871" t="s">
-        <v>2478</v>
+        <v>2492</v>
       </c>
       <c r="O10" s="871" t="s">
-        <v>2479</v>
+        <v>2493</v>
       </c>
       <c r="P10" s="576" t="s">
-        <v>2480</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="11" s="163" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50478,7 +49485,7 @@
         <v>549</v>
       </c>
       <c r="B11" s="194" t="s">
-        <v>2481</v>
+        <v>2495</v>
       </c>
       <c r="C11" s="744" t="s">
         <v>612</v>
@@ -50487,7 +49494,7 @@
         <v>100</v>
       </c>
       <c r="E11" s="197" t="s">
-        <v>2482</v>
+        <v>2496</v>
       </c>
       <c r="F11" s="198" t="s">
         <v>1614</v>
@@ -50512,10 +49519,10 @@
         <v>156</v>
       </c>
       <c r="N11" s="871" t="s">
-        <v>2483</v>
+        <v>2497</v>
       </c>
       <c r="O11" s="871" t="s">
-        <v>2484</v>
+        <v>2498</v>
       </c>
       <c r="P11" s="576"/>
     </row>
@@ -50524,7 +49531,7 @@
         <v>550</v>
       </c>
       <c r="B12" s="194" t="s">
-        <v>2485</v>
+        <v>2499</v>
       </c>
       <c r="C12" s="126" t="s">
         <v>535</v>
@@ -50533,7 +49540,7 @@
         <v>158</v>
       </c>
       <c r="E12" s="197" t="s">
-        <v>2486</v>
+        <v>2500</v>
       </c>
       <c r="F12" s="197" t="s">
         <v>537</v>
@@ -50556,7 +49563,7 @@
         <v>156</v>
       </c>
       <c r="N12" s="122" t="s">
-        <v>2487</v>
+        <v>2501</v>
       </c>
       <c r="O12" s="122"/>
       <c r="P12" s="576"/>
@@ -50566,7 +49573,7 @@
         <v>551</v>
       </c>
       <c r="B13" s="194" t="s">
-        <v>2488</v>
+        <v>2502</v>
       </c>
       <c r="C13" s="34" t="s">
         <v>418</v>
@@ -50575,7 +49582,7 @@
         <v>100</v>
       </c>
       <c r="E13" s="197" t="s">
-        <v>2489</v>
+        <v>2503</v>
       </c>
       <c r="F13" s="198" t="s">
         <v>656</v>
@@ -50600,7 +49607,7 @@
         <v>156</v>
       </c>
       <c r="N13" s="122" t="s">
-        <v>2490</v>
+        <v>2504</v>
       </c>
       <c r="O13" s="122"/>
       <c r="P13" s="576"/>
@@ -50610,7 +49617,7 @@
         <v>552</v>
       </c>
       <c r="B14" s="194" t="s">
-        <v>2491</v>
+        <v>2505</v>
       </c>
       <c r="C14" s="126" t="s">
         <v>535</v>
@@ -50619,7 +49626,7 @@
         <v>441</v>
       </c>
       <c r="E14" s="197" t="s">
-        <v>2492</v>
+        <v>2506</v>
       </c>
       <c r="F14" s="198" t="s">
         <v>834</v>
@@ -50638,13 +49645,13 @@
         <v>2359</v>
       </c>
       <c r="L14" s="224" t="s">
-        <v>2493</v>
+        <v>2507</v>
       </c>
       <c r="M14" s="752" t="s">
         <v>156</v>
       </c>
       <c r="N14" s="122" t="s">
-        <v>2494</v>
+        <v>2508</v>
       </c>
       <c r="O14" s="122"/>
       <c r="P14" s="576"/>
@@ -50654,7 +49661,7 @@
         <v>553</v>
       </c>
       <c r="B15" s="194" t="s">
-        <v>2495</v>
+        <v>2509</v>
       </c>
       <c r="C15" s="111" t="s">
         <v>570</v>
@@ -50698,7 +49705,7 @@
         <v>554</v>
       </c>
       <c r="B16" s="194" t="s">
-        <v>2496</v>
+        <v>2510</v>
       </c>
       <c r="C16" s="111" t="s">
         <v>570</v>
@@ -50707,7 +49714,7 @@
         <v>514</v>
       </c>
       <c r="E16" s="197" t="s">
-        <v>2497</v>
+        <v>2511</v>
       </c>
       <c r="F16" s="197" t="s">
         <v>699</v>
@@ -50742,7 +49749,7 @@
         <v>555</v>
       </c>
       <c r="B17" s="194" t="s">
-        <v>2498</v>
+        <v>2512</v>
       </c>
       <c r="C17" s="860" t="s">
         <v>487</v>
@@ -50751,7 +49758,7 @@
         <v>100</v>
       </c>
       <c r="E17" s="197" t="s">
-        <v>2499</v>
+        <v>2513</v>
       </c>
       <c r="F17" s="197" t="s">
         <v>672</v>
@@ -50776,7 +49783,7 @@
         <v>156</v>
       </c>
       <c r="N17" s="122" t="s">
-        <v>2500</v>
+        <v>2514</v>
       </c>
       <c r="O17" s="122"/>
       <c r="P17" s="576"/>
@@ -50786,14 +49793,14 @@
         <v>556</v>
       </c>
       <c r="B18" s="194" t="s">
-        <v>2501</v>
+        <v>2515</v>
       </c>
       <c r="C18" s="860" t="s">
         <v>487</v>
       </c>
       <c r="D18" s="601"/>
       <c r="E18" s="197" t="s">
-        <v>2502</v>
+        <v>2516</v>
       </c>
       <c r="F18" s="197" t="s">
         <v>676</v>
@@ -50816,7 +49823,7 @@
         <v>156</v>
       </c>
       <c r="N18" s="122" t="s">
-        <v>2503</v>
+        <v>2517</v>
       </c>
       <c r="O18" s="122"/>
       <c r="P18" s="576"/>
@@ -50826,7 +49833,7 @@
         <v>557</v>
       </c>
       <c r="B19" s="194" t="s">
-        <v>2504</v>
+        <v>2518</v>
       </c>
       <c r="C19" s="387" t="s">
         <v>141</v>
@@ -50835,7 +49842,7 @@
         <v>100</v>
       </c>
       <c r="E19" s="197" t="s">
-        <v>2505</v>
+        <v>2519</v>
       </c>
       <c r="F19" s="197" t="s">
         <v>413</v>
@@ -50858,7 +49865,7 @@
         <v>156</v>
       </c>
       <c r="N19" s="122" t="s">
-        <v>2506</v>
+        <v>2520</v>
       </c>
       <c r="O19" s="122"/>
       <c r="P19" s="576"/>
@@ -50868,7 +49875,7 @@
         <v>628</v>
       </c>
       <c r="B20" s="194" t="s">
-        <v>2507</v>
+        <v>2521</v>
       </c>
       <c r="C20" s="46" t="s">
         <v>440</v>
@@ -50877,7 +49884,7 @@
         <v>454</v>
       </c>
       <c r="E20" s="197" t="s">
-        <v>2508</v>
+        <v>2522</v>
       </c>
       <c r="F20" s="197" t="s">
         <v>443</v>
@@ -50904,7 +49911,7 @@
         <v>156</v>
       </c>
       <c r="N20" s="122" t="s">
-        <v>2509</v>
+        <v>2523</v>
       </c>
       <c r="O20" s="122"/>
       <c r="P20" s="576"/>
@@ -50914,7 +49921,7 @@
         <v>629</v>
       </c>
       <c r="B21" s="194" t="s">
-        <v>2510</v>
+        <v>2524</v>
       </c>
       <c r="C21" s="34" t="s">
         <v>418</v>
@@ -50923,10 +49930,10 @@
         <v>158</v>
       </c>
       <c r="E21" s="197" t="s">
-        <v>2511</v>
+        <v>2525</v>
       </c>
       <c r="F21" s="197" t="s">
-        <v>2512</v>
+        <v>2526</v>
       </c>
       <c r="G21" s="198"/>
       <c r="H21" s="198"/>
@@ -50946,10 +49953,10 @@
         <v>156</v>
       </c>
       <c r="N21" s="122" t="s">
-        <v>2513</v>
+        <v>2527</v>
       </c>
       <c r="O21" s="122" t="s">
-        <v>2514</v>
+        <v>2528</v>
       </c>
       <c r="P21" s="576"/>
     </row>
@@ -50958,7 +49965,7 @@
         <v>659</v>
       </c>
       <c r="B22" s="194" t="s">
-        <v>2515</v>
+        <v>2529</v>
       </c>
       <c r="C22" s="46" t="s">
         <v>440</v>
@@ -50967,7 +49974,7 @@
         <v>454</v>
       </c>
       <c r="E22" s="197" t="s">
-        <v>2516</v>
+        <v>2530</v>
       </c>
       <c r="F22" s="197" t="s">
         <v>455</v>
@@ -50992,7 +49999,7 @@
         <v>156</v>
       </c>
       <c r="N22" s="122" t="s">
-        <v>2517</v>
+        <v>2531</v>
       </c>
       <c r="O22" s="122"/>
       <c r="P22" s="576"/>
@@ -51002,7 +50009,7 @@
         <v>660</v>
       </c>
       <c r="B23" s="194" t="s">
-        <v>2518</v>
+        <v>2532</v>
       </c>
       <c r="C23" s="133" t="s">
         <v>78</v>
@@ -51011,7 +50018,7 @@
         <v>570</v>
       </c>
       <c r="E23" s="197" t="s">
-        <v>2519</v>
+        <v>2533</v>
       </c>
       <c r="F23" s="197" t="s">
         <v>2171</v>
@@ -51034,7 +50041,7 @@
         <v>156</v>
       </c>
       <c r="N23" s="122" t="s">
-        <v>2520</v>
+        <v>2534</v>
       </c>
       <c r="O23" s="122"/>
       <c r="P23" s="576"/>
@@ -51044,7 +50051,7 @@
         <v>661</v>
       </c>
       <c r="B24" s="194" t="s">
-        <v>2521</v>
+        <v>2535</v>
       </c>
       <c r="C24" s="46" t="s">
         <v>440</v>
@@ -51053,10 +50060,10 @@
         <v>100</v>
       </c>
       <c r="E24" s="197" t="s">
-        <v>2522</v>
+        <v>2536</v>
       </c>
       <c r="F24" s="197" t="s">
-        <v>2523</v>
+        <v>2537</v>
       </c>
       <c r="G24" s="198"/>
       <c r="H24" s="198"/>
@@ -51076,7 +50083,7 @@
         <v>156</v>
       </c>
       <c r="N24" s="122" t="s">
-        <v>2524</v>
+        <v>2538</v>
       </c>
       <c r="O24" s="122"/>
       <c r="P24" s="576"/>
@@ -51086,7 +50093,7 @@
         <v>662</v>
       </c>
       <c r="B25" s="194" t="s">
-        <v>2525</v>
+        <v>2539</v>
       </c>
       <c r="C25" s="126" t="s">
         <v>535</v>
@@ -51095,7 +50102,7 @@
         <v>78</v>
       </c>
       <c r="E25" s="197" t="s">
-        <v>2526</v>
+        <v>2540</v>
       </c>
       <c r="F25" s="197" t="s">
         <v>784</v>
@@ -51128,7 +50135,7 @@
         <v>663</v>
       </c>
       <c r="B26" s="194" t="s">
-        <v>2527</v>
+        <v>2541</v>
       </c>
       <c r="C26" s="52" t="s">
         <v>454</v>
@@ -51137,7 +50144,7 @@
         <v>441</v>
       </c>
       <c r="E26" s="197" t="s">
-        <v>2528</v>
+        <v>2542</v>
       </c>
       <c r="F26" s="197" t="s">
         <v>443</v>
@@ -51162,7 +50169,7 @@
         <v>20</v>
       </c>
       <c r="N26" s="122" t="s">
-        <v>2529</v>
+        <v>2543</v>
       </c>
       <c r="O26" s="122"/>
       <c r="P26" s="576"/>
@@ -51172,7 +50179,7 @@
         <v>664</v>
       </c>
       <c r="B27" s="194" t="s">
-        <v>2530</v>
+        <v>2544</v>
       </c>
       <c r="C27" s="52" t="s">
         <v>454</v>
@@ -51181,7 +50188,7 @@
         <v>441</v>
       </c>
       <c r="E27" s="197" t="s">
-        <v>2531</v>
+        <v>2545</v>
       </c>
       <c r="F27" s="197" t="s">
         <v>443</v>
@@ -51206,10 +50213,10 @@
         <v>40</v>
       </c>
       <c r="N27" s="122" t="s">
-        <v>2532</v>
+        <v>2546</v>
       </c>
       <c r="O27" s="122" t="s">
-        <v>2533</v>
+        <v>2547</v>
       </c>
       <c r="P27" s="576"/>
     </row>
@@ -51218,7 +50225,7 @@
         <v>665</v>
       </c>
       <c r="B28" s="194" t="s">
-        <v>2534</v>
+        <v>2548</v>
       </c>
       <c r="C28" s="52" t="s">
         <v>454</v>
@@ -51227,7 +50234,7 @@
         <v>441</v>
       </c>
       <c r="E28" s="197" t="s">
-        <v>2535</v>
+        <v>2549</v>
       </c>
       <c r="F28" s="197" t="s">
         <v>443</v>
@@ -51252,10 +50259,10 @@
         <v>156</v>
       </c>
       <c r="N28" s="122" t="s">
-        <v>2532</v>
+        <v>2546</v>
       </c>
       <c r="O28" s="122" t="s">
-        <v>2533</v>
+        <v>2547</v>
       </c>
       <c r="P28" s="576"/>
     </row>
@@ -51264,7 +50271,7 @@
         <v>666</v>
       </c>
       <c r="B29" s="194" t="s">
-        <v>2536</v>
+        <v>2550</v>
       </c>
       <c r="C29" s="744" t="s">
         <v>612</v>
@@ -51273,7 +50280,7 @@
         <v>141</v>
       </c>
       <c r="E29" s="197" t="s">
-        <v>2537</v>
+        <v>2551</v>
       </c>
       <c r="F29" s="197" t="s">
         <v>889</v>
@@ -51300,7 +50307,7 @@
         <v>156</v>
       </c>
       <c r="N29" s="122" t="s">
-        <v>2538</v>
+        <v>2552</v>
       </c>
       <c r="O29" s="122"/>
       <c r="P29" s="576"/>
@@ -51310,14 +50317,14 @@
         <v>667</v>
       </c>
       <c r="B30" s="194" t="s">
-        <v>2539</v>
+        <v>2553</v>
       </c>
       <c r="C30" s="115" t="s">
         <v>514</v>
       </c>
       <c r="D30" s="523"/>
       <c r="E30" s="197" t="s">
-        <v>2540</v>
+        <v>2554</v>
       </c>
       <c r="F30" s="197" t="s">
         <v>585</v>
@@ -51340,7 +50347,7 @@
         <v>30</v>
       </c>
       <c r="N30" s="122" t="s">
-        <v>2541</v>
+        <v>2555</v>
       </c>
       <c r="O30" s="122"/>
       <c r="P30" s="576"/>
@@ -51350,14 +50357,14 @@
         <v>668</v>
       </c>
       <c r="B31" s="194" t="s">
-        <v>2542</v>
+        <v>2556</v>
       </c>
       <c r="C31" s="115" t="s">
         <v>514</v>
       </c>
       <c r="D31" s="523"/>
       <c r="E31" s="197" t="s">
-        <v>2543</v>
+        <v>2557</v>
       </c>
       <c r="F31" s="197" t="s">
         <v>585</v>
@@ -51380,7 +50387,7 @@
         <v>55</v>
       </c>
       <c r="N31" s="122" t="s">
-        <v>2541</v>
+        <v>2555</v>
       </c>
       <c r="O31" s="122"/>
       <c r="P31" s="576"/>
@@ -51390,14 +50397,14 @@
         <v>669</v>
       </c>
       <c r="B32" s="194" t="s">
-        <v>2544</v>
+        <v>2558</v>
       </c>
       <c r="C32" s="115" t="s">
         <v>514</v>
       </c>
       <c r="D32" s="523"/>
       <c r="E32" s="197" t="s">
-        <v>2545</v>
+        <v>2559</v>
       </c>
       <c r="F32" s="197" t="s">
         <v>585</v>
@@ -51420,7 +50427,7 @@
         <v>156</v>
       </c>
       <c r="N32" s="122" t="s">
-        <v>2541</v>
+        <v>2555</v>
       </c>
       <c r="O32" s="122"/>
       <c r="P32" s="576"/>
@@ -51430,7 +50437,7 @@
         <v>670</v>
       </c>
       <c r="B33" s="194" t="s">
-        <v>2546</v>
+        <v>2560</v>
       </c>
       <c r="C33" s="652" t="s">
         <v>411</v>
@@ -51439,7 +50446,7 @@
         <v>514</v>
       </c>
       <c r="E33" s="197" t="s">
-        <v>2547</v>
+        <v>2561</v>
       </c>
       <c r="F33" s="197" t="s">
         <v>413</v>
@@ -51462,7 +50469,7 @@
         <v>40</v>
       </c>
       <c r="N33" s="122" t="s">
-        <v>2548</v>
+        <v>2562</v>
       </c>
       <c r="O33" s="122"/>
       <c r="P33" s="576"/>
@@ -51472,7 +50479,7 @@
         <v>671</v>
       </c>
       <c r="B34" s="194" t="s">
-        <v>2549</v>
+        <v>2563</v>
       </c>
       <c r="C34" s="652" t="s">
         <v>411</v>
@@ -51481,7 +50488,7 @@
         <v>78</v>
       </c>
       <c r="E34" s="197" t="s">
-        <v>2550</v>
+        <v>2564</v>
       </c>
       <c r="F34" s="197" t="s">
         <v>413</v>
@@ -51504,7 +50511,7 @@
         <v>156</v>
       </c>
       <c r="N34" s="122" t="s">
-        <v>2548</v>
+        <v>2562</v>
       </c>
       <c r="O34" s="122"/>
       <c r="P34" s="576"/>
@@ -51514,7 +50521,7 @@
         <v>672</v>
       </c>
       <c r="B35" s="396" t="s">
-        <v>2551</v>
+        <v>2565</v>
       </c>
       <c r="C35" s="115" t="s">
         <v>514</v>
@@ -51523,7 +50530,7 @@
         <v>535</v>
       </c>
       <c r="E35" s="197" t="s">
-        <v>2552</v>
+        <v>2566</v>
       </c>
       <c r="F35" s="197" t="s">
         <v>537</v>
@@ -51546,7 +50553,7 @@
         <v>156</v>
       </c>
       <c r="N35" s="122" t="s">
-        <v>2553</v>
+        <v>2567</v>
       </c>
       <c r="O35" s="122"/>
       <c r="P35" s="576"/>
@@ -51556,7 +50563,7 @@
         <v>673</v>
       </c>
       <c r="B36" s="396" t="s">
-        <v>2554</v>
+        <v>2568</v>
       </c>
       <c r="C36" s="126" t="s">
         <v>535</v>
@@ -51565,10 +50572,10 @@
         <v>411</v>
       </c>
       <c r="E36" s="197" t="s">
-        <v>2555</v>
+        <v>2569</v>
       </c>
       <c r="F36" s="197" t="s">
-        <v>2556</v>
+        <v>2431</v>
       </c>
       <c r="G36" s="198" t="s">
         <v>1552</v>
@@ -51581,7 +50588,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="201" t="s">
-        <v>2557</v>
+        <v>2570</v>
       </c>
       <c r="L36" s="224" t="s">
         <v>1101</v>
@@ -51590,7 +50597,7 @@
         <v>70</v>
       </c>
       <c r="N36" s="122" t="s">
-        <v>2558</v>
+        <v>2571</v>
       </c>
       <c r="O36" s="122"/>
       <c r="P36" s="576"/>
@@ -51600,7 +50607,7 @@
         <v>674</v>
       </c>
       <c r="B37" s="396" t="s">
-        <v>2559</v>
+        <v>2572</v>
       </c>
       <c r="C37" s="126" t="s">
         <v>535</v>
@@ -51609,10 +50616,10 @@
         <v>411</v>
       </c>
       <c r="E37" s="197" t="s">
-        <v>2560</v>
+        <v>2573</v>
       </c>
       <c r="F37" s="197" t="s">
-        <v>2556</v>
+        <v>2431</v>
       </c>
       <c r="G37" s="198" t="s">
         <v>1552</v>
@@ -51625,7 +50632,7 @@
         <v>300</v>
       </c>
       <c r="K37" s="201" t="s">
-        <v>2557</v>
+        <v>2570</v>
       </c>
       <c r="L37" s="224" t="s">
         <v>1101</v>
@@ -51634,7 +50641,7 @@
         <v>156</v>
       </c>
       <c r="N37" s="122" t="s">
-        <v>2561</v>
+        <v>2574</v>
       </c>
       <c r="O37" s="122"/>
       <c r="P37" s="576"/>
@@ -51644,7 +50651,7 @@
         <v>675</v>
       </c>
       <c r="B38" s="396" t="s">
-        <v>2562</v>
+        <v>2575</v>
       </c>
       <c r="C38" s="890" t="s">
         <v>141</v>
@@ -51653,7 +50660,7 @@
         <v>441</v>
       </c>
       <c r="E38" s="197" t="s">
-        <v>2563</v>
+        <v>2576</v>
       </c>
       <c r="F38" s="197" t="s">
         <v>443</v>
@@ -51678,7 +50685,7 @@
         <v>156</v>
       </c>
       <c r="N38" s="122" t="s">
-        <v>2564</v>
+        <v>2577</v>
       </c>
       <c r="O38" s="122"/>
       <c r="P38" s="576"/>
@@ -51688,14 +50695,14 @@
         <v>676</v>
       </c>
       <c r="B39" s="396" t="s">
-        <v>2565</v>
+        <v>2578</v>
       </c>
       <c r="C39" s="891" t="s">
         <v>1414</v>
       </c>
       <c r="D39" s="892"/>
       <c r="E39" s="197" t="s">
-        <v>2566</v>
+        <v>2579</v>
       </c>
       <c r="F39" s="197" t="s">
         <v>834</v>
@@ -51718,7 +50725,7 @@
         <v>156</v>
       </c>
       <c r="N39" s="122" t="s">
-        <v>2567</v>
+        <v>2580</v>
       </c>
       <c r="O39" s="122"/>
       <c r="P39" s="576"/>
@@ -51728,7 +50735,7 @@
         <v>677</v>
       </c>
       <c r="B40" s="194" t="s">
-        <v>2568</v>
+        <v>2581</v>
       </c>
       <c r="C40" s="126" t="s">
         <v>535</v>
@@ -51737,7 +50744,7 @@
         <v>100</v>
       </c>
       <c r="E40" s="197" t="s">
-        <v>2569</v>
+        <v>2582</v>
       </c>
       <c r="F40" s="197" t="s">
         <v>1552</v>
@@ -51753,7 +50760,7 @@
         <v>51</v>
       </c>
       <c r="K40" s="201" t="s">
-        <v>2570</v>
+        <v>2583</v>
       </c>
       <c r="L40" s="224" t="s">
         <v>1101</v>
@@ -51762,7 +50769,7 @@
         <v>156</v>
       </c>
       <c r="N40" s="122" t="s">
-        <v>2571</v>
+        <v>2584</v>
       </c>
       <c r="O40" s="122"/>
       <c r="P40" s="576"/>
@@ -51772,7 +50779,7 @@
         <v>678</v>
       </c>
       <c r="B41" s="194" t="s">
-        <v>2572</v>
+        <v>2585</v>
       </c>
       <c r="C41" s="890" t="s">
         <v>141</v>
@@ -51781,7 +50788,7 @@
         <v>468</v>
       </c>
       <c r="E41" s="197" t="s">
-        <v>2573</v>
+        <v>2586</v>
       </c>
       <c r="F41" s="197" t="s">
         <v>1140</v>
@@ -51806,7 +50813,7 @@
         <v>156</v>
       </c>
       <c r="N41" s="122" t="s">
-        <v>2574</v>
+        <v>2587</v>
       </c>
       <c r="O41" s="122"/>
       <c r="P41" s="576"/>
@@ -51816,7 +50823,7 @@
         <v>679</v>
       </c>
       <c r="B42" s="237" t="s">
-        <v>2575</v>
+        <v>2588</v>
       </c>
       <c r="C42" s="102" t="s">
         <v>468</v>
@@ -51825,7 +50832,7 @@
         <v>535</v>
       </c>
       <c r="E42" s="240" t="s">
-        <v>2576</v>
+        <v>2589</v>
       </c>
       <c r="F42" s="240" t="s">
         <v>1140</v>
@@ -51850,7 +50857,7 @@
         <v>156</v>
       </c>
       <c r="N42" s="896" t="s">
-        <v>2577</v>
+        <v>2590</v>
       </c>
       <c r="O42" s="896"/>
       <c r="P42" s="585"/>
@@ -51860,7 +50867,7 @@
         <v>680</v>
       </c>
       <c r="B43" s="194" t="s">
-        <v>2578</v>
+        <v>2591</v>
       </c>
       <c r="C43" s="133" t="s">
         <v>78</v>
@@ -51869,7 +50876,7 @@
         <v>440</v>
       </c>
       <c r="E43" s="197" t="s">
-        <v>2579</v>
+        <v>2592</v>
       </c>
       <c r="F43" s="197" t="s">
         <v>455</v>
@@ -51899,7 +50906,7 @@
         <v>347</v>
       </c>
       <c r="O43" s="122" t="s">
-        <v>2580</v>
+        <v>2593</v>
       </c>
       <c r="P43" s="576"/>
     </row>
@@ -51908,7 +50915,7 @@
         <v>681</v>
       </c>
       <c r="B44" s="194" t="s">
-        <v>2581</v>
+        <v>2594</v>
       </c>
       <c r="C44" s="34" t="s">
         <v>418</v>
@@ -51917,7 +50924,7 @@
         <v>411</v>
       </c>
       <c r="E44" s="197" t="s">
-        <v>2582</v>
+        <v>2595</v>
       </c>
       <c r="F44" s="197" t="s">
         <v>424</v>
@@ -51952,7 +50959,7 @@
         <v>682</v>
       </c>
       <c r="B45" s="194" t="s">
-        <v>2583</v>
+        <v>2596</v>
       </c>
       <c r="C45" s="890" t="s">
         <v>141</v>
@@ -51961,10 +50968,10 @@
         <v>612</v>
       </c>
       <c r="E45" s="197" t="s">
-        <v>2584</v>
+        <v>2597</v>
       </c>
       <c r="F45" s="197" t="s">
-        <v>2585</v>
+        <v>2598</v>
       </c>
       <c r="G45" s="198" t="s">
         <v>305</v>
@@ -51986,7 +50993,7 @@
         <v>40</v>
       </c>
       <c r="N45" s="122" t="s">
-        <v>2586</v>
+        <v>2599</v>
       </c>
       <c r="O45" s="122"/>
       <c r="P45" s="576"/>
@@ -51996,7 +51003,7 @@
         <v>683</v>
       </c>
       <c r="B46" s="194" t="s">
-        <v>2587</v>
+        <v>2600</v>
       </c>
       <c r="C46" s="890" t="s">
         <v>141</v>
@@ -52005,10 +51012,10 @@
         <v>44</v>
       </c>
       <c r="E46" s="197" t="s">
-        <v>2588</v>
+        <v>2601</v>
       </c>
       <c r="F46" s="197" t="s">
-        <v>2585</v>
+        <v>2598</v>
       </c>
       <c r="G46" s="198" t="s">
         <v>305</v>
@@ -52030,7 +51037,7 @@
         <v>156</v>
       </c>
       <c r="N46" s="122" t="s">
-        <v>2586</v>
+        <v>2599</v>
       </c>
       <c r="O46" s="122"/>
       <c r="P46" s="576"/>
@@ -52040,7 +51047,7 @@
         <v>684</v>
       </c>
       <c r="B47" s="194" t="s">
-        <v>2589</v>
+        <v>2602</v>
       </c>
       <c r="C47" s="890" t="s">
         <v>141</v>
@@ -52049,10 +51056,10 @@
         <v>100</v>
       </c>
       <c r="E47" s="197" t="s">
-        <v>2590</v>
+        <v>2603</v>
       </c>
       <c r="F47" s="197" t="s">
-        <v>2585</v>
+        <v>2598</v>
       </c>
       <c r="G47" s="198" t="s">
         <v>305</v>
@@ -52074,7 +51081,7 @@
         <v>156</v>
       </c>
       <c r="N47" s="122" t="s">
-        <v>2586</v>
+        <v>2599</v>
       </c>
       <c r="O47" s="122"/>
       <c r="P47" s="576"/>
@@ -52084,7 +51091,7 @@
         <v>685</v>
       </c>
       <c r="B48" s="194" t="s">
-        <v>2591</v>
+        <v>2604</v>
       </c>
       <c r="C48" s="59" t="s">
         <v>44</v>
@@ -52093,7 +51100,7 @@
         <v>158</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>2592</v>
+        <v>2605</v>
       </c>
       <c r="F48" s="23" t="s">
         <v>1363</v>
@@ -52116,7 +51123,7 @@
         <v>156</v>
       </c>
       <c r="N48" s="122" t="s">
-        <v>2593</v>
+        <v>2606</v>
       </c>
       <c r="O48" s="122"/>
       <c r="P48" s="576"/>
@@ -52126,7 +51133,7 @@
         <v>686</v>
       </c>
       <c r="B49" s="194" t="s">
-        <v>2594</v>
+        <v>2607</v>
       </c>
       <c r="C49" s="737" t="s">
         <v>158</v>
@@ -52135,7 +51142,7 @@
         <v>418</v>
       </c>
       <c r="E49" s="194" t="s">
-        <v>2595</v>
+        <v>2608</v>
       </c>
       <c r="F49" s="197" t="s">
         <v>656</v>
@@ -52160,7 +51167,7 @@
         <v>156</v>
       </c>
       <c r="N49" s="122" t="s">
-        <v>2596</v>
+        <v>2609</v>
       </c>
       <c r="O49" s="122"/>
       <c r="P49" s="576"/>
@@ -52170,7 +51177,7 @@
         <v>687</v>
       </c>
       <c r="B50" s="194" t="s">
-        <v>2597</v>
+        <v>2610</v>
       </c>
       <c r="C50" s="737" t="s">
         <v>158</v>
@@ -52179,7 +51186,7 @@
         <v>441</v>
       </c>
       <c r="E50" s="197" t="s">
-        <v>2598</v>
+        <v>2611</v>
       </c>
       <c r="F50" s="197" t="s">
         <v>443</v>
@@ -52210,7 +51217,7 @@
         <v>688</v>
       </c>
       <c r="B51" s="194" t="s">
-        <v>2599</v>
+        <v>2612</v>
       </c>
       <c r="C51" s="737" t="s">
         <v>158</v>
@@ -52219,7 +51226,7 @@
         <v>441</v>
       </c>
       <c r="E51" s="197" t="s">
-        <v>2600</v>
+        <v>2613</v>
       </c>
       <c r="F51" s="197" t="s">
         <v>1032</v>
@@ -52244,7 +51251,7 @@
         <v>156</v>
       </c>
       <c r="N51" s="122" t="s">
-        <v>2601</v>
+        <v>2614</v>
       </c>
       <c r="O51" s="122"/>
       <c r="P51" s="576"/>
@@ -52254,7 +51261,7 @@
         <v>707</v>
       </c>
       <c r="B52" s="194" t="s">
-        <v>2602</v>
+        <v>2615</v>
       </c>
       <c r="C52" s="737" t="s">
         <v>158</v>
@@ -52263,7 +51270,7 @@
         <v>44</v>
       </c>
       <c r="E52" s="197" t="s">
-        <v>2603</v>
+        <v>2616</v>
       </c>
       <c r="F52" s="197" t="s">
         <v>2171</v>
@@ -52286,7 +51293,7 @@
         <v>156</v>
       </c>
       <c r="N52" s="122" t="s">
-        <v>2604</v>
+        <v>2617</v>
       </c>
       <c r="O52" s="122"/>
       <c r="P52" s="576"/>
@@ -52296,14 +51303,14 @@
         <v>708</v>
       </c>
       <c r="B53" s="194" t="s">
-        <v>2605</v>
+        <v>2618</v>
       </c>
       <c r="C53" s="111" t="s">
         <v>570</v>
       </c>
       <c r="D53" s="504"/>
       <c r="E53" s="197" t="s">
-        <v>2606</v>
+        <v>2619</v>
       </c>
       <c r="F53" s="197" t="s">
         <v>699</v>
@@ -52317,7 +51324,7 @@
         <v>237</v>
       </c>
       <c r="K53" s="201" t="s">
-        <v>2429</v>
+        <v>2435</v>
       </c>
       <c r="L53" s="224" t="s">
         <v>1081</v>
@@ -52326,7 +51333,7 @@
         <v>156</v>
       </c>
       <c r="N53" s="122" t="s">
-        <v>2607</v>
+        <v>2620</v>
       </c>
       <c r="O53" s="122"/>
       <c r="P53" s="576"/>
@@ -52336,7 +51343,7 @@
         <v>709</v>
       </c>
       <c r="B54" s="194" t="s">
-        <v>2608</v>
+        <v>2621</v>
       </c>
       <c r="C54" s="890" t="s">
         <v>141</v>
@@ -52345,14 +51352,14 @@
         <v>100</v>
       </c>
       <c r="E54" s="197" t="s">
-        <v>2609</v>
+        <v>2622</v>
       </c>
       <c r="F54" s="197" t="s">
         <v>734</v>
       </c>
       <c r="G54" s="198"/>
       <c r="H54" s="198" t="s">
-        <v>2610</v>
+        <v>2623</v>
       </c>
       <c r="I54" s="199" t="n">
         <v>1.7</v>
@@ -52370,7 +51377,7 @@
         <v>156</v>
       </c>
       <c r="N54" s="122" t="s">
-        <v>2611</v>
+        <v>2624</v>
       </c>
       <c r="O54" s="122"/>
       <c r="P54" s="576"/>
@@ -52380,7 +51387,7 @@
         <v>710</v>
       </c>
       <c r="B55" s="194" t="s">
-        <v>2612</v>
+        <v>2625</v>
       </c>
       <c r="C55" s="737" t="s">
         <v>158</v>
@@ -52389,10 +51396,10 @@
         <v>440</v>
       </c>
       <c r="E55" s="197" t="s">
-        <v>2613</v>
+        <v>2626</v>
       </c>
       <c r="F55" s="198" t="s">
-        <v>2610</v>
+        <v>2623</v>
       </c>
       <c r="G55" s="198"/>
       <c r="H55" s="198" t="s">
@@ -52405,7 +51412,7 @@
         <v>430</v>
       </c>
       <c r="K55" s="201" t="s">
-        <v>2429</v>
+        <v>2435</v>
       </c>
       <c r="L55" s="224" t="s">
         <v>1101</v>
@@ -52414,7 +51421,7 @@
         <v>156</v>
       </c>
       <c r="N55" s="897" t="s">
-        <v>2614</v>
+        <v>2627</v>
       </c>
       <c r="O55" s="122"/>
       <c r="P55" s="576"/>
@@ -52424,7 +51431,7 @@
         <v>711</v>
       </c>
       <c r="B56" s="194" t="s">
-        <v>2615</v>
+        <v>2628</v>
       </c>
       <c r="C56" s="652" t="s">
         <v>411</v>
@@ -52433,7 +51440,7 @@
         <v>514</v>
       </c>
       <c r="E56" s="197" t="s">
-        <v>2616</v>
+        <v>2629</v>
       </c>
       <c r="F56" s="197" t="s">
         <v>992</v>
@@ -52458,7 +51465,7 @@
         <v>156</v>
       </c>
       <c r="N56" s="122" t="s">
-        <v>2617</v>
+        <v>2630</v>
       </c>
       <c r="O56" s="122"/>
       <c r="P56" s="576"/>
@@ -52468,7 +51475,7 @@
         <v>712</v>
       </c>
       <c r="B57" s="194" t="s">
-        <v>2618</v>
+        <v>2631</v>
       </c>
       <c r="C57" s="890" t="s">
         <v>141</v>
@@ -52477,7 +51484,7 @@
         <v>468</v>
       </c>
       <c r="E57" s="197" t="s">
-        <v>2619</v>
+        <v>2632</v>
       </c>
       <c r="F57" s="197" t="s">
         <v>1140</v>
@@ -52502,7 +51509,7 @@
         <v>156</v>
       </c>
       <c r="N57" s="122" t="s">
-        <v>2620</v>
+        <v>2633</v>
       </c>
       <c r="O57" s="122"/>
       <c r="P57" s="576"/>
@@ -52512,7 +51519,7 @@
         <v>713</v>
       </c>
       <c r="B58" s="194" t="s">
-        <v>2621</v>
+        <v>2634</v>
       </c>
       <c r="C58" s="111" t="s">
         <v>570</v>
@@ -52521,7 +51528,7 @@
         <v>487</v>
       </c>
       <c r="E58" s="197" t="s">
-        <v>2622</v>
+        <v>2635</v>
       </c>
       <c r="F58" s="197" t="s">
         <v>676</v>
@@ -52535,7 +51542,7 @@
         <v>25</v>
       </c>
       <c r="K58" s="201" t="s">
-        <v>2429</v>
+        <v>2435</v>
       </c>
       <c r="L58" s="875" t="s">
         <v>1081</v>
@@ -52544,7 +51551,7 @@
         <v>156</v>
       </c>
       <c r="N58" s="122" t="s">
-        <v>2623</v>
+        <v>2636</v>
       </c>
       <c r="O58" s="122"/>
       <c r="P58" s="576"/>
@@ -52554,7 +51561,7 @@
         <v>714</v>
       </c>
       <c r="B59" s="194" t="s">
-        <v>2624</v>
+        <v>2637</v>
       </c>
       <c r="C59" s="111" t="s">
         <v>570</v>
@@ -52569,7 +51576,7 @@
       <c r="I59" s="199"/>
       <c r="J59" s="200"/>
       <c r="K59" s="201" t="s">
-        <v>2429</v>
+        <v>2435</v>
       </c>
       <c r="L59" s="875" t="s">
         <v>1081</v>
@@ -52578,7 +51585,7 @@
         <v>30</v>
       </c>
       <c r="N59" s="122" t="s">
-        <v>2623</v>
+        <v>2636</v>
       </c>
       <c r="O59" s="122"/>
       <c r="P59" s="576"/>
@@ -52588,7 +51595,7 @@
         <v>715</v>
       </c>
       <c r="B60" s="194" t="s">
-        <v>2625</v>
+        <v>2638</v>
       </c>
       <c r="C60" s="133" t="s">
         <v>78</v>
@@ -52597,7 +51604,7 @@
         <v>406</v>
       </c>
       <c r="E60" s="197" t="s">
-        <v>2626</v>
+        <v>2639</v>
       </c>
       <c r="F60" s="197" t="s">
         <v>979</v>
@@ -52606,7 +51613,7 @@
         <v>408</v>
       </c>
       <c r="H60" s="198" t="s">
-        <v>2627</v>
+        <v>2640</v>
       </c>
       <c r="I60" s="199" t="n">
         <v>0.1</v>
@@ -52624,7 +51631,7 @@
         <v>156</v>
       </c>
       <c r="N60" s="122" t="s">
-        <v>2628</v>
+        <v>2641</v>
       </c>
       <c r="O60" s="122"/>
       <c r="P60" s="576"/>
@@ -52634,7 +51641,7 @@
         <v>716</v>
       </c>
       <c r="B61" s="194" t="s">
-        <v>2629</v>
+        <v>2642</v>
       </c>
       <c r="C61" s="133" t="s">
         <v>78</v>
@@ -52643,7 +51650,7 @@
         <v>406</v>
       </c>
       <c r="E61" s="197" t="s">
-        <v>2630</v>
+        <v>2643</v>
       </c>
       <c r="F61" s="197" t="s">
         <v>979</v>
@@ -52652,7 +51659,7 @@
         <v>408</v>
       </c>
       <c r="H61" s="198" t="s">
-        <v>2627</v>
+        <v>2640</v>
       </c>
       <c r="I61" s="199" t="n">
         <v>0.8</v>
@@ -52670,7 +51677,7 @@
         <v>20</v>
       </c>
       <c r="N61" s="122" t="s">
-        <v>2628</v>
+        <v>2641</v>
       </c>
       <c r="O61" s="122"/>
       <c r="P61" s="576"/>
@@ -52680,7 +51687,7 @@
         <v>717</v>
       </c>
       <c r="B62" s="194" t="s">
-        <v>2631</v>
+        <v>2644</v>
       </c>
       <c r="C62" s="46" t="s">
         <v>440</v>
@@ -52689,7 +51696,7 @@
         <v>418</v>
       </c>
       <c r="E62" s="197" t="s">
-        <v>2632</v>
+        <v>2645</v>
       </c>
       <c r="F62" s="197" t="s">
         <v>1000</v>
@@ -52712,10 +51719,10 @@
         <v>156</v>
       </c>
       <c r="N62" s="122" t="s">
-        <v>2633</v>
+        <v>2646</v>
       </c>
       <c r="O62" s="122" t="s">
-        <v>2634</v>
+        <v>2647</v>
       </c>
       <c r="P62" s="576"/>
     </row>
@@ -52724,7 +51731,7 @@
         <v>718</v>
       </c>
       <c r="B63" s="194" t="s">
-        <v>2635</v>
+        <v>2648</v>
       </c>
       <c r="C63" s="34" t="s">
         <v>418</v>
@@ -52733,7 +51740,7 @@
         <v>141</v>
       </c>
       <c r="E63" s="197" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="F63" s="197" t="s">
         <v>2029</v>
@@ -52758,7 +51765,7 @@
         <v>156</v>
       </c>
       <c r="N63" s="122" t="s">
-        <v>2637</v>
+        <v>2650</v>
       </c>
       <c r="O63" s="899"/>
       <c r="P63" s="593"/>
@@ -52768,7 +51775,7 @@
         <v>719</v>
       </c>
       <c r="B64" s="194" t="s">
-        <v>2638</v>
+        <v>2651</v>
       </c>
       <c r="C64" s="34" t="s">
         <v>418</v>
@@ -52777,7 +51784,7 @@
         <v>100</v>
       </c>
       <c r="E64" s="197" t="s">
-        <v>2639</v>
+        <v>2652</v>
       </c>
       <c r="F64" s="197" t="s">
         <v>1303</v>
@@ -52802,7 +51809,7 @@
         <v>156</v>
       </c>
       <c r="N64" s="122" t="s">
-        <v>2640</v>
+        <v>2653</v>
       </c>
       <c r="O64" s="122"/>
       <c r="P64" s="576"/>
@@ -52812,7 +51819,7 @@
         <v>720</v>
       </c>
       <c r="B65" s="194" t="s">
-        <v>2641</v>
+        <v>2654</v>
       </c>
       <c r="C65" s="737" t="s">
         <v>158</v>
@@ -52821,7 +51828,7 @@
         <v>514</v>
       </c>
       <c r="E65" s="197" t="s">
-        <v>2642</v>
+        <v>2655</v>
       </c>
       <c r="F65" s="197" t="s">
         <v>537</v>
@@ -52844,10 +51851,10 @@
         <v>156</v>
       </c>
       <c r="N65" s="122" t="s">
-        <v>2643</v>
+        <v>2656</v>
       </c>
       <c r="O65" s="122" t="s">
-        <v>2479</v>
+        <v>2493</v>
       </c>
       <c r="P65" s="576"/>
     </row>
@@ -52856,7 +51863,7 @@
         <v>721</v>
       </c>
       <c r="B66" s="194" t="s">
-        <v>2644</v>
+        <v>2657</v>
       </c>
       <c r="C66" s="126" t="s">
         <v>535</v>
@@ -52865,7 +51872,7 @@
         <v>44</v>
       </c>
       <c r="E66" s="197" t="s">
-        <v>2645</v>
+        <v>2658</v>
       </c>
       <c r="F66" s="197" t="s">
         <v>537</v>
@@ -52888,7 +51895,7 @@
         <v>156</v>
       </c>
       <c r="N66" s="122" t="s">
-        <v>2646</v>
+        <v>2659</v>
       </c>
       <c r="O66" s="122"/>
       <c r="P66" s="576"/>
@@ -52898,7 +51905,7 @@
         <v>722</v>
       </c>
       <c r="B67" s="194" t="s">
-        <v>2647</v>
+        <v>2660</v>
       </c>
       <c r="C67" s="171" t="s">
         <v>100</v>
@@ -52907,7 +51914,7 @@
         <v>514</v>
       </c>
       <c r="E67" s="197" t="s">
-        <v>2648</v>
+        <v>2661</v>
       </c>
       <c r="F67" s="197" t="s">
         <v>1270</v>
@@ -52930,7 +51937,7 @@
         <v>156</v>
       </c>
       <c r="N67" s="122" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="O67" s="122"/>
       <c r="P67" s="576"/>
@@ -52940,7 +51947,7 @@
         <v>723</v>
       </c>
       <c r="B68" s="194" t="s">
-        <v>2650</v>
+        <v>2663</v>
       </c>
       <c r="C68" s="171" t="s">
         <v>100</v>
@@ -52972,7 +51979,7 @@
         <v>156</v>
       </c>
       <c r="N68" s="122" t="s">
-        <v>2651</v>
+        <v>2664</v>
       </c>
       <c r="O68" s="122" t="s">
         <v>595</v>
@@ -52984,14 +51991,14 @@
         <v>724</v>
       </c>
       <c r="B69" s="194" t="s">
-        <v>2652</v>
+        <v>2665</v>
       </c>
       <c r="C69" s="133" t="s">
         <v>78</v>
       </c>
       <c r="D69" s="385"/>
       <c r="E69" s="197" t="s">
-        <v>2653</v>
+        <v>2666</v>
       </c>
       <c r="F69" s="197" t="s">
         <v>676</v>
@@ -53016,10 +52023,10 @@
         <v>156</v>
       </c>
       <c r="N69" s="122" t="s">
-        <v>2654</v>
+        <v>2667</v>
       </c>
       <c r="O69" s="122" t="s">
-        <v>2655</v>
+        <v>2668</v>
       </c>
       <c r="P69" s="576"/>
     </row>
@@ -53028,7 +52035,7 @@
         <v>725</v>
       </c>
       <c r="B70" s="194" t="s">
-        <v>2656</v>
+        <v>2669</v>
       </c>
       <c r="C70" s="652" t="s">
         <v>411</v>
@@ -53037,14 +52044,14 @@
         <v>44</v>
       </c>
       <c r="E70" s="197" t="s">
-        <v>2657</v>
+        <v>2670</v>
       </c>
       <c r="F70" s="197" t="s">
         <v>413</v>
       </c>
       <c r="G70" s="198"/>
       <c r="H70" s="198" t="s">
-        <v>2658</v>
+        <v>2671</v>
       </c>
       <c r="I70" s="199" t="n">
         <v>0.9</v>
@@ -53062,7 +52069,7 @@
         <v>156</v>
       </c>
       <c r="N70" s="122" t="s">
-        <v>2659</v>
+        <v>2672</v>
       </c>
       <c r="O70" s="122"/>
       <c r="P70" s="576"/>
@@ -53072,7 +52079,7 @@
         <v>726</v>
       </c>
       <c r="B71" s="194" t="s">
-        <v>2660</v>
+        <v>2673</v>
       </c>
       <c r="C71" s="737" t="s">
         <v>158</v>
@@ -53081,7 +52088,7 @@
         <v>514</v>
       </c>
       <c r="E71" s="197" t="s">
-        <v>2661</v>
+        <v>2674</v>
       </c>
       <c r="F71" s="197" t="s">
         <v>516</v>
@@ -53106,10 +52113,10 @@
         <v>156</v>
       </c>
       <c r="N71" s="122" t="s">
-        <v>2662</v>
+        <v>2675</v>
       </c>
       <c r="O71" s="122" t="s">
-        <v>2541</v>
+        <v>2555</v>
       </c>
       <c r="P71" s="576"/>
     </row>
@@ -53118,7 +52125,7 @@
         <v>727</v>
       </c>
       <c r="B72" s="194" t="s">
-        <v>2663</v>
+        <v>2676</v>
       </c>
       <c r="C72" s="115" t="s">
         <v>514</v>
@@ -53127,7 +52134,7 @@
         <v>44</v>
       </c>
       <c r="E72" s="197" t="s">
-        <v>2664</v>
+        <v>2677</v>
       </c>
       <c r="F72" s="197" t="s">
         <v>435</v>
@@ -53152,7 +52159,7 @@
         <v>156</v>
       </c>
       <c r="N72" s="122" t="s">
-        <v>2665</v>
+        <v>2678</v>
       </c>
       <c r="O72" s="122"/>
       <c r="P72" s="576"/>
@@ -53162,7 +52169,7 @@
         <v>728</v>
       </c>
       <c r="B73" s="194" t="s">
-        <v>2666</v>
+        <v>2679</v>
       </c>
       <c r="C73" s="18" t="s">
         <v>406</v>
@@ -53171,7 +52178,7 @@
         <v>514</v>
       </c>
       <c r="E73" s="197" t="s">
-        <v>2667</v>
+        <v>2680</v>
       </c>
       <c r="F73" s="197" t="s">
         <v>765</v>
@@ -53196,7 +52203,7 @@
         <v>156</v>
       </c>
       <c r="N73" s="122" t="s">
-        <v>2668</v>
+        <v>2681</v>
       </c>
       <c r="O73" s="122"/>
       <c r="P73" s="576"/>
@@ -53206,7 +52213,7 @@
         <v>729</v>
       </c>
       <c r="B74" s="194" t="s">
-        <v>2669</v>
+        <v>2682</v>
       </c>
       <c r="C74" s="34" t="s">
         <v>418</v>
@@ -53215,7 +52222,7 @@
         <v>100</v>
       </c>
       <c r="E74" s="197" t="s">
-        <v>2670</v>
+        <v>2683</v>
       </c>
       <c r="F74" s="197" t="s">
         <v>656</v>
@@ -53240,7 +52247,7 @@
         <v>156</v>
       </c>
       <c r="N74" s="122" t="s">
-        <v>2671</v>
+        <v>2684</v>
       </c>
       <c r="O74" s="122"/>
       <c r="P74" s="576"/>
@@ -53250,7 +52257,7 @@
         <v>730</v>
       </c>
       <c r="B75" s="194" t="s">
-        <v>2672</v>
+        <v>2685</v>
       </c>
       <c r="C75" s="890" t="s">
         <v>141</v>
@@ -53259,7 +52266,7 @@
         <v>441</v>
       </c>
       <c r="E75" s="197" t="s">
-        <v>2673</v>
+        <v>2686</v>
       </c>
       <c r="F75" s="197" t="s">
         <v>910</v>
@@ -53282,10 +52289,10 @@
         <v>156</v>
       </c>
       <c r="N75" s="122" t="s">
-        <v>2674</v>
+        <v>2687</v>
       </c>
       <c r="O75" s="122" t="s">
-        <v>2675</v>
+        <v>2688</v>
       </c>
       <c r="P75" s="576"/>
     </row>
@@ -53294,7 +52301,7 @@
         <v>731</v>
       </c>
       <c r="B76" s="194" t="s">
-        <v>2676</v>
+        <v>2689</v>
       </c>
       <c r="C76" s="34" t="s">
         <v>418</v>
@@ -53303,7 +52310,7 @@
         <v>570</v>
       </c>
       <c r="E76" s="197" t="s">
-        <v>2677</v>
+        <v>2690</v>
       </c>
       <c r="F76" s="197" t="s">
         <v>656</v>
@@ -53319,7 +52326,7 @@
         <v>200</v>
       </c>
       <c r="K76" s="201" t="s">
-        <v>2429</v>
+        <v>2435</v>
       </c>
       <c r="L76" s="224" t="s">
         <v>1081</v>
@@ -53328,7 +52335,7 @@
         <v>156</v>
       </c>
       <c r="N76" s="122" t="s">
-        <v>2678</v>
+        <v>2691</v>
       </c>
       <c r="O76" s="122"/>
       <c r="P76" s="576"/>
@@ -53338,7 +52345,7 @@
         <v>732</v>
       </c>
       <c r="B77" s="194" t="s">
-        <v>2679</v>
+        <v>2692</v>
       </c>
       <c r="C77" s="115" t="s">
         <v>514</v>
@@ -53347,7 +52354,7 @@
         <v>141</v>
       </c>
       <c r="E77" s="197" t="s">
-        <v>2680</v>
+        <v>2693</v>
       </c>
       <c r="F77" s="197" t="s">
         <v>1270</v>
@@ -53372,7 +52379,7 @@
         <v>156</v>
       </c>
       <c r="N77" s="122" t="s">
-        <v>2675</v>
+        <v>2688</v>
       </c>
       <c r="O77" s="122"/>
       <c r="P77" s="576"/>
@@ -53382,7 +52389,7 @@
         <v>733</v>
       </c>
       <c r="B78" s="194" t="s">
-        <v>2681</v>
+        <v>2694</v>
       </c>
       <c r="C78" s="115" t="s">
         <v>514</v>
@@ -53391,7 +52398,7 @@
         <v>464</v>
       </c>
       <c r="E78" s="197" t="s">
-        <v>2682</v>
+        <v>2695</v>
       </c>
       <c r="F78" s="197" t="s">
         <v>1270</v>
@@ -53426,7 +52433,7 @@
         <v>734</v>
       </c>
       <c r="B79" s="194" t="s">
-        <v>2683</v>
+        <v>2696</v>
       </c>
       <c r="C79" s="115" t="s">
         <v>514</v>
@@ -53435,7 +52442,7 @@
         <v>158</v>
       </c>
       <c r="E79" s="197" t="s">
-        <v>2684</v>
+        <v>2697</v>
       </c>
       <c r="F79" s="197" t="s">
         <v>1270</v>
@@ -53470,7 +52477,7 @@
         <v>735</v>
       </c>
       <c r="B80" s="194" t="s">
-        <v>2685</v>
+        <v>2698</v>
       </c>
       <c r="C80" s="102" t="s">
         <v>468</v>
@@ -53479,7 +52486,7 @@
         <v>100</v>
       </c>
       <c r="E80" s="197" t="s">
-        <v>2686</v>
+        <v>2699</v>
       </c>
       <c r="F80" s="197" t="s">
         <v>470</v>
@@ -53504,7 +52511,7 @@
         <v>60</v>
       </c>
       <c r="N80" s="122" t="s">
-        <v>2687</v>
+        <v>2700</v>
       </c>
       <c r="O80" s="122"/>
       <c r="P80" s="576"/>
@@ -53514,7 +52521,7 @@
         <v>736</v>
       </c>
       <c r="B81" s="194" t="s">
-        <v>2688</v>
+        <v>2701</v>
       </c>
       <c r="C81" s="102" t="s">
         <v>468</v>
@@ -53523,7 +52530,7 @@
         <v>100</v>
       </c>
       <c r="E81" s="197" t="s">
-        <v>2686</v>
+        <v>2699</v>
       </c>
       <c r="F81" s="197" t="s">
         <v>470</v>
@@ -53548,7 +52555,7 @@
         <v>156</v>
       </c>
       <c r="N81" s="122" t="s">
-        <v>2687</v>
+        <v>2700</v>
       </c>
       <c r="O81" s="122"/>
       <c r="P81" s="576"/>
@@ -53558,7 +52565,7 @@
         <v>737</v>
       </c>
       <c r="B82" s="194" t="s">
-        <v>2689</v>
+        <v>2702</v>
       </c>
       <c r="C82" s="18" t="s">
         <v>406</v>
@@ -53567,7 +52574,7 @@
         <v>514</v>
       </c>
       <c r="E82" s="197" t="s">
-        <v>2690</v>
+        <v>2703</v>
       </c>
       <c r="F82" s="197" t="s">
         <v>765</v>
@@ -53592,7 +52599,7 @@
         <v>156</v>
       </c>
       <c r="N82" s="122" t="s">
-        <v>2691</v>
+        <v>2704</v>
       </c>
       <c r="O82" s="122"/>
       <c r="P82" s="576"/>
@@ -53602,17 +52609,17 @@
         <v>738</v>
       </c>
       <c r="B83" s="194" t="s">
-        <v>2692</v>
+        <v>2705</v>
       </c>
       <c r="C83" s="133" t="s">
         <v>78</v>
       </c>
       <c r="D83" s="385"/>
       <c r="E83" s="197" t="s">
-        <v>2693</v>
+        <v>2706</v>
       </c>
       <c r="F83" s="197" t="s">
-        <v>2694</v>
+        <v>2707</v>
       </c>
       <c r="G83" s="198"/>
       <c r="H83" s="198"/>
@@ -53632,7 +52639,7 @@
         <v>156</v>
       </c>
       <c r="N83" s="122" t="s">
-        <v>2695</v>
+        <v>2708</v>
       </c>
       <c r="O83" s="122"/>
       <c r="P83" s="576"/>
@@ -53642,7 +52649,7 @@
         <v>739</v>
       </c>
       <c r="B84" s="396" t="s">
-        <v>2696</v>
+        <v>2709</v>
       </c>
       <c r="C84" s="737" t="s">
         <v>158</v>
@@ -53651,7 +52658,7 @@
         <v>78</v>
       </c>
       <c r="E84" s="197" t="s">
-        <v>2697</v>
+        <v>2710</v>
       </c>
       <c r="F84" s="197" t="s">
         <v>834</v>
@@ -53674,7 +52681,7 @@
         <v>156</v>
       </c>
       <c r="N84" s="122" t="s">
-        <v>2698</v>
+        <v>2711</v>
       </c>
       <c r="O84" s="122"/>
       <c r="P84" s="576"/>
@@ -53684,7 +52691,7 @@
         <v>740</v>
       </c>
       <c r="B85" s="194" t="s">
-        <v>2699</v>
+        <v>2712</v>
       </c>
       <c r="C85" s="737" t="s">
         <v>158</v>
@@ -53693,7 +52700,7 @@
         <v>100</v>
       </c>
       <c r="E85" s="197" t="s">
-        <v>2700</v>
+        <v>2713</v>
       </c>
       <c r="F85" s="197" t="s">
         <v>975</v>
@@ -53718,7 +52725,7 @@
         <v>156</v>
       </c>
       <c r="N85" s="122" t="s">
-        <v>2701</v>
+        <v>2714</v>
       </c>
       <c r="O85" s="122"/>
       <c r="P85" s="576"/>
@@ -53728,20 +52735,20 @@
         <v>741</v>
       </c>
       <c r="B86" s="194" t="s">
-        <v>2702</v>
+        <v>2715</v>
       </c>
       <c r="C86" s="133" t="s">
         <v>78</v>
       </c>
       <c r="D86" s="385"/>
       <c r="E86" s="197" t="s">
-        <v>2703</v>
+        <v>2716</v>
       </c>
       <c r="F86" s="197" t="s">
         <v>676</v>
       </c>
       <c r="G86" s="198" t="s">
-        <v>2694</v>
+        <v>2707</v>
       </c>
       <c r="H86" s="198"/>
       <c r="I86" s="199" t="n">
@@ -53757,10 +52764,10 @@
         <v>1081</v>
       </c>
       <c r="M86" s="752" t="s">
-        <v>2704</v>
+        <v>2717</v>
       </c>
       <c r="N86" s="122" t="s">
-        <v>2705</v>
+        <v>2718</v>
       </c>
       <c r="O86" s="122"/>
       <c r="P86" s="576"/>
@@ -53770,7 +52777,7 @@
         <v>742</v>
       </c>
       <c r="B87" s="194" t="s">
-        <v>2706</v>
+        <v>2719</v>
       </c>
       <c r="C87" s="34" t="s">
         <v>418</v>
@@ -53779,7 +52786,7 @@
         <v>535</v>
       </c>
       <c r="E87" s="197" t="s">
-        <v>2707</v>
+        <v>2720</v>
       </c>
       <c r="F87" s="197" t="s">
         <v>656</v>
@@ -53804,7 +52811,7 @@
         <v>156</v>
       </c>
       <c r="N87" s="122" t="s">
-        <v>2708</v>
+        <v>2721</v>
       </c>
       <c r="O87" s="122"/>
       <c r="P87" s="576"/>
@@ -53814,7 +52821,7 @@
         <v>743</v>
       </c>
       <c r="B88" s="194" t="s">
-        <v>2709</v>
+        <v>2722</v>
       </c>
       <c r="C88" s="171" t="s">
         <v>100</v>
@@ -53823,13 +52830,13 @@
         <v>535</v>
       </c>
       <c r="E88" s="197" t="s">
-        <v>2710</v>
+        <v>2723</v>
       </c>
       <c r="F88" s="197" t="s">
         <v>1357</v>
       </c>
       <c r="G88" s="198" t="s">
-        <v>2711</v>
+        <v>2724</v>
       </c>
       <c r="H88" s="198"/>
       <c r="I88" s="199" t="n">
@@ -53848,7 +52855,7 @@
         <v>156</v>
       </c>
       <c r="N88" s="122" t="s">
-        <v>2712</v>
+        <v>2725</v>
       </c>
       <c r="O88" s="122"/>
       <c r="P88" s="576"/>
@@ -53858,7 +52865,7 @@
         <v>744</v>
       </c>
       <c r="B89" s="194" t="s">
-        <v>2713</v>
+        <v>2726</v>
       </c>
       <c r="C89" s="46" t="s">
         <v>440</v>
@@ -53867,10 +52874,10 @@
         <v>454</v>
       </c>
       <c r="E89" s="197" t="s">
-        <v>2714</v>
+        <v>2727</v>
       </c>
       <c r="F89" s="197" t="s">
-        <v>2585</v>
+        <v>2598</v>
       </c>
       <c r="G89" s="198"/>
       <c r="H89" s="198"/>
@@ -53890,7 +52897,7 @@
         <v>156</v>
       </c>
       <c r="N89" s="122" t="s">
-        <v>2715</v>
+        <v>2728</v>
       </c>
       <c r="O89" s="122"/>
       <c r="P89" s="576"/>
@@ -53900,7 +52907,7 @@
         <v>745</v>
       </c>
       <c r="B90" s="194" t="s">
-        <v>2716</v>
+        <v>2729</v>
       </c>
       <c r="C90" s="171" t="s">
         <v>100</v>
@@ -53909,14 +52916,14 @@
         <v>141</v>
       </c>
       <c r="E90" s="197" t="s">
-        <v>2717</v>
+        <v>2730</v>
       </c>
       <c r="F90" s="197" t="s">
         <v>1357</v>
       </c>
       <c r="G90" s="198"/>
       <c r="H90" s="198" t="s">
-        <v>2718</v>
+        <v>2731</v>
       </c>
       <c r="I90" s="199" t="n">
         <v>0.8</v>
@@ -53934,10 +52941,10 @@
         <v>156</v>
       </c>
       <c r="N90" s="122" t="s">
-        <v>2719</v>
+        <v>2732</v>
       </c>
       <c r="O90" s="122" t="s">
-        <v>2564</v>
+        <v>2577</v>
       </c>
       <c r="P90" s="576"/>
     </row>
@@ -53946,7 +52953,7 @@
         <v>746</v>
       </c>
       <c r="B91" s="194" t="s">
-        <v>2720</v>
+        <v>2733</v>
       </c>
       <c r="C91" s="115" t="s">
         <v>514</v>
@@ -53955,10 +52962,10 @@
         <v>100</v>
       </c>
       <c r="E91" s="197" t="s">
-        <v>2721</v>
+        <v>2734</v>
       </c>
       <c r="F91" s="197" t="s">
-        <v>2722</v>
+        <v>2735</v>
       </c>
       <c r="G91" s="198" t="s">
         <v>1357</v>
@@ -53982,418 +52989,1214 @@
         <v>156</v>
       </c>
       <c r="N91" s="122" t="s">
-        <v>2723</v>
+        <v>2736</v>
       </c>
       <c r="O91" s="122" t="s">
-        <v>2724</v>
+        <v>2737</v>
       </c>
       <c r="P91" s="576"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="867"/>
-      <c r="B92" s="213"/>
-      <c r="C92" s="900"/>
-      <c r="D92" s="901"/>
-      <c r="E92" s="216"/>
-      <c r="F92" s="216"/>
-      <c r="G92" s="217"/>
-      <c r="H92" s="217"/>
-      <c r="I92" s="218"/>
-      <c r="J92" s="219"/>
-      <c r="K92" s="220"/>
-      <c r="L92" s="875"/>
+      <c r="A92" s="867" t="n">
+        <v>747</v>
+      </c>
+      <c r="B92" s="213" t="s">
+        <v>2738</v>
+      </c>
+      <c r="C92" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="D92" s="34" t="s">
+        <v>418</v>
+      </c>
+      <c r="E92" s="216" t="s">
+        <v>2739</v>
+      </c>
+      <c r="F92" s="216" t="s">
+        <v>489</v>
+      </c>
+      <c r="G92" s="217" t="s">
+        <v>656</v>
+      </c>
+      <c r="H92" s="217" t="s">
+        <v>1391</v>
+      </c>
+      <c r="I92" s="218" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J92" s="219" t="n">
+        <v>30</v>
+      </c>
+      <c r="K92" s="220" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L92" s="875" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M92" s="752" t="s">
+        <v>156</v>
+      </c>
+      <c r="N92" s="888" t="s">
+        <v>2740</v>
+      </c>
+      <c r="O92" s="888" t="s">
+        <v>2741</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="867"/>
-      <c r="B93" s="194"/>
-      <c r="C93" s="792"/>
-      <c r="D93" s="727"/>
-      <c r="E93" s="197"/>
-      <c r="F93" s="197"/>
-      <c r="G93" s="198"/>
+      <c r="A93" s="867" t="n">
+        <v>748</v>
+      </c>
+      <c r="B93" s="194" t="s">
+        <v>2742</v>
+      </c>
+      <c r="C93" s="171" t="s">
+        <v>100</v>
+      </c>
+      <c r="D93" s="171"/>
+      <c r="E93" s="197" t="s">
+        <v>2743</v>
+      </c>
+      <c r="F93" s="197" t="s">
+        <v>750</v>
+      </c>
+      <c r="G93" s="198" t="s">
+        <v>646</v>
+      </c>
       <c r="H93" s="198"/>
-      <c r="I93" s="199"/>
-      <c r="J93" s="200"/>
-      <c r="K93" s="201"/>
-      <c r="L93" s="224"/>
+      <c r="I93" s="199" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J93" s="200" t="n">
+        <v>330</v>
+      </c>
+      <c r="K93" s="201" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L93" s="224" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M93" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N93" s="900" t="s">
+        <v>2744</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="867"/>
-      <c r="B94" s="194"/>
-      <c r="C94" s="792"/>
-      <c r="D94" s="727"/>
-      <c r="E94" s="197"/>
-      <c r="F94" s="197"/>
+      <c r="A94" s="867" t="n">
+        <v>749</v>
+      </c>
+      <c r="B94" s="194" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C94" s="330" t="s">
+        <v>44</v>
+      </c>
+      <c r="D94" s="388" t="s">
+        <v>141</v>
+      </c>
+      <c r="E94" s="197" t="s">
+        <v>2746</v>
+      </c>
+      <c r="F94" s="197" t="s">
+        <v>537</v>
+      </c>
       <c r="G94" s="198"/>
       <c r="H94" s="198"/>
-      <c r="I94" s="199"/>
-      <c r="J94" s="200"/>
-      <c r="K94" s="201"/>
-      <c r="L94" s="224"/>
+      <c r="I94" s="199" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J94" s="200" t="n">
+        <v>390</v>
+      </c>
+      <c r="K94" s="201" t="s">
+        <v>1986</v>
+      </c>
+      <c r="L94" s="224" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M94" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N94" s="888" t="s">
+        <v>2747</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="867"/>
-      <c r="B95" s="194"/>
-      <c r="C95" s="902"/>
-      <c r="D95" s="606"/>
-      <c r="E95" s="197"/>
-      <c r="F95" s="197"/>
-      <c r="G95" s="198"/>
+      <c r="A95" s="867" t="n">
+        <v>750</v>
+      </c>
+      <c r="B95" s="194" t="s">
+        <v>2748</v>
+      </c>
+      <c r="C95" s="330" t="s">
+        <v>44</v>
+      </c>
+      <c r="D95" s="102" t="s">
+        <v>468</v>
+      </c>
+      <c r="E95" s="197" t="s">
+        <v>2749</v>
+      </c>
+      <c r="F95" s="197" t="s">
+        <v>646</v>
+      </c>
+      <c r="G95" s="198" t="s">
+        <v>1140</v>
+      </c>
       <c r="H95" s="198"/>
-      <c r="I95" s="199"/>
-      <c r="J95" s="200"/>
-      <c r="K95" s="201"/>
-      <c r="L95" s="224"/>
+      <c r="I95" s="199" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J95" s="200" t="n">
+        <v>11</v>
+      </c>
+      <c r="K95" s="201" t="s">
+        <v>1277</v>
+      </c>
+      <c r="L95" s="224" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M95" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N95" s="888" t="s">
+        <v>2750</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="867"/>
-      <c r="B96" s="194"/>
-      <c r="C96" s="902"/>
-      <c r="D96" s="606"/>
-      <c r="E96" s="197"/>
-      <c r="F96" s="197"/>
-      <c r="G96" s="198"/>
+      <c r="A96" s="867" t="n">
+        <v>751</v>
+      </c>
+      <c r="B96" s="194" t="s">
+        <v>2751</v>
+      </c>
+      <c r="C96" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="D96" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="E96" s="197" t="s">
+        <v>2752</v>
+      </c>
+      <c r="F96" s="197" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G96" s="198" t="s">
+        <v>455</v>
+      </c>
       <c r="H96" s="198"/>
-      <c r="I96" s="199"/>
-      <c r="J96" s="200"/>
-      <c r="K96" s="201"/>
-      <c r="L96" s="224"/>
+      <c r="I96" s="199" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J96" s="200" t="n">
+        <v>9</v>
+      </c>
+      <c r="K96" s="201" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L96" s="224" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M96" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N96" s="888" t="s">
+        <v>2753</v>
+      </c>
+      <c r="O96" s="888" t="s">
+        <v>2754</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="867"/>
-      <c r="B97" s="194"/>
-      <c r="C97" s="902"/>
-      <c r="D97" s="606"/>
-      <c r="E97" s="197"/>
-      <c r="F97" s="197"/>
+      <c r="A97" s="867" t="n">
+        <v>752</v>
+      </c>
+      <c r="B97" s="194" t="s">
+        <v>2755</v>
+      </c>
+      <c r="C97" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="D97" s="133"/>
+      <c r="E97" s="197" t="s">
+        <v>2756</v>
+      </c>
+      <c r="F97" s="197" t="s">
+        <v>646</v>
+      </c>
       <c r="G97" s="198"/>
       <c r="H97" s="198"/>
-      <c r="I97" s="199"/>
-      <c r="J97" s="200"/>
-      <c r="K97" s="201"/>
-      <c r="L97" s="224"/>
+      <c r="I97" s="199" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J97" s="200" t="n">
+        <v>20</v>
+      </c>
+      <c r="K97" s="201" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L97" s="224" t="s">
+        <v>1091</v>
+      </c>
+      <c r="M97" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N97" s="888" t="s">
+        <v>2757</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="867"/>
-      <c r="B98" s="194"/>
-      <c r="C98" s="902"/>
-      <c r="D98" s="606"/>
-      <c r="E98" s="197"/>
-      <c r="F98" s="197"/>
+      <c r="A98" s="867" t="n">
+        <v>753</v>
+      </c>
+      <c r="B98" s="194" t="s">
+        <v>2758</v>
+      </c>
+      <c r="C98" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="D98" s="133"/>
+      <c r="E98" s="197" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F98" s="197" t="s">
+        <v>646</v>
+      </c>
       <c r="G98" s="198"/>
       <c r="H98" s="198"/>
-      <c r="I98" s="199"/>
-      <c r="J98" s="200"/>
-      <c r="K98" s="201"/>
-      <c r="L98" s="224"/>
+      <c r="I98" s="199" t="s">
+        <v>156</v>
+      </c>
+      <c r="J98" s="200" t="s">
+        <v>156</v>
+      </c>
+      <c r="K98" s="201" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L98" s="224" t="s">
+        <v>1091</v>
+      </c>
+      <c r="M98" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N98" s="888" t="s">
+        <v>2757</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="867"/>
-      <c r="B99" s="203"/>
-      <c r="C99" s="828"/>
-      <c r="D99" s="638"/>
-      <c r="E99" s="206"/>
-      <c r="F99" s="206"/>
-      <c r="G99" s="207"/>
+      <c r="A99" s="867" t="n">
+        <v>754</v>
+      </c>
+      <c r="B99" s="203" t="s">
+        <v>2759</v>
+      </c>
+      <c r="C99" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="D99" s="134" t="s">
+        <v>158</v>
+      </c>
+      <c r="E99" s="206" t="s">
+        <v>2760</v>
+      </c>
+      <c r="F99" s="206" t="s">
+        <v>888</v>
+      </c>
+      <c r="G99" s="207" t="s">
+        <v>889</v>
+      </c>
       <c r="H99" s="207"/>
-      <c r="I99" s="208"/>
-      <c r="J99" s="209"/>
-      <c r="K99" s="210"/>
-      <c r="L99" s="875"/>
+      <c r="I99" s="208" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J99" s="209" t="n">
+        <v>45</v>
+      </c>
+      <c r="K99" s="210" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L99" s="875" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M99" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N99" s="888" t="s">
+        <v>2761</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="867"/>
-      <c r="B100" s="194"/>
-      <c r="C100" s="902"/>
-      <c r="D100" s="606"/>
-      <c r="E100" s="197"/>
-      <c r="F100" s="198"/>
-      <c r="G100" s="198"/>
+      <c r="A100" s="867" t="n">
+        <v>755</v>
+      </c>
+      <c r="B100" s="194" t="s">
+        <v>2762</v>
+      </c>
+      <c r="C100" s="890" t="s">
+        <v>141</v>
+      </c>
+      <c r="D100" s="223" t="s">
+        <v>100</v>
+      </c>
+      <c r="E100" s="197" t="s">
+        <v>2763</v>
+      </c>
+      <c r="F100" s="198" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G100" s="198" t="s">
+        <v>808</v>
+      </c>
       <c r="H100" s="198"/>
-      <c r="I100" s="199"/>
-      <c r="J100" s="200"/>
-      <c r="K100" s="201"/>
-      <c r="L100" s="875"/>
+      <c r="I100" s="199" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J100" s="200" t="n">
+        <v>15</v>
+      </c>
+      <c r="K100" s="201" t="s">
+        <v>2373</v>
+      </c>
+      <c r="L100" s="875" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M100" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N100" s="888" t="s">
+        <v>2764</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="867"/>
-      <c r="B101" s="194"/>
-      <c r="C101" s="902"/>
-      <c r="D101" s="606"/>
-      <c r="E101" s="197"/>
-      <c r="F101" s="198"/>
-      <c r="G101" s="198"/>
+      <c r="A101" s="867" t="n">
+        <v>756</v>
+      </c>
+      <c r="B101" s="194" t="s">
+        <v>2765</v>
+      </c>
+      <c r="C101" s="890" t="s">
+        <v>141</v>
+      </c>
+      <c r="D101" s="223" t="s">
+        <v>100</v>
+      </c>
+      <c r="E101" s="197" t="s">
+        <v>2766</v>
+      </c>
+      <c r="F101" s="198" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G101" s="198" t="s">
+        <v>460</v>
+      </c>
       <c r="H101" s="198"/>
-      <c r="I101" s="199"/>
-      <c r="J101" s="200"/>
-      <c r="K101" s="201"/>
-      <c r="L101" s="875"/>
+      <c r="I101" s="199" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J101" s="200" t="n">
+        <v>350</v>
+      </c>
+      <c r="K101" s="201" t="s">
+        <v>2373</v>
+      </c>
+      <c r="L101" s="875" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M101" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N101" s="888" t="s">
+        <v>2764</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="867"/>
-      <c r="B102" s="194"/>
-      <c r="C102" s="902"/>
-      <c r="D102" s="606"/>
-      <c r="E102" s="197"/>
-      <c r="F102" s="197"/>
-      <c r="G102" s="198"/>
-      <c r="H102" s="198"/>
-      <c r="I102" s="199"/>
-      <c r="J102" s="200"/>
-      <c r="K102" s="201"/>
-      <c r="L102" s="875"/>
+      <c r="A102" s="867" t="n">
+        <v>757</v>
+      </c>
+      <c r="B102" s="194" t="s">
+        <v>2767</v>
+      </c>
+      <c r="C102" s="330" t="s">
+        <v>44</v>
+      </c>
+      <c r="D102" s="102" t="s">
+        <v>468</v>
+      </c>
+      <c r="E102" s="197" t="s">
+        <v>2768</v>
+      </c>
+      <c r="F102" s="197" t="s">
+        <v>443</v>
+      </c>
+      <c r="G102" s="198" t="s">
+        <v>828</v>
+      </c>
+      <c r="H102" s="198" t="s">
+        <v>1363</v>
+      </c>
+      <c r="I102" s="199" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J102" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="K102" s="201" t="s">
+        <v>1277</v>
+      </c>
+      <c r="L102" s="875" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M102" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N102" s="900" t="s">
+        <v>2769</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="867"/>
-      <c r="B103" s="194"/>
-      <c r="C103" s="902"/>
-      <c r="D103" s="606"/>
-      <c r="E103" s="197"/>
-      <c r="F103" s="197"/>
-      <c r="G103" s="198"/>
-      <c r="H103" s="198"/>
-      <c r="I103" s="199"/>
-      <c r="J103" s="200"/>
-      <c r="K103" s="201"/>
-      <c r="L103" s="224"/>
+      <c r="A103" s="867" t="n">
+        <v>758</v>
+      </c>
+      <c r="B103" s="194" t="s">
+        <v>2770</v>
+      </c>
+      <c r="C103" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="D103" s="223" t="s">
+        <v>100</v>
+      </c>
+      <c r="E103" s="197" t="s">
+        <v>2771</v>
+      </c>
+      <c r="F103" s="197" t="s">
+        <v>577</v>
+      </c>
+      <c r="G103" s="198" t="s">
+        <v>413</v>
+      </c>
+      <c r="H103" s="198" t="s">
+        <v>1204</v>
+      </c>
+      <c r="I103" s="199" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J103" s="200" t="n">
+        <v>30</v>
+      </c>
+      <c r="K103" s="201" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L103" s="224" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M103" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N103" s="888" t="s">
+        <v>2772</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="867"/>
-      <c r="B104" s="194"/>
-      <c r="C104" s="902"/>
-      <c r="D104" s="606"/>
-      <c r="E104" s="197"/>
-      <c r="F104" s="197"/>
+      <c r="A104" s="867" t="n">
+        <v>759</v>
+      </c>
+      <c r="B104" s="194" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C104" s="102" t="s">
+        <v>468</v>
+      </c>
+      <c r="D104" s="223" t="s">
+        <v>100</v>
+      </c>
+      <c r="E104" s="197" t="s">
+        <v>2774</v>
+      </c>
+      <c r="F104" s="197" t="s">
+        <v>828</v>
+      </c>
       <c r="G104" s="198"/>
-      <c r="H104" s="198"/>
-      <c r="I104" s="199"/>
-      <c r="J104" s="200"/>
-      <c r="K104" s="201"/>
-      <c r="L104" s="224"/>
+      <c r="H104" s="198" t="s">
+        <v>1363</v>
+      </c>
+      <c r="I104" s="199" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J104" s="200" t="n">
+        <v>35</v>
+      </c>
+      <c r="K104" s="201" t="s">
+        <v>1277</v>
+      </c>
+      <c r="L104" s="224" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M104" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N104" s="888" t="s">
+        <v>2775</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="867"/>
-      <c r="B105" s="194"/>
-      <c r="C105" s="902"/>
-      <c r="D105" s="606"/>
-      <c r="E105" s="197"/>
-      <c r="F105" s="197"/>
-      <c r="G105" s="198"/>
-      <c r="H105" s="198"/>
-      <c r="I105" s="199"/>
-      <c r="J105" s="200"/>
-      <c r="K105" s="201"/>
-      <c r="L105" s="224"/>
+      <c r="A105" s="867" t="n">
+        <v>760</v>
+      </c>
+      <c r="B105" s="194" t="s">
+        <v>2776</v>
+      </c>
+      <c r="C105" s="171" t="s">
+        <v>100</v>
+      </c>
+      <c r="D105" s="171"/>
+      <c r="E105" s="197" t="s">
+        <v>2777</v>
+      </c>
+      <c r="F105" s="197" t="s">
+        <v>953</v>
+      </c>
+      <c r="G105" s="198" t="s">
+        <v>646</v>
+      </c>
+      <c r="H105" s="198" t="s">
+        <v>2778</v>
+      </c>
+      <c r="I105" s="199" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="200" t="n">
+        <v>25</v>
+      </c>
+      <c r="K105" s="201" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L105" s="224" t="s">
+        <v>1764</v>
+      </c>
+      <c r="M105" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N105" s="888" t="s">
+        <v>2779</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="867"/>
-      <c r="B106" s="194"/>
-      <c r="C106" s="902"/>
-      <c r="D106" s="606"/>
-      <c r="E106" s="197"/>
-      <c r="F106" s="197"/>
-      <c r="G106" s="198"/>
+      <c r="A106" s="867" t="n">
+        <v>761</v>
+      </c>
+      <c r="B106" s="194" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C106" s="890" t="s">
+        <v>141</v>
+      </c>
+      <c r="D106" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="E106" s="197" t="s">
+        <v>2781</v>
+      </c>
+      <c r="F106" s="197" t="s">
+        <v>646</v>
+      </c>
+      <c r="G106" s="198" t="s">
+        <v>910</v>
+      </c>
       <c r="H106" s="198"/>
-      <c r="I106" s="199"/>
-      <c r="J106" s="200"/>
-      <c r="K106" s="201"/>
-      <c r="L106" s="224"/>
+      <c r="I106" s="199" t="n">
+        <v>3</v>
+      </c>
+      <c r="J106" s="200" t="n">
+        <v>225</v>
+      </c>
+      <c r="K106" s="201" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L106" s="224" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M106" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N106" s="888" t="s">
+        <v>2782</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="867"/>
-      <c r="B107" s="194"/>
-      <c r="C107" s="606"/>
-      <c r="D107" s="606"/>
-      <c r="E107" s="197"/>
-      <c r="F107" s="197"/>
-      <c r="G107" s="198"/>
+      <c r="A107" s="867" t="n">
+        <v>762</v>
+      </c>
+      <c r="B107" s="194" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C107" s="330" t="s">
+        <v>44</v>
+      </c>
+      <c r="D107" s="235" t="s">
+        <v>441</v>
+      </c>
+      <c r="E107" s="197" t="s">
+        <v>2784</v>
+      </c>
+      <c r="F107" s="197" t="s">
+        <v>819</v>
+      </c>
+      <c r="G107" s="198" t="s">
+        <v>443</v>
+      </c>
       <c r="H107" s="198"/>
-      <c r="I107" s="199"/>
-      <c r="J107" s="200"/>
-      <c r="K107" s="201"/>
-      <c r="L107" s="224"/>
+      <c r="I107" s="199" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="200" t="n">
+        <v>15</v>
+      </c>
+      <c r="K107" s="201" t="s">
+        <v>1277</v>
+      </c>
+      <c r="L107" s="224" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M107" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N107" s="888" t="s">
+        <v>2785</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="867"/>
-      <c r="B108" s="194"/>
-      <c r="C108" s="606"/>
-      <c r="D108" s="606"/>
-      <c r="E108" s="197"/>
-      <c r="F108" s="197"/>
+      <c r="A108" s="867" t="n">
+        <v>763</v>
+      </c>
+      <c r="B108" s="194" t="s">
+        <v>2786</v>
+      </c>
+      <c r="C108" s="115" t="s">
+        <v>514</v>
+      </c>
+      <c r="D108" s="134" t="s">
+        <v>158</v>
+      </c>
+      <c r="E108" s="197" t="s">
+        <v>2559</v>
+      </c>
+      <c r="F108" s="197" t="s">
+        <v>585</v>
+      </c>
       <c r="G108" s="198"/>
       <c r="H108" s="198"/>
-      <c r="I108" s="199"/>
-      <c r="J108" s="200"/>
-      <c r="K108" s="201"/>
-      <c r="L108" s="224"/>
+      <c r="I108" s="199" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J108" s="200" t="n">
+        <v>55</v>
+      </c>
+      <c r="K108" s="201" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L108" s="224" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M108" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N108" s="888" t="s">
+        <v>2787</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="867"/>
-      <c r="B109" s="194"/>
-      <c r="C109" s="606"/>
-      <c r="D109" s="606"/>
-      <c r="E109" s="197"/>
-      <c r="F109" s="197"/>
-      <c r="G109" s="198"/>
+      <c r="A109" s="867" t="n">
+        <v>764</v>
+      </c>
+      <c r="B109" s="194" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C109" s="102" t="s">
+        <v>468</v>
+      </c>
+      <c r="D109" s="601" t="s">
+        <v>487</v>
+      </c>
+      <c r="E109" s="197" t="s">
+        <v>2789</v>
+      </c>
+      <c r="F109" s="197" t="s">
+        <v>676</v>
+      </c>
+      <c r="G109" s="198" t="s">
+        <v>470</v>
+      </c>
       <c r="H109" s="198"/>
-      <c r="I109" s="199"/>
-      <c r="J109" s="200"/>
-      <c r="K109" s="201"/>
-      <c r="L109" s="875"/>
+      <c r="I109" s="199" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J109" s="200" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K109" s="201" t="s">
+        <v>2790</v>
+      </c>
+      <c r="L109" s="224" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M109" s="561" t="n">
+        <v>10</v>
+      </c>
+      <c r="N109" s="888" t="s">
+        <v>2791</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="867"/>
-      <c r="B110" s="194"/>
-      <c r="C110" s="902"/>
-      <c r="D110" s="606"/>
-      <c r="E110" s="197"/>
-      <c r="F110" s="197"/>
-      <c r="G110" s="198"/>
+      <c r="A110" s="867" t="n">
+        <v>765</v>
+      </c>
+      <c r="B110" s="194" t="s">
+        <v>2792</v>
+      </c>
+      <c r="C110" s="102" t="s">
+        <v>468</v>
+      </c>
+      <c r="D110" s="601" t="s">
+        <v>487</v>
+      </c>
+      <c r="E110" s="197" t="s">
+        <v>2793</v>
+      </c>
+      <c r="F110" s="197" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G110" s="198" t="s">
+        <v>470</v>
+      </c>
       <c r="H110" s="198"/>
-      <c r="I110" s="199"/>
-      <c r="J110" s="200"/>
-      <c r="K110" s="201"/>
-      <c r="L110" s="875"/>
+      <c r="I110" s="199" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" s="201" t="s">
+        <v>2790</v>
+      </c>
+      <c r="L110" s="224" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M110" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N110" s="888" t="s">
+        <v>2791</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="867"/>
-      <c r="B111" s="194"/>
-      <c r="C111" s="902"/>
-      <c r="D111" s="606"/>
-      <c r="E111" s="197"/>
-      <c r="F111" s="197"/>
+      <c r="A111" s="867" t="n">
+        <v>766</v>
+      </c>
+      <c r="B111" s="194" t="s">
+        <v>2794</v>
+      </c>
+      <c r="C111" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="D111" s="223" t="s">
+        <v>100</v>
+      </c>
+      <c r="E111" s="197" t="s">
+        <v>2795</v>
+      </c>
+      <c r="F111" s="197" t="s">
+        <v>2796</v>
+      </c>
       <c r="G111" s="198"/>
       <c r="H111" s="198"/>
-      <c r="I111" s="199"/>
-      <c r="J111" s="200"/>
-      <c r="K111" s="201"/>
-      <c r="L111" s="875"/>
+      <c r="I111" s="199" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J111" s="200" t="n">
+        <v>50</v>
+      </c>
+      <c r="K111" s="201" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L111" s="875" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M111" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N111" s="888" t="s">
+        <v>2797</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="867"/>
-      <c r="B112" s="194"/>
-      <c r="C112" s="902"/>
-      <c r="D112" s="606"/>
-      <c r="E112" s="197"/>
-      <c r="F112" s="197"/>
-      <c r="G112" s="198"/>
+      <c r="A112" s="867" t="n">
+        <v>767</v>
+      </c>
+      <c r="B112" s="194" t="s">
+        <v>2798</v>
+      </c>
+      <c r="C112" s="235" t="s">
+        <v>441</v>
+      </c>
+      <c r="D112" s="102" t="s">
+        <v>468</v>
+      </c>
+      <c r="E112" s="197" t="s">
+        <v>2799</v>
+      </c>
+      <c r="F112" s="197" t="s">
+        <v>443</v>
+      </c>
+      <c r="G112" s="198" t="s">
+        <v>537</v>
+      </c>
       <c r="H112" s="198"/>
-      <c r="I112" s="199"/>
-      <c r="J112" s="200"/>
-      <c r="K112" s="201"/>
-      <c r="L112" s="875"/>
+      <c r="I112" s="199" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J112" s="200" t="n">
+        <v>50</v>
+      </c>
+      <c r="K112" s="201" t="s">
+        <v>1381</v>
+      </c>
+      <c r="L112" s="875" t="s">
+        <v>1381</v>
+      </c>
+      <c r="M112" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N112" s="888" t="s">
+        <v>2800</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="867"/>
-      <c r="B113" s="194"/>
-      <c r="C113" s="902"/>
-      <c r="D113" s="606"/>
-      <c r="E113" s="197"/>
-      <c r="F113" s="197"/>
+      <c r="A113" s="867" t="n">
+        <v>768</v>
+      </c>
+      <c r="B113" s="194" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C113" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="D113" s="361" t="s">
+        <v>406</v>
+      </c>
+      <c r="E113" s="197" t="s">
+        <v>2802</v>
+      </c>
+      <c r="F113" s="197" t="s">
+        <v>2803</v>
+      </c>
       <c r="G113" s="198"/>
       <c r="H113" s="198"/>
-      <c r="I113" s="199"/>
-      <c r="J113" s="200"/>
-      <c r="K113" s="201"/>
-      <c r="L113" s="224"/>
+      <c r="I113" s="199" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J113" s="200" t="n">
+        <v>50</v>
+      </c>
+      <c r="K113" s="201" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L113" s="224" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M113" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N113" s="888" t="s">
+        <v>2754</v>
+      </c>
+      <c r="O113" s="888" t="s">
+        <v>2804</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="867"/>
-      <c r="B114" s="194"/>
-      <c r="C114" s="902"/>
-      <c r="D114" s="606"/>
-      <c r="E114" s="197"/>
-      <c r="F114" s="197"/>
+      <c r="A114" s="867" t="n">
+        <v>769</v>
+      </c>
+      <c r="B114" s="194" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C114" s="171" t="s">
+        <v>100</v>
+      </c>
+      <c r="D114" s="134" t="s">
+        <v>158</v>
+      </c>
+      <c r="E114" s="197" t="s">
+        <v>2806</v>
+      </c>
+      <c r="F114" s="197" t="s">
+        <v>2139</v>
+      </c>
       <c r="G114" s="198"/>
       <c r="H114" s="198"/>
-      <c r="I114" s="199"/>
-      <c r="J114" s="200"/>
-      <c r="K114" s="201"/>
-      <c r="L114" s="224"/>
+      <c r="I114" s="199" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J114" s="200" t="n">
+        <v>55</v>
+      </c>
+      <c r="K114" s="201" t="s">
+        <v>1175</v>
+      </c>
+      <c r="L114" s="224" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M114" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N114" s="888" t="s">
+        <v>2807</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="867"/>
-      <c r="B115" s="194"/>
-      <c r="C115" s="902"/>
-      <c r="D115" s="606"/>
-      <c r="E115" s="197"/>
-      <c r="F115" s="197"/>
+      <c r="A115" s="867" t="n">
+        <v>770</v>
+      </c>
+      <c r="B115" s="194" t="s">
+        <v>2808</v>
+      </c>
+      <c r="C115" s="744" t="s">
+        <v>612</v>
+      </c>
+      <c r="D115" s="235" t="s">
+        <v>441</v>
+      </c>
+      <c r="E115" s="197" t="s">
+        <v>2809</v>
+      </c>
+      <c r="F115" s="197" t="s">
+        <v>2671</v>
+      </c>
       <c r="G115" s="198"/>
       <c r="H115" s="198"/>
-      <c r="I115" s="199"/>
-      <c r="J115" s="200"/>
-      <c r="K115" s="201"/>
-      <c r="L115" s="224"/>
+      <c r="I115" s="199" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J115" s="200" t="n">
+        <v>650</v>
+      </c>
+      <c r="K115" s="201" t="s">
+        <v>1131</v>
+      </c>
+      <c r="L115" s="224" t="s">
+        <v>1091</v>
+      </c>
+      <c r="M115" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N115" s="888" t="s">
+        <v>2810</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="867"/>
-      <c r="B116" s="194"/>
-      <c r="C116" s="902"/>
-      <c r="D116" s="606"/>
-      <c r="E116" s="197"/>
-      <c r="F116" s="197"/>
+      <c r="A116" s="867" t="n">
+        <v>771</v>
+      </c>
+      <c r="B116" s="194" t="s">
+        <v>2811</v>
+      </c>
+      <c r="C116" s="330" t="s">
+        <v>44</v>
+      </c>
+      <c r="D116" s="235" t="s">
+        <v>441</v>
+      </c>
+      <c r="E116" s="197" t="s">
+        <v>2812</v>
+      </c>
+      <c r="F116" s="197" t="s">
+        <v>676</v>
+      </c>
       <c r="G116" s="198"/>
       <c r="H116" s="198"/>
-      <c r="I116" s="199"/>
-      <c r="J116" s="200"/>
-      <c r="K116" s="201"/>
-      <c r="L116" s="224"/>
+      <c r="I116" s="199" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J116" s="200" t="n">
+        <v>10</v>
+      </c>
+      <c r="K116" s="201" t="s">
+        <v>1277</v>
+      </c>
+      <c r="L116" s="224" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M116" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N116" s="901" t="s">
+        <v>2813</v>
+      </c>
+      <c r="O116" s="888" t="s">
+        <v>2814</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="867"/>
-      <c r="B117" s="194"/>
-      <c r="C117" s="902"/>
-      <c r="D117" s="606"/>
-      <c r="E117" s="197"/>
-      <c r="F117" s="197"/>
+      <c r="A117" s="867" t="n">
+        <v>772</v>
+      </c>
+      <c r="B117" s="194" t="s">
+        <v>2815</v>
+      </c>
+      <c r="C117" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="D117" s="881" t="s">
+        <v>411</v>
+      </c>
+      <c r="E117" s="197" t="s">
+        <v>2816</v>
+      </c>
+      <c r="F117" s="197" t="s">
+        <v>447</v>
+      </c>
       <c r="G117" s="198"/>
       <c r="H117" s="198"/>
-      <c r="I117" s="199"/>
-      <c r="J117" s="200"/>
-      <c r="K117" s="201"/>
-      <c r="L117" s="224"/>
+      <c r="I117" s="199" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J117" s="200" t="n">
+        <v>55</v>
+      </c>
+      <c r="K117" s="201" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L117" s="224" t="s">
+        <v>1091</v>
+      </c>
+      <c r="M117" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N117" s="901" t="s">
+        <v>2817</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="867"/>
-      <c r="B118" s="194"/>
-      <c r="C118" s="902"/>
-      <c r="D118" s="606"/>
-      <c r="E118" s="197"/>
-      <c r="F118" s="197"/>
+      <c r="A118" s="867" t="n">
+        <v>773</v>
+      </c>
+      <c r="B118" s="194" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C118" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="D118" s="223" t="s">
+        <v>100</v>
+      </c>
+      <c r="E118" s="197" t="s">
+        <v>2819</v>
+      </c>
+      <c r="F118" s="197" t="s">
+        <v>2820</v>
+      </c>
       <c r="G118" s="198"/>
       <c r="H118" s="198"/>
-      <c r="I118" s="199"/>
-      <c r="J118" s="200"/>
-      <c r="K118" s="201"/>
-      <c r="L118" s="224"/>
+      <c r="I118" s="199" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J118" s="200" t="n">
+        <v>30</v>
+      </c>
+      <c r="K118" s="201" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L118" s="224" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M118" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N118" s="888" t="s">
+        <v>2821</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="867"/>
-      <c r="B119" s="194"/>
-      <c r="C119" s="902"/>
-      <c r="D119" s="606"/>
-      <c r="E119" s="197"/>
-      <c r="F119" s="197"/>
+      <c r="A119" s="867" t="n">
+        <v>774</v>
+      </c>
+      <c r="B119" s="194" t="s">
+        <v>2822</v>
+      </c>
+      <c r="C119" s="46" t="s">
+        <v>440</v>
+      </c>
+      <c r="D119" s="34" t="s">
+        <v>418</v>
+      </c>
+      <c r="E119" s="197" t="s">
+        <v>2823</v>
+      </c>
+      <c r="F119" s="197" t="s">
+        <v>656</v>
+      </c>
       <c r="G119" s="198"/>
       <c r="H119" s="198"/>
-      <c r="I119" s="199"/>
-      <c r="J119" s="200"/>
-      <c r="K119" s="201"/>
-      <c r="L119" s="875"/>
+      <c r="I119" s="199" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J119" s="200" t="n">
+        <v>25</v>
+      </c>
+      <c r="K119" s="201" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L119" s="875" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M119" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N119" s="888" t="s">
+        <v>2824</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="867"/>
-      <c r="B120" s="194"/>
-      <c r="C120" s="792"/>
-      <c r="D120" s="727"/>
-      <c r="E120" s="197"/>
+      <c r="A120" s="867" t="n">
+        <v>775</v>
+      </c>
+      <c r="B120" s="194" t="s">
+        <v>2825</v>
+      </c>
+      <c r="C120" s="330" t="s">
+        <v>44</v>
+      </c>
+      <c r="D120" s="223" t="s">
+        <v>100</v>
+      </c>
+      <c r="E120" s="197" t="s">
+        <v>2826</v>
+      </c>
       <c r="F120" s="197"/>
       <c r="G120" s="198"/>
       <c r="H120" s="198"/>
-      <c r="I120" s="199"/>
-      <c r="J120" s="200"/>
-      <c r="K120" s="201"/>
-      <c r="L120" s="875"/>
+      <c r="I120" s="199" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J120" s="200" t="n">
+        <v>5</v>
+      </c>
+      <c r="K120" s="201" t="s">
+        <v>1277</v>
+      </c>
+      <c r="L120" s="224" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M120" s="561" t="s">
+        <v>156</v>
+      </c>
+      <c r="N120" s="888" t="s">
+        <v>2813</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="867"/>
@@ -54467,9 +54270,9 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="867"/>
-      <c r="B126" s="194"/>
-      <c r="C126" s="902"/>
-      <c r="D126" s="606"/>
+      <c r="B126" s="396"/>
+      <c r="C126" s="792"/>
+      <c r="D126" s="727"/>
       <c r="E126" s="197"/>
       <c r="F126" s="197"/>
       <c r="G126" s="198"/>
@@ -56389,1540 +56192,244 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="B2:C30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="58" width="6.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="889" width="6.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="6.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="888" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="889" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="2" width="6.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="2" width="6.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="11.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="33.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="181.29"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>2725</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
-        <v>2726</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>2727</v>
-      </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>2728</v>
-      </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
-        <v>2729</v>
-      </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>2730</v>
-      </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-    </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="904" t="s">
-        <v>2731</v>
-      </c>
-      <c r="B2" s="905" t="s">
-        <v>2732</v>
-      </c>
-      <c r="C2" s="906" t="s">
-        <v>2731</v>
-      </c>
-      <c r="D2" s="905" t="s">
-        <v>2732</v>
-      </c>
-      <c r="E2" s="907" t="s">
-        <v>2732</v>
-      </c>
-      <c r="F2" s="908" t="s">
-        <v>2731</v>
-      </c>
-      <c r="G2" s="905" t="s">
-        <v>2732</v>
-      </c>
-      <c r="H2" s="305" t="s">
-        <v>2732</v>
-      </c>
-      <c r="I2" s="909" t="s">
-        <v>2731</v>
-      </c>
-      <c r="J2" s="905" t="s">
-        <v>2732</v>
-      </c>
-      <c r="K2" s="907" t="s">
-        <v>2732</v>
-      </c>
-      <c r="L2" s="904" t="s">
-        <v>2731</v>
-      </c>
-      <c r="M2" s="905" t="s">
-        <v>2732</v>
-      </c>
-      <c r="N2" s="907" t="s">
-        <v>2732</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>2733</v>
-      </c>
-      <c r="P2" s="904" t="s">
-        <v>2731</v>
-      </c>
-      <c r="Q2" s="905" t="s">
-        <v>2732</v>
-      </c>
-      <c r="R2" s="907" t="s">
-        <v>2732</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>2733</v>
+      <c r="B2" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C2" s="660" t="s">
+        <v>2827</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="910" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="911" t="n">
-        <v>27</v>
-      </c>
-      <c r="C3" s="912" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="911" t="n">
-        <v>13</v>
-      </c>
-      <c r="E3" s="913" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="914" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="911" t="n">
-        <v>33</v>
-      </c>
-      <c r="H3" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="I3" s="914" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="911" t="n">
-        <v>17</v>
-      </c>
-      <c r="K3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="915" t="s">
-        <v>44</v>
-      </c>
-      <c r="M3" s="916" t="n">
-        <v>19</v>
-      </c>
-      <c r="N3" s="917" t="n">
-        <v>7</v>
-      </c>
-      <c r="O3" s="571" t="n">
-        <f aca="false">SUM(M3:N3)</f>
-        <v>26</v>
-      </c>
-      <c r="P3" s="915" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q3" s="916" t="n">
-        <v>10</v>
-      </c>
-      <c r="R3" s="917" t="n">
-        <v>4</v>
-      </c>
-      <c r="S3" s="571" t="n">
-        <f aca="false">SUM(Q3:R3)</f>
-        <v>14</v>
+      <c r="B3" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C3" s="904" t="s">
+        <v>2828</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="918" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="919" t="n">
-        <v>14</v>
-      </c>
-      <c r="C4" s="920" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="919" t="n">
-        <v>9</v>
-      </c>
-      <c r="E4" s="921" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="922" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="919" t="n">
-        <v>19</v>
-      </c>
-      <c r="H4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="922" t="s">
-        <v>78</v>
-      </c>
-      <c r="J4" s="919" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" s="922" t="s">
-        <v>78</v>
-      </c>
-      <c r="M4" s="919" t="n">
-        <v>15</v>
-      </c>
-      <c r="N4" s="921" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="577" t="n">
-        <f aca="false">SUM(M4:N4)</f>
-        <v>16</v>
-      </c>
-      <c r="P4" s="922" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q4" s="919" t="n">
-        <v>10</v>
-      </c>
-      <c r="R4" s="921" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="577" t="n">
-        <f aca="false">SUM(Q4:R4)</f>
-        <v>11</v>
+      <c r="B4" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C4" s="904" t="s">
+        <v>2829</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="923" t="s">
-        <v>468</v>
-      </c>
-      <c r="B5" s="919" t="n">
-        <v>14</v>
-      </c>
-      <c r="C5" s="924" t="s">
-        <v>468</v>
-      </c>
-      <c r="D5" s="919" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="921" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="925" t="s">
-        <v>468</v>
-      </c>
-      <c r="G5" s="919" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="I5" s="925" t="s">
-        <v>468</v>
-      </c>
-      <c r="J5" s="919" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="925" t="s">
-        <v>468</v>
-      </c>
-      <c r="M5" s="919" t="n">
-        <v>6</v>
-      </c>
-      <c r="N5" s="921" t="n">
-        <v>8</v>
-      </c>
-      <c r="O5" s="577" t="n">
-        <f aca="false">SUM(M5:N5)</f>
-        <v>14</v>
-      </c>
-      <c r="P5" s="925" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q5" s="919" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="921" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" s="577" t="n">
-        <f aca="false">SUM(Q5:R5)</f>
-        <v>3</v>
+      <c r="B5" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="C5" s="904" t="s">
+        <v>2830</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="926" t="s">
-        <v>2734</v>
-      </c>
-      <c r="B6" s="919" t="n">
-        <v>12</v>
-      </c>
-      <c r="C6" s="927" t="s">
-        <v>2734</v>
-      </c>
-      <c r="D6" s="919" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" s="921" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="928" t="s">
-        <v>418</v>
-      </c>
-      <c r="G6" s="919" t="n">
-        <v>12</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="I6" s="928" t="s">
-        <v>418</v>
-      </c>
-      <c r="J6" s="919" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="928" t="s">
-        <v>418</v>
-      </c>
-      <c r="M6" s="919" t="n">
-        <v>10</v>
-      </c>
-      <c r="N6" s="921" t="n">
-        <v>12</v>
-      </c>
-      <c r="O6" s="577" t="n">
-        <f aca="false">SUM(M6:N6)</f>
-        <v>22</v>
-      </c>
-      <c r="P6" s="928" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q6" s="919" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" s="921" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" s="577" t="n">
-        <f aca="false">SUM(Q6:R6)</f>
-        <v>6</v>
+      <c r="B6" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C6" s="904" t="s">
+        <v>2831</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="929" t="s">
-        <v>406</v>
-      </c>
-      <c r="B7" s="919" t="n">
-        <v>12</v>
-      </c>
-      <c r="C7" s="930" t="s">
-        <v>406</v>
-      </c>
-      <c r="D7" s="919" t="n">
-        <v>14</v>
-      </c>
-      <c r="E7" s="921" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="931" t="s">
-        <v>406</v>
-      </c>
-      <c r="G7" s="919" t="n">
-        <v>32</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="I7" s="931" t="s">
-        <v>406</v>
-      </c>
-      <c r="J7" s="919" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="931" t="s">
-        <v>406</v>
-      </c>
-      <c r="M7" s="919" t="n">
-        <v>26</v>
-      </c>
-      <c r="N7" s="921" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="577" t="n">
-        <f aca="false">SUM(M7:N7)</f>
-        <v>27</v>
-      </c>
-      <c r="P7" s="931" t="s">
-        <v>406</v>
-      </c>
-      <c r="Q7" s="919" t="n">
-        <v>10</v>
-      </c>
-      <c r="R7" s="921" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="577" t="n">
-        <f aca="false">SUM(Q7:R7)</f>
-        <v>10</v>
+      <c r="B7" s="2" t="s">
+        <v>2832</v>
+      </c>
+      <c r="C7" s="660" t="s">
+        <v>2833</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="932" t="s">
-        <v>440</v>
-      </c>
-      <c r="B8" s="919" t="n">
-        <v>12</v>
-      </c>
-      <c r="C8" s="933" t="s">
-        <v>440</v>
-      </c>
-      <c r="D8" s="919" t="n">
-        <v>15</v>
-      </c>
-      <c r="E8" s="921" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="934" t="s">
-        <v>440</v>
-      </c>
-      <c r="G8" s="919" t="n">
-        <v>20</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="934" t="s">
-        <v>440</v>
-      </c>
-      <c r="J8" s="935" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" s="936" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="934" t="s">
-        <v>440</v>
-      </c>
-      <c r="M8" s="935" t="n">
-        <v>25</v>
-      </c>
-      <c r="N8" s="937" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" s="938" t="n">
-        <f aca="false">SUM(M8:N8)</f>
-        <v>27</v>
-      </c>
-      <c r="P8" s="934" t="s">
-        <v>440</v>
-      </c>
-      <c r="Q8" s="919" t="n">
-        <v>13</v>
-      </c>
-      <c r="R8" s="921" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" s="577" t="n">
-        <f aca="false">SUM(Q8:R8)</f>
-        <v>15</v>
+      <c r="B8" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>2834</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="939" t="s">
-        <v>441</v>
-      </c>
-      <c r="B9" s="919" t="n">
-        <v>9</v>
-      </c>
-      <c r="C9" s="940" t="s">
-        <v>441</v>
-      </c>
-      <c r="D9" s="919" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="921" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="941" t="s">
-        <v>441</v>
-      </c>
-      <c r="G9" s="919" t="n">
-        <v>9</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="941" t="s">
-        <v>441</v>
-      </c>
-      <c r="J9" s="935" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" s="936" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="941" t="s">
-        <v>441</v>
-      </c>
-      <c r="M9" s="935" t="n">
-        <v>6</v>
-      </c>
-      <c r="N9" s="937" t="n">
-        <v>7</v>
-      </c>
-      <c r="O9" s="938" t="n">
-        <f aca="false">SUM(M9:N9)</f>
-        <v>13</v>
-      </c>
-      <c r="P9" s="941" t="s">
-        <v>441</v>
-      </c>
-      <c r="Q9" s="919" t="n">
-        <v>7</v>
-      </c>
-      <c r="R9" s="921" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" s="577" t="n">
-        <f aca="false">SUM(Q9:R9)</f>
-        <v>9</v>
+      <c r="B9" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C9" s="904" t="s">
+        <v>2835</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="942" t="s">
-        <v>612</v>
-      </c>
-      <c r="B10" s="919" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" s="943" t="s">
-        <v>612</v>
-      </c>
-      <c r="D10" s="919" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" s="921" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="944" t="s">
-        <v>612</v>
-      </c>
-      <c r="G10" s="919" t="n">
-        <v>9</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="944" t="s">
-        <v>612</v>
-      </c>
-      <c r="J10" s="935" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" s="936" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="944" t="s">
-        <v>612</v>
-      </c>
-      <c r="M10" s="935" t="n">
-        <v>11</v>
-      </c>
-      <c r="N10" s="937" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" s="938" t="n">
-        <f aca="false">SUM(M10:N10)</f>
-        <v>16</v>
-      </c>
-      <c r="P10" s="944" t="s">
-        <v>612</v>
-      </c>
-      <c r="Q10" s="919" t="n">
-        <v>6</v>
-      </c>
-      <c r="R10" s="921" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="577" t="n">
-        <f aca="false">SUM(Q10:R10)</f>
-        <v>6</v>
+      <c r="B10" s="2" t="s">
+        <v>2836</v>
+      </c>
+      <c r="C10" s="904" t="s">
+        <v>2837</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="945" t="s">
-        <v>514</v>
-      </c>
-      <c r="B11" s="919" t="n">
-        <v>9</v>
-      </c>
-      <c r="C11" s="946" t="s">
-        <v>514</v>
-      </c>
-      <c r="D11" s="919" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="921" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="947" t="s">
-        <v>514</v>
-      </c>
-      <c r="G11" s="919" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" s="947" t="s">
-        <v>514</v>
-      </c>
-      <c r="J11" s="935" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="936" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" s="947" t="s">
-        <v>514</v>
-      </c>
-      <c r="M11" s="935" t="n">
-        <f aca="false">14-9</f>
-        <v>5</v>
-      </c>
-      <c r="N11" s="937" t="n">
-        <v>11</v>
-      </c>
-      <c r="O11" s="938" t="n">
-        <f aca="false">SUM(M11:N11)</f>
-        <v>16</v>
-      </c>
-      <c r="P11" s="947" t="s">
-        <v>514</v>
-      </c>
-      <c r="Q11" s="919" t="n">
-        <v>7</v>
-      </c>
-      <c r="R11" s="921" t="n">
-        <v>6</v>
-      </c>
-      <c r="S11" s="577" t="n">
-        <f aca="false">SUM(Q11:R11)</f>
-        <v>13</v>
+      <c r="B11" s="660" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C11" s="904" t="s">
+        <v>2839</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="948" t="s">
-        <v>487</v>
-      </c>
-      <c r="B12" s="919" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="949" t="s">
-        <v>487</v>
-      </c>
-      <c r="D12" s="919" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="921" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="950" t="s">
-        <v>487</v>
-      </c>
-      <c r="G12" s="919" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" s="950" t="s">
-        <v>487</v>
-      </c>
-      <c r="J12" s="935" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" s="936" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="950" t="s">
-        <v>487</v>
-      </c>
-      <c r="M12" s="935" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" s="937" t="n">
-        <v>12</v>
-      </c>
-      <c r="O12" s="938" t="n">
-        <f aca="false">SUM(M12:N12)</f>
-        <v>17</v>
-      </c>
-      <c r="P12" s="950" t="s">
-        <v>487</v>
-      </c>
-      <c r="Q12" s="919" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" s="921" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" s="577" t="n">
-        <f aca="false">SUM(Q12:R12)</f>
-        <v>3</v>
+      <c r="B12" s="2" t="s">
+        <v>2840</v>
+      </c>
+      <c r="C12" s="905" t="s">
+        <v>2841</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="951" t="s">
-        <v>411</v>
-      </c>
-      <c r="B13" s="919" t="n">
-        <v>7</v>
-      </c>
-      <c r="C13" s="952" t="s">
-        <v>411</v>
-      </c>
-      <c r="D13" s="919" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" s="921" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="953" t="s">
-        <v>411</v>
-      </c>
-      <c r="G13" s="919" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" s="953" t="s">
-        <v>411</v>
-      </c>
-      <c r="J13" s="935" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" s="936" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" s="953" t="s">
-        <v>411</v>
-      </c>
-      <c r="M13" s="935" t="n">
-        <v>13</v>
-      </c>
-      <c r="N13" s="937" t="n">
-        <v>4</v>
-      </c>
-      <c r="O13" s="938" t="n">
-        <f aca="false">SUM(M13:N13)</f>
-        <v>17</v>
-      </c>
-      <c r="P13" s="953" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q13" s="919" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" s="921" t="n">
-        <v>4</v>
-      </c>
-      <c r="S13" s="577" t="n">
-        <f aca="false">SUM(Q13:R13)</f>
-        <v>5</v>
+      <c r="B13" s="2" t="s">
+        <v>2842</v>
+      </c>
+      <c r="C13" s="904" t="s">
+        <v>2843</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="954" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14" s="919" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="955" t="s">
-        <v>141</v>
-      </c>
-      <c r="D14" s="919" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" s="921" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="956" t="s">
-        <v>141</v>
-      </c>
-      <c r="G14" s="919" t="n">
-        <v>9</v>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="956" t="s">
-        <v>141</v>
-      </c>
-      <c r="J14" s="935" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="936" t="n">
-        <v>5</v>
-      </c>
-      <c r="L14" s="956" t="s">
-        <v>141</v>
-      </c>
-      <c r="M14" s="935" t="n">
-        <v>5</v>
-      </c>
-      <c r="N14" s="937" t="n">
-        <v>6</v>
-      </c>
-      <c r="O14" s="938" t="n">
-        <f aca="false">SUM(M14:N14)</f>
-        <v>11</v>
-      </c>
-      <c r="P14" s="956" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q14" s="919" t="n">
-        <v>5</v>
-      </c>
-      <c r="R14" s="921" t="n">
-        <v>6</v>
-      </c>
-      <c r="S14" s="577" t="n">
-        <f aca="false">SUM(Q14:R14)</f>
-        <v>11</v>
+      <c r="B14" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C14" s="904" t="s">
+        <v>2844</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="957" t="s">
-        <v>535</v>
-      </c>
-      <c r="B15" s="919" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="958" t="s">
-        <v>535</v>
-      </c>
-      <c r="D15" s="919" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" s="921" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" s="959" t="s">
-        <v>535</v>
-      </c>
-      <c r="G15" s="919" t="n">
-        <v>11</v>
-      </c>
-      <c r="H15" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="I15" s="959" t="s">
-        <v>535</v>
-      </c>
-      <c r="J15" s="935" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="960" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="959" t="s">
-        <v>535</v>
-      </c>
-      <c r="M15" s="935" t="n">
-        <v>10</v>
-      </c>
-      <c r="N15" s="961" t="n">
-        <v>8</v>
-      </c>
-      <c r="O15" s="962" t="n">
-        <f aca="false">SUM(M15:N15)</f>
-        <v>18</v>
-      </c>
-      <c r="P15" s="959" t="s">
-        <v>535</v>
-      </c>
-      <c r="Q15" s="919" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" s="921" t="n">
-        <v>6</v>
-      </c>
-      <c r="S15" s="577" t="n">
-        <f aca="false">SUM(Q15:R15)</f>
-        <v>8</v>
+      <c r="B15" s="2" t="s">
+        <v>2845</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>2846</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="963" t="s">
-        <v>158</v>
-      </c>
-      <c r="B16" s="919" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="964" t="s">
-        <v>158</v>
-      </c>
-      <c r="D16" s="919" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="921" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="965" t="s">
-        <v>158</v>
-      </c>
-      <c r="G16" s="919" t="n">
-        <v>9</v>
-      </c>
-      <c r="H16" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="I16" s="965" t="s">
-        <v>158</v>
-      </c>
-      <c r="J16" s="935" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" s="936" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" s="965" t="s">
-        <v>158</v>
-      </c>
-      <c r="M16" s="935" t="n">
-        <v>6</v>
-      </c>
-      <c r="N16" s="937" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" s="938" t="n">
-        <f aca="false">SUM(M16:N16)</f>
-        <v>8</v>
-      </c>
-      <c r="P16" s="965" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q16" s="919" t="n">
-        <v>4</v>
-      </c>
-      <c r="R16" s="921" t="n">
-        <v>3</v>
-      </c>
-      <c r="S16" s="577" t="n">
-        <f aca="false">SUM(Q16:R16)</f>
-        <v>7</v>
+      <c r="B16" s="2" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>2847</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="966" t="s">
-        <v>570</v>
-      </c>
-      <c r="B17" s="919" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="967" t="s">
-        <v>570</v>
-      </c>
-      <c r="D17" s="919" t="n">
-        <v>6</v>
-      </c>
-      <c r="E17" s="921" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="968" t="s">
-        <v>570</v>
-      </c>
-      <c r="G17" s="919" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="968" t="s">
-        <v>570</v>
-      </c>
-      <c r="J17" s="919" t="n">
-        <v>6</v>
-      </c>
-      <c r="K17" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" s="968" t="s">
-        <v>570</v>
-      </c>
-      <c r="M17" s="919" t="n">
-        <v>6</v>
-      </c>
-      <c r="N17" s="969" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" s="970" t="n">
-        <f aca="false">SUM(M17:N17)</f>
-        <v>8</v>
-      </c>
-      <c r="P17" s="968" t="s">
-        <v>570</v>
-      </c>
-      <c r="Q17" s="919" t="n">
-        <v>8</v>
-      </c>
-      <c r="R17" s="921" t="n">
-        <v>3</v>
-      </c>
-      <c r="S17" s="577" t="n">
-        <f aca="false">SUM(Q17:R17)</f>
-        <v>11</v>
+      <c r="B17" s="2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>2848</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="971" t="s">
-        <v>464</v>
-      </c>
-      <c r="B18" s="919" t="n">
-        <v>8</v>
-      </c>
-      <c r="C18" s="972" t="s">
-        <v>464</v>
-      </c>
-      <c r="D18" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="921" t="n">
-        <v>13</v>
-      </c>
-      <c r="F18" s="973" t="s">
-        <v>464</v>
-      </c>
-      <c r="G18" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="I18" s="973" t="s">
-        <v>464</v>
-      </c>
-      <c r="J18" s="974" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="L18" s="973" t="s">
-        <v>464</v>
-      </c>
-      <c r="M18" s="974" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" s="921" t="n">
-        <v>14</v>
-      </c>
-      <c r="O18" s="577" t="n">
-        <f aca="false">SUM(M18:N18)</f>
-        <v>15</v>
-      </c>
-      <c r="P18" s="973" t="s">
-        <v>464</v>
-      </c>
-      <c r="Q18" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="921" t="n">
-        <v>9</v>
-      </c>
-      <c r="S18" s="577" t="n">
-        <f aca="false">SUM(Q18:R18)</f>
-        <v>9</v>
+      <c r="B18" s="2" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>2849</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="975" t="s">
-        <v>454</v>
-      </c>
-      <c r="B19" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="976" t="s">
-        <v>454</v>
-      </c>
-      <c r="D19" s="919" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="921" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" s="977" t="s">
-        <v>454</v>
-      </c>
-      <c r="G19" s="919" t="n">
-        <v>10</v>
-      </c>
-      <c r="H19" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="I19" s="977" t="s">
-        <v>454</v>
-      </c>
-      <c r="J19" s="919" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" s="977" t="s">
-        <v>454</v>
-      </c>
-      <c r="M19" s="919" t="n">
-        <v>6</v>
-      </c>
-      <c r="N19" s="921" t="n">
-        <v>8</v>
-      </c>
-      <c r="O19" s="577" t="n">
-        <f aca="false">SUM(M19:N19)</f>
-        <v>14</v>
-      </c>
-      <c r="P19" s="977" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q19" s="919" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" s="921" t="n">
-        <v>3</v>
-      </c>
-      <c r="S19" s="577" t="n">
-        <f aca="false">SUM(Q19:R19)</f>
-        <v>8</v>
+      <c r="B19" s="2" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C19" s="660" t="s">
+        <v>2850</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="978" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="979" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="919" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" s="921" t="n">
-        <v>6</v>
-      </c>
-      <c r="F20" s="980" t="s">
-        <v>100</v>
-      </c>
-      <c r="G20" s="919" t="n">
-        <v>6</v>
-      </c>
-      <c r="H20" s="22" t="n">
-        <v>21</v>
-      </c>
-      <c r="I20" s="980" t="s">
-        <v>100</v>
-      </c>
-      <c r="J20" s="919" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="L20" s="980" t="s">
-        <v>100</v>
-      </c>
-      <c r="M20" s="919" t="n">
-        <v>11</v>
-      </c>
-      <c r="N20" s="921" t="n">
-        <v>15</v>
-      </c>
-      <c r="O20" s="577" t="n">
-        <f aca="false">SUM(M20:N20)</f>
-        <v>26</v>
-      </c>
-      <c r="P20" s="980" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q20" s="919" t="n">
-        <v>6</v>
-      </c>
-      <c r="R20" s="921" t="n">
-        <v>12</v>
-      </c>
-      <c r="S20" s="577" t="n">
-        <f aca="false">SUM(Q20:R20)</f>
-        <v>18</v>
+      <c r="B20" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>2851</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="546" t="s">
-        <v>1414</v>
-      </c>
-      <c r="B21" s="916" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="981" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D21" s="916" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="917" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="982" t="s">
-        <v>1414</v>
-      </c>
-      <c r="G21" s="916" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="982" t="s">
-        <v>1414</v>
-      </c>
-      <c r="J21" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" s="982" t="s">
-        <v>1414</v>
-      </c>
-      <c r="M21" s="919" t="n">
-        <v>4</v>
-      </c>
-      <c r="N21" s="921" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" s="577" t="n">
-        <f aca="false">SUM(M21:N21)</f>
-        <v>6</v>
-      </c>
-      <c r="P21" s="982" t="s">
-        <v>1414</v>
-      </c>
-      <c r="Q21" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="921" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" s="577" t="n">
-        <f aca="false">SUM(Q21:R21)</f>
-        <v>1</v>
+      <c r="B21" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C21" s="660" t="s">
+        <v>2852</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="559" t="s">
-        <v>1440</v>
-      </c>
-      <c r="B22" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="559" t="s">
-        <v>1440</v>
-      </c>
-      <c r="D22" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="921" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="559" t="s">
-        <v>1440</v>
-      </c>
-      <c r="G22" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="559" t="s">
-        <v>1440</v>
-      </c>
-      <c r="J22" s="919" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="559" t="s">
-        <v>1440</v>
-      </c>
-      <c r="M22" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="921" t="n">
-        <v>6</v>
-      </c>
-      <c r="O22" s="577" t="n">
-        <f aca="false">SUM(M22:N22)</f>
-        <v>6</v>
-      </c>
-      <c r="P22" s="559" t="s">
-        <v>1440</v>
-      </c>
-      <c r="Q22" s="919" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" s="921" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="577" t="n">
-        <f aca="false">SUM(Q22:R22)</f>
-        <v>1</v>
+      <c r="B22" s="2" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>2854</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="635" t="s">
-        <v>1575</v>
-      </c>
-      <c r="B23" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="635" t="s">
-        <v>1575</v>
-      </c>
-      <c r="D23" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="635" t="s">
-        <v>1575</v>
-      </c>
-      <c r="G23" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="635" t="s">
-        <v>1575</v>
-      </c>
-      <c r="J23" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="635" t="s">
-        <v>1575</v>
-      </c>
-      <c r="M23" s="919" t="n">
-        <v>11</v>
-      </c>
-      <c r="N23" s="921" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="577" t="n">
-        <f aca="false">SUM(M23:N23)</f>
-        <v>11</v>
-      </c>
-      <c r="P23" s="635" t="s">
-        <v>1575</v>
-      </c>
-      <c r="Q23" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="921" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="577" t="n">
-        <f aca="false">SUM(Q23:R23)</f>
-        <v>0</v>
+      <c r="B23" s="2" t="s">
+        <v>2855</v>
+      </c>
+      <c r="C23" s="660" t="s">
+        <v>2856</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="983"/>
-      <c r="B24" s="916" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="984"/>
-      <c r="D24" s="916" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="917" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="985"/>
-      <c r="G24" s="919" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="985"/>
-      <c r="J24" s="919"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="985"/>
-      <c r="M24" s="919"/>
-      <c r="N24" s="921"/>
-      <c r="O24" s="600"/>
-      <c r="P24" s="985"/>
-      <c r="Q24" s="919"/>
-      <c r="R24" s="921"/>
-      <c r="S24" s="600"/>
+      <c r="B24" s="2" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>2857</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="986"/>
-      <c r="B25" s="987" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="988"/>
-      <c r="D25" s="987" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="989" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="990"/>
-      <c r="G25" s="987" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="990"/>
-      <c r="J25" s="987"/>
-      <c r="K25" s="97"/>
-      <c r="L25" s="990"/>
-      <c r="M25" s="987"/>
-      <c r="N25" s="989"/>
-      <c r="O25" s="626"/>
-      <c r="P25" s="990"/>
-      <c r="Q25" s="987"/>
-      <c r="R25" s="989"/>
-      <c r="S25" s="626"/>
-    </row>
-    <row r="26" s="312" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="68" t="s">
-        <v>2733</v>
-      </c>
-      <c r="B26" s="705" t="n">
-        <f aca="false">SUM(B3:B25)</f>
-        <v>151</v>
-      </c>
-      <c r="C26" s="68" t="s">
-        <v>2733</v>
-      </c>
-      <c r="D26" s="991" t="n">
-        <f aca="false">SUM(D3:D25)</f>
-        <v>111</v>
-      </c>
-      <c r="E26" s="992" t="n">
-        <f aca="false">SUM(E3:E25)</f>
-        <v>64</v>
-      </c>
-      <c r="F26" s="68" t="s">
-        <v>2733</v>
-      </c>
-      <c r="G26" s="991" t="n">
-        <f aca="false">SUM(G3:G25)</f>
-        <v>200</v>
-      </c>
-      <c r="H26" s="70" t="n">
-        <f aca="false">SUM(H3:H25)</f>
-        <v>138</v>
-      </c>
-      <c r="I26" s="68" t="s">
-        <v>2733</v>
-      </c>
-      <c r="J26" s="991" t="n">
-        <f aca="false">SUM(J3:J25)</f>
-        <v>100</v>
-      </c>
-      <c r="K26" s="70" t="n">
-        <f aca="false">SUM(K3:K25)</f>
-        <v>64</v>
-      </c>
-      <c r="L26" s="68" t="s">
-        <v>2733</v>
-      </c>
-      <c r="M26" s="993" t="n">
-        <f aca="false">SUM(M3:M25)</f>
-        <v>201</v>
-      </c>
-      <c r="N26" s="994" t="n">
-        <f aca="false">SUM(N3:N25)</f>
-        <v>133</v>
-      </c>
-      <c r="O26" s="847" t="n">
-        <f aca="false">SUM(O3:O25)</f>
-        <v>334</v>
-      </c>
-      <c r="P26" s="68" t="s">
-        <v>2733</v>
-      </c>
-      <c r="Q26" s="993" t="n">
-        <f aca="false">SUM(Q3:Q25)</f>
-        <v>101</v>
-      </c>
-      <c r="R26" s="994" t="n">
-        <f aca="false">SUM(R3:R25)</f>
-        <v>68</v>
-      </c>
-      <c r="S26" s="847" t="n">
-        <f aca="false">SUM(S3:S25)</f>
-        <v>169</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B25" s="2" t="s">
+        <v>2858</v>
+      </c>
+      <c r="C25" s="660" t="s">
+        <v>2859</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="2" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="2" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C27" s="660" t="s">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="2" t="s">
+        <v>2861</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="2" t="s">
+        <v>2863</v>
+      </c>
+      <c r="C29" s="660" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="2" t="s">
+        <v>2865</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>2866</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S2"/>
-  <mergeCells count="6">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="P1:S1"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -57930,6 +56437,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>